--- a/database/event/3428/event_3428_evp_summary.xlsx
+++ b/database/event/3428/event_3428_evp_summary.xlsx
@@ -496,28 +496,28 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.4757</v>
+        <v>9.7438</v>
       </c>
       <c r="C2" t="n">
-        <v>0.834</v>
+        <v>0.8576</v>
       </c>
       <c r="D2" t="n">
-        <v>3.4066</v>
+        <v>3.438</v>
       </c>
       <c r="E2" t="n">
-        <v>9.4757</v>
+        <v>9.7438</v>
       </c>
       <c r="F2" t="n">
-        <v>3.2166</v>
+        <v>3.4847</v>
       </c>
       <c r="G2" t="n">
         <v>6.2591</v>
       </c>
       <c r="H2" t="n">
-        <v>3.2166</v>
+        <v>3.4847</v>
       </c>
       <c r="I2" t="n">
-        <v>2.6071</v>
+        <v>2.8244</v>
       </c>
       <c r="J2" t="n">
         <v>6.2591</v>
@@ -529,7 +529,7 @@
         <v>97</v>
       </c>
       <c r="M2" t="n">
-        <v>8.866199999999999</v>
+        <v>9.083500000000001</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,28 +542,28 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7129</v>
+        <v>5.7154</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5028</v>
+        <v>0.5031</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8865</v>
+        <v>1.8331</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7129</v>
+        <v>5.7154</v>
       </c>
       <c r="F3" t="n">
-        <v>3.401</v>
+        <v>3.4035</v>
       </c>
       <c r="G3" t="n">
         <v>2.3119</v>
       </c>
       <c r="H3" t="n">
-        <v>3.401</v>
+        <v>3.4035</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7566</v>
+        <v>2.7586</v>
       </c>
       <c r="J3" t="n">
         <v>2.3119</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0685</v>
+        <v>5.0705</v>
       </c>
       <c r="N3" t="n">
         <v>227</v>
@@ -584,277 +584,277 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.8049</v>
+        <v>3.796</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3349</v>
+        <v>0.3341</v>
       </c>
       <c r="D4" t="n">
-        <v>1.1157</v>
+        <v>1.0684</v>
       </c>
       <c r="E4" t="n">
-        <v>3.8049</v>
+        <v>3.796</v>
       </c>
       <c r="F4" t="n">
-        <v>3.8049</v>
+        <v>3.0353</v>
       </c>
       <c r="G4" t="n">
-        <v>0</v>
+        <v>0.7607</v>
       </c>
       <c r="H4" t="n">
-        <v>3.8049</v>
+        <v>3.0353</v>
       </c>
       <c r="I4" t="n">
-        <v>3.8226</v>
+        <v>2.4602</v>
       </c>
       <c r="J4" t="n">
-        <v>0</v>
+        <v>0.7607</v>
       </c>
       <c r="K4" t="n">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M4" t="n">
-        <v>3.8226</v>
+        <v>3.2209</v>
       </c>
       <c r="N4" t="n">
-        <v>156</v>
+        <v>91</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.5131</v>
+        <v>3.7907</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3092</v>
+        <v>0.3337</v>
       </c>
       <c r="D5" t="n">
-        <v>0.9979</v>
+        <v>1.0663</v>
       </c>
       <c r="E5" t="n">
-        <v>3.5131</v>
+        <v>3.7907</v>
       </c>
       <c r="F5" t="n">
-        <v>1.1906</v>
+        <v>3.7907</v>
       </c>
       <c r="G5" t="n">
-        <v>2.3225</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1.1906</v>
+        <v>3.7907</v>
       </c>
       <c r="I5" t="n">
-        <v>0.965</v>
+        <v>3.8226</v>
       </c>
       <c r="J5" t="n">
-        <v>2.3225</v>
+        <v>0</v>
       </c>
       <c r="K5" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="L5" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2875</v>
+        <v>3.8226</v>
       </c>
       <c r="N5" t="n">
-        <v>227</v>
+        <v>156</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.1728</v>
+        <v>3.532</v>
       </c>
       <c r="C6" t="n">
-        <v>0.2793</v>
+        <v>0.3109</v>
       </c>
       <c r="D6" t="n">
-        <v>0.8604000000000001</v>
+        <v>0.9631999999999999</v>
       </c>
       <c r="E6" t="n">
-        <v>3.1728</v>
+        <v>3.532</v>
       </c>
       <c r="F6" t="n">
-        <v>2.4121</v>
+        <v>1.2095</v>
       </c>
       <c r="G6" t="n">
-        <v>0.7607</v>
+        <v>2.3225</v>
       </c>
       <c r="H6" t="n">
-        <v>2.4121</v>
+        <v>1.2095</v>
       </c>
       <c r="I6" t="n">
-        <v>1.9551</v>
+        <v>0.9802999999999999</v>
       </c>
       <c r="J6" t="n">
-        <v>0.7607</v>
+        <v>2.3225</v>
       </c>
       <c r="K6" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="L6" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="M6" t="n">
-        <v>2.7158</v>
+        <v>3.3028</v>
       </c>
       <c r="N6" t="n">
-        <v>91</v>
+        <v>227</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.0978</v>
+        <v>3.3207</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2727</v>
+        <v>0.2923</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8300999999999999</v>
+        <v>0.8791</v>
       </c>
       <c r="E7" t="n">
-        <v>3.0978</v>
+        <v>3.3207</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0508</v>
+        <v>2.0468</v>
       </c>
       <c r="G7" t="n">
-        <v>1.047</v>
+        <v>1.2739</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0508</v>
+        <v>2.0468</v>
       </c>
       <c r="I7" t="n">
-        <v>1.6622</v>
+        <v>1.659</v>
       </c>
       <c r="J7" t="n">
-        <v>1.047</v>
+        <v>1.2739</v>
       </c>
       <c r="K7" t="n">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="L7" t="n">
-        <v>123</v>
+        <v>97</v>
       </c>
       <c r="M7" t="n">
-        <v>2.7092</v>
+        <v>2.9329</v>
       </c>
       <c r="N7" t="n">
-        <v>255</v>
+        <v>227</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0404</v>
+        <v>3.0978</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2676</v>
+        <v>0.2727</v>
       </c>
       <c r="D8" t="n">
-        <v>0.8069</v>
+        <v>0.7903</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0404</v>
+        <v>3.0978</v>
       </c>
       <c r="F8" t="n">
-        <v>3.0404</v>
+        <v>2.0508</v>
       </c>
       <c r="G8" t="n">
-        <v>0</v>
+        <v>1.047</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0404</v>
+        <v>2.0508</v>
       </c>
       <c r="I8" t="n">
-        <v>3.0546</v>
+        <v>1.6622</v>
       </c>
       <c r="J8" t="n">
-        <v>0</v>
+        <v>1.047</v>
       </c>
       <c r="K8" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="L8" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M8" t="n">
-        <v>3.0546</v>
+        <v>2.7092</v>
       </c>
       <c r="N8" t="n">
-        <v>153</v>
+        <v>255</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>2.8468</v>
+        <v>3.0291</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2506</v>
+        <v>0.2666</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7287</v>
+        <v>0.7629</v>
       </c>
       <c r="E9" t="n">
-        <v>2.8468</v>
+        <v>3.0291</v>
       </c>
       <c r="F9" t="n">
-        <v>1.5729</v>
+        <v>3.0291</v>
       </c>
       <c r="G9" t="n">
-        <v>1.2739</v>
+        <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>1.5729</v>
+        <v>3.0291</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2749</v>
+        <v>3.0546</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2739</v>
+        <v>0</v>
       </c>
       <c r="K9" t="n">
-        <v>130</v>
+        <v>153</v>
       </c>
       <c r="L9" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>2.5488</v>
+        <v>3.0546</v>
       </c>
       <c r="N9" t="n">
-        <v>227</v>
+        <v>153</v>
       </c>
     </row>
     <row r="10">
@@ -864,28 +864,28 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.4923</v>
+        <v>2.5952</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2194</v>
+        <v>0.2284</v>
       </c>
       <c r="D10" t="n">
-        <v>0.5855</v>
+        <v>0.59</v>
       </c>
       <c r="E10" t="n">
-        <v>2.4923</v>
+        <v>2.5952</v>
       </c>
       <c r="F10" t="n">
-        <v>1.7853</v>
+        <v>1.8882</v>
       </c>
       <c r="G10" t="n">
         <v>0.707</v>
       </c>
       <c r="H10" t="n">
-        <v>1.7853</v>
+        <v>1.8882</v>
       </c>
       <c r="I10" t="n">
-        <v>1.447</v>
+        <v>1.5304</v>
       </c>
       <c r="J10" t="n">
         <v>0.707</v>
@@ -897,7 +897,7 @@
         <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>2.154</v>
+        <v>2.2374</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.2488</v>
+        <v>2.5265</v>
       </c>
       <c r="C11" t="n">
-        <v>0.1979</v>
+        <v>0.2224</v>
       </c>
       <c r="D11" t="n">
-        <v>0.4871</v>
+        <v>0.5626</v>
       </c>
       <c r="E11" t="n">
-        <v>2.2488</v>
+        <v>2.5265</v>
       </c>
       <c r="F11" t="n">
-        <v>1.3164</v>
+        <v>1.5941</v>
       </c>
       <c r="G11" t="n">
         <v>0.9324</v>
       </c>
       <c r="H11" t="n">
-        <v>1.3164</v>
+        <v>1.5941</v>
       </c>
       <c r="I11" t="n">
-        <v>1.067</v>
+        <v>1.2921</v>
       </c>
       <c r="J11" t="n">
         <v>0.9324</v>
@@ -943,7 +943,7 @@
         <v>75</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9994</v>
+        <v>2.2245</v>
       </c>
       <c r="N11" t="n">
         <v>126</v>
@@ -956,25 +956,25 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.9744</v>
+        <v>1.967</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1738</v>
+        <v>0.1731</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3763</v>
+        <v>0.3397</v>
       </c>
       <c r="E12" t="n">
-        <v>1.9744</v>
+        <v>1.967</v>
       </c>
       <c r="F12" t="n">
-        <v>1.9744</v>
+        <v>1.967</v>
       </c>
       <c r="G12" t="n">
         <v>0</v>
       </c>
       <c r="H12" t="n">
-        <v>1.9744</v>
+        <v>1.967</v>
       </c>
       <c r="I12" t="n">
         <v>1.9836</v>
@@ -998,231 +998,231 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>dragonfly</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.7264</v>
+        <v>1.9089</v>
       </c>
       <c r="C13" t="n">
-        <v>0.152</v>
+        <v>0.168</v>
       </c>
       <c r="D13" t="n">
-        <v>0.2761</v>
+        <v>0.3166</v>
       </c>
       <c r="E13" t="n">
-        <v>1.7264</v>
+        <v>1.9089</v>
       </c>
       <c r="F13" t="n">
-        <v>1.7264</v>
+        <v>2.2446</v>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>-0.3357</v>
       </c>
       <c r="H13" t="n">
-        <v>1.7264</v>
+        <v>2.2446</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7345</v>
+        <v>1.8193</v>
       </c>
       <c r="J13" t="n">
-        <v>0</v>
+        <v>-0.3357</v>
       </c>
       <c r="K13" t="n">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7345</v>
+        <v>1.4836</v>
       </c>
       <c r="N13" t="n">
-        <v>156</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.5835</v>
+        <v>1.7224</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1394</v>
+        <v>0.1516</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2183</v>
+        <v>0.2423</v>
       </c>
       <c r="E14" t="n">
-        <v>1.5835</v>
+        <v>1.7224</v>
       </c>
       <c r="F14" t="n">
-        <v>1.9192</v>
+        <v>1.7224</v>
       </c>
       <c r="G14" t="n">
-        <v>-0.3357</v>
+        <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.9192</v>
+        <v>1.7224</v>
       </c>
       <c r="I14" t="n">
-        <v>1.5556</v>
+        <v>1.7369</v>
       </c>
       <c r="J14" t="n">
-        <v>-0.3357</v>
+        <v>0</v>
       </c>
       <c r="K14" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="L14" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.2199</v>
+        <v>1.7369</v>
       </c>
       <c r="N14" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.1228</v>
+        <v>1.4391</v>
       </c>
       <c r="C15" t="n">
-        <v>0.0988</v>
+        <v>0.1267</v>
       </c>
       <c r="D15" t="n">
-        <v>0.0322</v>
+        <v>0.1294</v>
       </c>
       <c r="E15" t="n">
-        <v>1.1228</v>
+        <v>1.4391</v>
       </c>
       <c r="F15" t="n">
-        <v>1.0813</v>
+        <v>1.9406</v>
       </c>
       <c r="G15" t="n">
-        <v>0.0415</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="H15" t="n">
-        <v>1.0813</v>
+        <v>1.9406</v>
       </c>
       <c r="I15" t="n">
-        <v>0.8764</v>
+        <v>1.5729</v>
       </c>
       <c r="J15" t="n">
-        <v>0.0415</v>
+        <v>-0.5014999999999999</v>
       </c>
       <c r="K15" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L15" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="M15" t="n">
-        <v>0.9178999999999999</v>
+        <v>1.0714</v>
       </c>
       <c r="N15" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>phr</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>0.8977000000000001</v>
+        <v>1.3089</v>
       </c>
       <c r="C16" t="n">
-        <v>0.079</v>
+        <v>0.1152</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.0587</v>
+        <v>0.0776</v>
       </c>
       <c r="E16" t="n">
-        <v>0.8977000000000001</v>
+        <v>1.3089</v>
       </c>
       <c r="F16" t="n">
-        <v>0.8977000000000001</v>
+        <v>1.2674</v>
       </c>
       <c r="G16" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8977000000000001</v>
+        <v>1.2674</v>
       </c>
       <c r="I16" t="n">
-        <v>0.9019</v>
+        <v>1.0273</v>
       </c>
       <c r="J16" t="n">
-        <v>0</v>
+        <v>0.0415</v>
       </c>
       <c r="K16" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="L16" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M16" t="n">
-        <v>0.9019</v>
+        <v>1.0688</v>
       </c>
       <c r="N16" t="n">
-        <v>153</v>
+        <v>126</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>phr</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.874</v>
+        <v>0.8944</v>
       </c>
       <c r="C17" t="n">
-        <v>0.0769</v>
+        <v>0.07870000000000001</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0683</v>
+        <v>-0.0876</v>
       </c>
       <c r="E17" t="n">
-        <v>0.874</v>
+        <v>0.8944</v>
       </c>
       <c r="F17" t="n">
-        <v>1.3755</v>
+        <v>0.8944</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0</v>
       </c>
       <c r="H17" t="n">
-        <v>1.3755</v>
+        <v>0.8944</v>
       </c>
       <c r="I17" t="n">
-        <v>1.1148</v>
+        <v>0.9019</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0</v>
       </c>
       <c r="K17" t="n">
-        <v>42</v>
+        <v>153</v>
       </c>
       <c r="L17" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M17" t="n">
-        <v>0.6133000000000001</v>
+        <v>0.9019</v>
       </c>
       <c r="N17" t="n">
-        <v>91</v>
+        <v>153</v>
       </c>
     </row>
     <row r="18">
@@ -1232,25 +1232,25 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8095</v>
+        <v>0.8065</v>
       </c>
       <c r="C18" t="n">
-        <v>0.0713</v>
+        <v>0.07099999999999999</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.09429999999999999</v>
+        <v>-0.1226</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8095</v>
+        <v>0.8065</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8095</v>
+        <v>0.8065</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8095</v>
+        <v>0.8065</v>
       </c>
       <c r="I18" t="n">
         <v>0.8133</v>
@@ -1278,25 +1278,25 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7524</v>
+        <v>0.7496</v>
       </c>
       <c r="C19" t="n">
-        <v>0.06619999999999999</v>
+        <v>0.066</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1174</v>
+        <v>-0.1453</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7524</v>
+        <v>0.7496</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7524</v>
+        <v>0.7496</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7524</v>
+        <v>0.7496</v>
       </c>
       <c r="I19" t="n">
         <v>0.7559</v>
@@ -1320,139 +1320,139 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.6954</v>
+        <v>0.7005</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0612</v>
+        <v>0.0617</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1404</v>
+        <v>-0.1648</v>
       </c>
       <c r="E20" t="n">
-        <v>0.6954</v>
+        <v>0.7005</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.0344</v>
+        <v>1.5353</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7298</v>
+        <v>-0.8348</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.0344</v>
+        <v>1.5353</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.0279</v>
+        <v>1.2444</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7298</v>
+        <v>-0.8348</v>
       </c>
       <c r="K20" t="n">
-        <v>132</v>
+        <v>51</v>
       </c>
       <c r="L20" t="n">
-        <v>123</v>
+        <v>75</v>
       </c>
       <c r="M20" t="n">
-        <v>0.7019</v>
+        <v>0.4096</v>
       </c>
       <c r="N20" t="n">
-        <v>255</v>
+        <v>126</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6475</v>
+        <v>0.6954</v>
       </c>
       <c r="C21" t="n">
-        <v>0.057</v>
+        <v>0.0612</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1598</v>
+        <v>-0.1669</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6475</v>
+        <v>0.6954</v>
       </c>
       <c r="F21" t="n">
-        <v>0.6475</v>
+        <v>-0.0344</v>
       </c>
       <c r="G21" t="n">
-        <v>0</v>
+        <v>0.7298</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6475</v>
+        <v>-0.0344</v>
       </c>
       <c r="I21" t="n">
-        <v>0.6505</v>
+        <v>-0.0279</v>
       </c>
       <c r="J21" t="n">
-        <v>0</v>
+        <v>0.7298</v>
       </c>
       <c r="K21" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="L21" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M21" t="n">
-        <v>0.6505</v>
+        <v>0.7019</v>
       </c>
       <c r="N21" t="n">
-        <v>153</v>
+        <v>255</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6146</v>
+        <v>0.6451</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0541</v>
+        <v>0.0568</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1731</v>
+        <v>-0.1869</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6146</v>
+        <v>0.6451</v>
       </c>
       <c r="F22" t="n">
-        <v>1.4494</v>
+        <v>0.6451</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.8348</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.4494</v>
+        <v>0.6451</v>
       </c>
       <c r="I22" t="n">
-        <v>1.1748</v>
+        <v>0.6505</v>
       </c>
       <c r="J22" t="n">
-        <v>-0.8348</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="L22" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.3400000000000001</v>
+        <v>0.6505</v>
       </c>
       <c r="N22" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1468,7 +1468,7 @@
         <v>0.0336</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2669</v>
+        <v>-0.2916</v>
       </c>
       <c r="E23" t="n">
         <v>0.3823</v>
@@ -1514,7 +1514,7 @@
         <v>0.004</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4032</v>
+        <v>-0.426</v>
       </c>
       <c r="E24" t="n">
         <v>0.0449</v>
@@ -1550,35 +1550,35 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1955</v>
+        <v>-0.1547</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0172</v>
+        <v>-0.0136</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5003</v>
+        <v>-0.5054999999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1955</v>
+        <v>-0.1547</v>
       </c>
       <c r="F25" t="n">
-        <v>0.2121</v>
+        <v>-0.0459</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.4076</v>
+        <v>-0.1088</v>
       </c>
       <c r="H25" t="n">
-        <v>0.2121</v>
+        <v>-0.0459</v>
       </c>
       <c r="I25" t="n">
-        <v>0.1719</v>
+        <v>-0.0372</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.4076</v>
+        <v>-0.1088</v>
       </c>
       <c r="K25" t="n">
         <v>132</v>
@@ -1587,7 +1587,7 @@
         <v>123</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.2357</v>
+        <v>-0.146</v>
       </c>
       <c r="N25" t="n">
         <v>255</v>
@@ -1596,35 +1596,35 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.3464</v>
+        <v>-0.1955</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0305</v>
+        <v>-0.0172</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5613</v>
+        <v>-0.5218</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.3464</v>
+        <v>-0.1955</v>
       </c>
       <c r="F26" t="n">
-        <v>-0.2376</v>
+        <v>0.2121</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.1088</v>
+        <v>-0.4076</v>
       </c>
       <c r="H26" t="n">
-        <v>-0.2376</v>
+        <v>0.2121</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.1926</v>
+        <v>0.1719</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.1088</v>
+        <v>-0.4076</v>
       </c>
       <c r="K26" t="n">
         <v>132</v>
@@ -1633,7 +1633,7 @@
         <v>123</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.3014</v>
+        <v>-0.2357</v>
       </c>
       <c r="N26" t="n">
         <v>255</v>
@@ -1652,7 +1652,7 @@
         <v>-0.0313</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5651</v>
+        <v>-0.5856</v>
       </c>
       <c r="E27" t="n">
         <v>-0.3557</v>
@@ -1698,7 +1698,7 @@
         <v>-0.0394</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6021</v>
+        <v>-0.6222</v>
       </c>
       <c r="E28" t="n">
         <v>-0.4474</v>
@@ -1738,28 +1738,28 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4681</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0479</v>
+        <v>-0.0412</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6411</v>
+        <v>-0.6304</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.5439000000000001</v>
+        <v>-0.4681</v>
       </c>
       <c r="F29" t="n">
-        <v>0.4561</v>
+        <v>0.5319</v>
       </c>
       <c r="G29" t="n">
         <v>-1</v>
       </c>
       <c r="H29" t="n">
-        <v>0.4561</v>
+        <v>0.5319</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3697</v>
+        <v>0.4311</v>
       </c>
       <c r="J29" t="n">
         <v>-1</v>
@@ -1771,7 +1771,7 @@
         <v>49</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.6303000000000001</v>
+        <v>-0.5689</v>
       </c>
       <c r="N29" t="n">
         <v>91</v>
@@ -1790,7 +1790,7 @@
         <v>-0.0552</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6745</v>
+        <v>-0.6935</v>
       </c>
       <c r="E30" t="n">
         <v>-0.6266</v>
@@ -1836,7 +1836,7 @@
         <v>-0.0649</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7191</v>
+        <v>-0.7375</v>
       </c>
       <c r="E31" t="n">
         <v>-0.737</v>
@@ -1882,7 +1882,7 @@
         <v>-0.07049999999999999</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7451</v>
+        <v>-0.7631</v>
       </c>
       <c r="E32" t="n">
         <v>-0.8013</v>
@@ -1922,25 +1922,25 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0254</v>
+        <v>-1.0216</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.09030000000000001</v>
+        <v>-0.08989999999999999</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8356</v>
+        <v>-0.8509</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0254</v>
+        <v>-1.0216</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0254</v>
+        <v>-1.0216</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0254</v>
+        <v>-1.0216</v>
       </c>
       <c r="I33" t="n">
         <v>-1.0302</v>
@@ -1974,7 +1974,7 @@
         <v>-0.0968</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8659</v>
+        <v>-0.8823</v>
       </c>
       <c r="E34" t="n">
         <v>-1.1003</v>
@@ -2020,7 +2020,7 @@
         <v>-0.101</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.8851</v>
+        <v>-0.9013</v>
       </c>
       <c r="E35" t="n">
         <v>-1.148</v>
@@ -2066,7 +2066,7 @@
         <v>-0.1152</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9500999999999999</v>
+        <v>-0.9654</v>
       </c>
       <c r="E36" t="n">
         <v>-1.3089</v>
@@ -2112,7 +2112,7 @@
         <v>-0.1199</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9716</v>
+        <v>-0.9866</v>
       </c>
       <c r="E37" t="n">
         <v>-1.3621</v>
@@ -2158,7 +2158,7 @@
         <v>-0.1228</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.985</v>
+        <v>-0.9998</v>
       </c>
       <c r="E38" t="n">
         <v>-1.3953</v>
@@ -2198,25 +2198,25 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6663</v>
+        <v>-1.6601</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1467</v>
+        <v>-0.1461</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.0945</v>
+        <v>-1.1053</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6663</v>
+        <v>-1.6601</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6663</v>
+        <v>-1.6601</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6663</v>
+        <v>-1.6601</v>
       </c>
       <c r="I39" t="n">
         <v>-1.6741</v>
@@ -2250,7 +2250,7 @@
         <v>-0.1585</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1486</v>
+        <v>-1.1611</v>
       </c>
       <c r="E40" t="n">
         <v>-1.8002</v>
@@ -2296,7 +2296,7 @@
         <v>-0.2379</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5133</v>
+        <v>-1.5208</v>
       </c>
       <c r="E41" t="n">
         <v>-2.703</v>

--- a/database/event/3428/event_3428_evp_summary.xlsx
+++ b/database/event/3428/event_3428_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>9.7438</v>
+        <v>8.3866</v>
       </c>
       <c r="C2" t="n">
-        <v>0.8576</v>
+        <v>0.7382</v>
       </c>
       <c r="D2" t="n">
-        <v>3.438</v>
+        <v>3.1481</v>
       </c>
       <c r="E2" t="n">
-        <v>9.7438</v>
+        <v>8.3866</v>
       </c>
       <c r="F2" t="n">
-        <v>3.4847</v>
+        <v>3.1316</v>
       </c>
       <c r="G2" t="n">
-        <v>6.2591</v>
+        <v>5.255</v>
       </c>
       <c r="H2" t="n">
-        <v>3.4847</v>
+        <v>5.5474</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8244</v>
+        <v>2.8844</v>
       </c>
       <c r="J2" t="n">
-        <v>6.2591</v>
+        <v>5.255</v>
       </c>
       <c r="K2" t="n">
         <v>130</v>
@@ -529,7 +529,7 @@
         <v>97</v>
       </c>
       <c r="M2" t="n">
-        <v>9.083500000000001</v>
+        <v>8.1394</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.7154</v>
+        <v>5.4397</v>
       </c>
       <c r="C3" t="n">
-        <v>0.5031</v>
+        <v>0.4788</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8331</v>
+        <v>1.8177</v>
       </c>
       <c r="E3" t="n">
-        <v>5.7154</v>
+        <v>5.4397</v>
       </c>
       <c r="F3" t="n">
-        <v>3.4035</v>
+        <v>3.3302</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3119</v>
+        <v>2.1095</v>
       </c>
       <c r="H3" t="n">
-        <v>3.4035</v>
+        <v>6.2473</v>
       </c>
       <c r="I3" t="n">
-        <v>2.7586</v>
+        <v>3.2483</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3119</v>
+        <v>2.1095</v>
       </c>
       <c r="K3" t="n">
         <v>130</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>5.0705</v>
+        <v>5.3578</v>
       </c>
       <c r="N3" t="n">
         <v>227</v>
@@ -584,185 +584,185 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>aizy</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>3.796</v>
+        <v>4.2636</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3341</v>
+        <v>0.3753</v>
       </c>
       <c r="D4" t="n">
-        <v>1.0684</v>
+        <v>1.2868</v>
       </c>
       <c r="E4" t="n">
-        <v>3.796</v>
+        <v>4.2636</v>
       </c>
       <c r="F4" t="n">
-        <v>3.0353</v>
+        <v>2.2629</v>
       </c>
       <c r="G4" t="n">
-        <v>0.7607</v>
+        <v>2.0007</v>
       </c>
       <c r="H4" t="n">
-        <v>3.0353</v>
+        <v>2.4866</v>
       </c>
       <c r="I4" t="n">
-        <v>2.4602</v>
+        <v>1.2929</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7607</v>
+        <v>2.0007</v>
       </c>
       <c r="K4" t="n">
-        <v>42</v>
+        <v>130</v>
       </c>
       <c r="L4" t="n">
-        <v>49</v>
+        <v>97</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2209</v>
+        <v>3.2936</v>
       </c>
       <c r="N4" t="n">
-        <v>91</v>
+        <v>227</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>Kjaerbye</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>3.7907</v>
+        <v>4.0123</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3337</v>
+        <v>0.3532</v>
       </c>
       <c r="D5" t="n">
-        <v>1.0663</v>
+        <v>1.1733</v>
       </c>
       <c r="E5" t="n">
-        <v>3.7907</v>
+        <v>4.0123</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7907</v>
+        <v>2.5244</v>
       </c>
       <c r="G5" t="n">
-        <v>0</v>
+        <v>1.4879</v>
       </c>
       <c r="H5" t="n">
-        <v>3.7907</v>
+        <v>3.408</v>
       </c>
       <c r="I5" t="n">
-        <v>3.8226</v>
+        <v>1.772</v>
       </c>
       <c r="J5" t="n">
-        <v>0</v>
+        <v>1.4879</v>
       </c>
       <c r="K5" t="n">
-        <v>156</v>
+        <v>130</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>3.8226</v>
+        <v>3.2599</v>
       </c>
       <c r="N5" t="n">
-        <v>156</v>
+        <v>227</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>aizy</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.532</v>
+        <v>3.6746</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3109</v>
+        <v>0.3234</v>
       </c>
       <c r="D6" t="n">
-        <v>0.9631999999999999</v>
+        <v>1.0209</v>
       </c>
       <c r="E6" t="n">
-        <v>3.532</v>
+        <v>3.6746</v>
       </c>
       <c r="F6" t="n">
-        <v>1.2095</v>
+        <v>3.6746</v>
       </c>
       <c r="G6" t="n">
-        <v>2.3225</v>
+        <v>0</v>
       </c>
       <c r="H6" t="n">
-        <v>1.2095</v>
+        <v>4.709</v>
       </c>
       <c r="I6" t="n">
-        <v>0.9802999999999999</v>
+        <v>4.9027</v>
       </c>
       <c r="J6" t="n">
-        <v>2.3225</v>
+        <v>0</v>
       </c>
       <c r="K6" t="n">
-        <v>130</v>
+        <v>156</v>
       </c>
       <c r="L6" t="n">
-        <v>97</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>3.3028</v>
+        <v>4.9027</v>
       </c>
       <c r="N6" t="n">
-        <v>227</v>
+        <v>156</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Kjaerbye</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.3207</v>
+        <v>3.6238</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2923</v>
+        <v>0.319</v>
       </c>
       <c r="D7" t="n">
-        <v>0.8791</v>
+        <v>0.998</v>
       </c>
       <c r="E7" t="n">
-        <v>3.3207</v>
+        <v>3.6238</v>
       </c>
       <c r="F7" t="n">
-        <v>2.0468</v>
+        <v>2.8472</v>
       </c>
       <c r="G7" t="n">
-        <v>1.2739</v>
+        <v>0.7766</v>
       </c>
       <c r="H7" t="n">
-        <v>2.0468</v>
+        <v>4.5454</v>
       </c>
       <c r="I7" t="n">
-        <v>1.659</v>
+        <v>2.3634</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2739</v>
+        <v>0.7766</v>
       </c>
       <c r="K7" t="n">
-        <v>130</v>
+        <v>42</v>
       </c>
       <c r="L7" t="n">
-        <v>97</v>
+        <v>49</v>
       </c>
       <c r="M7" t="n">
-        <v>2.9329</v>
+        <v>3.14</v>
       </c>
       <c r="N7" t="n">
-        <v>227</v>
+        <v>91</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.0978</v>
+        <v>3.2716</v>
       </c>
       <c r="C8" t="n">
-        <v>0.2727</v>
+        <v>0.288</v>
       </c>
       <c r="D8" t="n">
-        <v>0.7903</v>
+        <v>0.839</v>
       </c>
       <c r="E8" t="n">
-        <v>3.0978</v>
+        <v>3.2716</v>
       </c>
       <c r="F8" t="n">
-        <v>2.0508</v>
+        <v>2.5002</v>
       </c>
       <c r="G8" t="n">
-        <v>1.047</v>
+        <v>0.7714</v>
       </c>
       <c r="H8" t="n">
-        <v>2.0508</v>
+        <v>3.3228</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6622</v>
+        <v>1.7277</v>
       </c>
       <c r="J8" t="n">
-        <v>1.047</v>
+        <v>0.7714</v>
       </c>
       <c r="K8" t="n">
         <v>132</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="M8" t="n">
-        <v>2.7092</v>
+        <v>2.4991</v>
       </c>
       <c r="N8" t="n">
         <v>255</v>
@@ -818,28 +818,28 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0291</v>
+        <v>3.054</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2666</v>
+        <v>0.2688</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7629</v>
+        <v>0.7407</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0291</v>
+        <v>3.054</v>
       </c>
       <c r="F9" t="n">
-        <v>3.0291</v>
+        <v>3.054</v>
       </c>
       <c r="G9" t="n">
         <v>0</v>
       </c>
       <c r="H9" t="n">
-        <v>3.0291</v>
+        <v>3.3463</v>
       </c>
       <c r="I9" t="n">
-        <v>3.0546</v>
+        <v>3.4839</v>
       </c>
       <c r="J9" t="n">
         <v>0</v>
@@ -851,7 +851,7 @@
         <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>3.0546</v>
+        <v>3.4839</v>
       </c>
       <c r="N9" t="n">
         <v>153</v>
@@ -860,35 +860,35 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.5952</v>
+        <v>3.0374</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2284</v>
+        <v>0.2673</v>
       </c>
       <c r="D10" t="n">
-        <v>0.59</v>
+        <v>0.7332</v>
       </c>
       <c r="E10" t="n">
-        <v>2.5952</v>
+        <v>3.0374</v>
       </c>
       <c r="F10" t="n">
-        <v>1.8882</v>
+        <v>2.2707</v>
       </c>
       <c r="G10" t="n">
-        <v>0.707</v>
+        <v>0.7667</v>
       </c>
       <c r="H10" t="n">
-        <v>1.8882</v>
+        <v>2.5141</v>
       </c>
       <c r="I10" t="n">
-        <v>1.5304</v>
+        <v>1.3072</v>
       </c>
       <c r="J10" t="n">
-        <v>0.707</v>
+        <v>0.7667</v>
       </c>
       <c r="K10" t="n">
         <v>51</v>
@@ -897,7 +897,7 @@
         <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>2.2374</v>
+        <v>2.0739</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -906,35 +906,35 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.5265</v>
+        <v>2.8372</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2224</v>
+        <v>0.2497</v>
       </c>
       <c r="D11" t="n">
-        <v>0.5626</v>
+        <v>0.6428</v>
       </c>
       <c r="E11" t="n">
-        <v>2.5265</v>
+        <v>2.8372</v>
       </c>
       <c r="F11" t="n">
-        <v>1.5941</v>
+        <v>2.4059</v>
       </c>
       <c r="G11" t="n">
-        <v>0.9324</v>
+        <v>0.4313</v>
       </c>
       <c r="H11" t="n">
-        <v>1.5941</v>
+        <v>2.9905</v>
       </c>
       <c r="I11" t="n">
-        <v>1.2921</v>
+        <v>1.5549</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9324</v>
+        <v>0.4313</v>
       </c>
       <c r="K11" t="n">
         <v>51</v>
@@ -943,7 +943,7 @@
         <v>75</v>
       </c>
       <c r="M11" t="n">
-        <v>2.2245</v>
+        <v>1.9862</v>
       </c>
       <c r="N11" t="n">
         <v>126</v>
@@ -952,47 +952,47 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>1.967</v>
+        <v>2.2783</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1731</v>
+        <v>0.2005</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3397</v>
+        <v>0.3905</v>
       </c>
       <c r="E12" t="n">
-        <v>1.967</v>
+        <v>2.2783</v>
       </c>
       <c r="F12" t="n">
-        <v>1.967</v>
+        <v>2.1073</v>
       </c>
       <c r="G12" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="H12" t="n">
-        <v>1.967</v>
+        <v>2.1073</v>
       </c>
       <c r="I12" t="n">
-        <v>1.9836</v>
+        <v>1.0957</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>0.171</v>
       </c>
       <c r="K12" t="n">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M12" t="n">
-        <v>1.9836</v>
+        <v>1.2667</v>
       </c>
       <c r="N12" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
     </row>
     <row r="13">
@@ -1002,31 +1002,31 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>1.9089</v>
+        <v>2.2716</v>
       </c>
       <c r="C13" t="n">
-        <v>0.168</v>
+        <v>0.1999</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3166</v>
+        <v>0.3875</v>
       </c>
       <c r="E13" t="n">
-        <v>1.9089</v>
+        <v>2.2716</v>
       </c>
       <c r="F13" t="n">
-        <v>2.2446</v>
+        <v>2.5173</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.3357</v>
+        <v>-0.2457</v>
       </c>
       <c r="H13" t="n">
-        <v>2.2446</v>
+        <v>3.3832</v>
       </c>
       <c r="I13" t="n">
-        <v>1.8193</v>
+        <v>1.7591</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.3357</v>
+        <v>-0.2457</v>
       </c>
       <c r="K13" t="n">
         <v>42</v>
@@ -1035,7 +1035,7 @@
         <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>1.4836</v>
+        <v>1.5134</v>
       </c>
       <c r="N13" t="n">
         <v>91</v>
@@ -1044,32 +1044,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>1.7224</v>
+        <v>2.0997</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1516</v>
+        <v>0.1848</v>
       </c>
       <c r="D14" t="n">
-        <v>0.2423</v>
+        <v>0.3099</v>
       </c>
       <c r="E14" t="n">
-        <v>1.7224</v>
+        <v>2.0997</v>
       </c>
       <c r="F14" t="n">
-        <v>1.7224</v>
+        <v>2.0997</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>1.7224</v>
+        <v>2.0997</v>
       </c>
       <c r="I14" t="n">
-        <v>1.7369</v>
+        <v>2.1861</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>1.7369</v>
+        <v>2.1861</v>
       </c>
       <c r="N14" t="n">
         <v>156</v>
@@ -1090,495 +1090,495 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>1.4391</v>
+        <v>2.0253</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1267</v>
+        <v>0.1783</v>
       </c>
       <c r="D15" t="n">
-        <v>0.1294</v>
+        <v>0.2763</v>
       </c>
       <c r="E15" t="n">
-        <v>1.4391</v>
+        <v>2.0253</v>
       </c>
       <c r="F15" t="n">
-        <v>1.9406</v>
+        <v>2.0253</v>
       </c>
       <c r="G15" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>1.9406</v>
+        <v>2.0253</v>
       </c>
       <c r="I15" t="n">
-        <v>1.5729</v>
+        <v>2.1086</v>
       </c>
       <c r="J15" t="n">
-        <v>-0.5014999999999999</v>
+        <v>0</v>
       </c>
       <c r="K15" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="L15" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>1.0714</v>
+        <v>2.1086</v>
       </c>
       <c r="N15" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>1.3089</v>
+        <v>2.0185</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1152</v>
+        <v>0.1777</v>
       </c>
       <c r="D16" t="n">
-        <v>0.0776</v>
+        <v>0.2732</v>
       </c>
       <c r="E16" t="n">
-        <v>1.3089</v>
+        <v>2.0185</v>
       </c>
       <c r="F16" t="n">
-        <v>1.2674</v>
+        <v>2.3478</v>
       </c>
       <c r="G16" t="n">
-        <v>0.0415</v>
+        <v>-0.3293</v>
       </c>
       <c r="H16" t="n">
-        <v>1.2674</v>
+        <v>2.7859</v>
       </c>
       <c r="I16" t="n">
-        <v>1.0273</v>
+        <v>1.4485</v>
       </c>
       <c r="J16" t="n">
-        <v>0.0415</v>
+        <v>-0.3293</v>
       </c>
       <c r="K16" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L16" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.0688</v>
+        <v>1.1192</v>
       </c>
       <c r="N16" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>phr</t>
+          <t>friberg</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>0.8944</v>
+        <v>1.8398</v>
       </c>
       <c r="C17" t="n">
-        <v>0.07870000000000001</v>
+        <v>0.1619</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.0876</v>
+        <v>0.1926</v>
       </c>
       <c r="E17" t="n">
-        <v>0.8944</v>
+        <v>1.8398</v>
       </c>
       <c r="F17" t="n">
-        <v>0.8944</v>
+        <v>2.2732</v>
       </c>
       <c r="G17" t="n">
-        <v>0</v>
+        <v>-0.4334</v>
       </c>
       <c r="H17" t="n">
-        <v>0.8944</v>
+        <v>2.5231</v>
       </c>
       <c r="I17" t="n">
-        <v>0.9019</v>
+        <v>1.3119</v>
       </c>
       <c r="J17" t="n">
-        <v>0</v>
+        <v>-0.4334</v>
       </c>
       <c r="K17" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="L17" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>0.9019</v>
+        <v>0.8785000000000001</v>
       </c>
       <c r="N17" t="n">
-        <v>153</v>
+        <v>126</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>kennyS</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>0.8065</v>
+        <v>1.3157</v>
       </c>
       <c r="C18" t="n">
-        <v>0.07099999999999999</v>
+        <v>0.1158</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.1226</v>
+        <v>-0.044</v>
       </c>
       <c r="E18" t="n">
-        <v>0.8065</v>
+        <v>1.3157</v>
       </c>
       <c r="F18" t="n">
-        <v>0.8065</v>
+        <v>1.3157</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8065</v>
+        <v>1.3157</v>
       </c>
       <c r="I18" t="n">
-        <v>0.8133</v>
+        <v>1.3698</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
       </c>
       <c r="K18" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
       <c r="L18" t="n">
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>0.8133</v>
+        <v>1.3698</v>
       </c>
       <c r="N18" t="n">
-        <v>153</v>
+        <v>156</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>kennyS</t>
+          <t>phr</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>0.7496</v>
+        <v>1.2269</v>
       </c>
       <c r="C19" t="n">
-        <v>0.066</v>
+        <v>0.108</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.1453</v>
+        <v>-0.08409999999999999</v>
       </c>
       <c r="E19" t="n">
-        <v>0.7496</v>
+        <v>1.2269</v>
       </c>
       <c r="F19" t="n">
-        <v>0.7496</v>
+        <v>1.2269</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>0.7496</v>
+        <v>1.2269</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7559</v>
+        <v>1.2774</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
       </c>
       <c r="K19" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="L19" t="n">
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>0.7559</v>
+        <v>1.2774</v>
       </c>
       <c r="N19" t="n">
-        <v>156</v>
+        <v>153</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>friberg</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>0.7005</v>
+        <v>1.1181</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0617</v>
+        <v>0.0984</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1648</v>
+        <v>-0.1332</v>
       </c>
       <c r="E20" t="n">
-        <v>0.7005</v>
+        <v>1.1181</v>
       </c>
       <c r="F20" t="n">
-        <v>1.5353</v>
+        <v>1.1181</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8348</v>
+        <v>0</v>
       </c>
       <c r="H20" t="n">
-        <v>1.5353</v>
+        <v>1.1181</v>
       </c>
       <c r="I20" t="n">
-        <v>1.2444</v>
+        <v>1.1641</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.8348</v>
+        <v>0</v>
       </c>
       <c r="K20" t="n">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="L20" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M20" t="n">
-        <v>0.4096</v>
+        <v>1.1641</v>
       </c>
       <c r="N20" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>0.6954</v>
+        <v>1.0714</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0612</v>
+        <v>0.09429999999999999</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1669</v>
+        <v>-0.1543</v>
       </c>
       <c r="E21" t="n">
-        <v>0.6954</v>
+        <v>1.0714</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.0344</v>
+        <v>1.0714</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7298</v>
+        <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>-0.0344</v>
+        <v>1.0714</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.0279</v>
+        <v>1.1155</v>
       </c>
       <c r="J21" t="n">
-        <v>0.7298</v>
+        <v>0</v>
       </c>
       <c r="K21" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L21" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>0.7019</v>
+        <v>1.1155</v>
       </c>
       <c r="N21" t="n">
-        <v>255</v>
+        <v>153</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>0.6451</v>
+        <v>1.0491</v>
       </c>
       <c r="C22" t="n">
-        <v>0.0568</v>
+        <v>0.09229999999999999</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1869</v>
+        <v>-0.1644</v>
       </c>
       <c r="E22" t="n">
-        <v>0.6451</v>
+        <v>1.0491</v>
       </c>
       <c r="F22" t="n">
-        <v>0.6451</v>
+        <v>0.371</v>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>0.6781</v>
       </c>
       <c r="H22" t="n">
-        <v>0.6451</v>
+        <v>0.371</v>
       </c>
       <c r="I22" t="n">
-        <v>0.6505</v>
+        <v>0.1929</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>0.6781</v>
       </c>
       <c r="K22" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M22" t="n">
-        <v>0.6505</v>
+        <v>0.871</v>
       </c>
       <c r="N22" t="n">
-        <v>153</v>
+        <v>255</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>steel</t>
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.3823</v>
+        <v>0.6891</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0336</v>
+        <v>0.0607</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.2916</v>
+        <v>-0.3269</v>
       </c>
       <c r="E23" t="n">
-        <v>0.3823</v>
+        <v>0.6891</v>
       </c>
       <c r="F23" t="n">
-        <v>0.3823</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="G23" t="n">
-        <v>0</v>
+        <v>0.1241</v>
       </c>
       <c r="H23" t="n">
-        <v>0.3823</v>
+        <v>0.5649999999999999</v>
       </c>
       <c r="I23" t="n">
-        <v>0.3823</v>
+        <v>0.2938</v>
       </c>
       <c r="J23" t="n">
-        <v>0</v>
+        <v>0.1241</v>
       </c>
       <c r="K23" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="L23" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M23" t="n">
-        <v>0.3823</v>
+        <v>0.4179</v>
       </c>
       <c r="N23" t="n">
-        <v>66</v>
+        <v>255</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>KILLDREAM</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.0449</v>
+        <v>0.4878</v>
       </c>
       <c r="C24" t="n">
-        <v>0.004</v>
+        <v>0.0429</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.426</v>
+        <v>-0.4178</v>
       </c>
       <c r="E24" t="n">
-        <v>0.0449</v>
+        <v>0.4878</v>
       </c>
       <c r="F24" t="n">
-        <v>0.0449</v>
+        <v>0.4878</v>
       </c>
       <c r="G24" t="n">
         <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.0449</v>
+        <v>0.4878</v>
       </c>
       <c r="I24" t="n">
-        <v>0.0449</v>
+        <v>0.4878</v>
       </c>
       <c r="J24" t="n">
         <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L24" t="n">
         <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.0449</v>
+        <v>0.4878</v>
       </c>
       <c r="N24" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>steel</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>-0.1547</v>
+        <v>0.4655</v>
       </c>
       <c r="C25" t="n">
-        <v>-0.0136</v>
+        <v>0.041</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.5054999999999999</v>
+        <v>-0.4279</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.1547</v>
+        <v>0.4655</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.0459</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1088</v>
+        <v>-0.1872</v>
       </c>
       <c r="H25" t="n">
-        <v>-0.0459</v>
+        <v>0.6526999999999999</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.0372</v>
+        <v>0.3394</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1088</v>
+        <v>-0.1872</v>
       </c>
       <c r="K25" t="n">
         <v>132</v>
@@ -1587,7 +1587,7 @@
         <v>123</v>
       </c>
       <c r="M25" t="n">
-        <v>-0.146</v>
+        <v>0.1522</v>
       </c>
       <c r="N25" t="n">
         <v>255</v>
@@ -1596,78 +1596,78 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>torben</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>-0.1955</v>
+        <v>0.4273</v>
       </c>
       <c r="C26" t="n">
-        <v>-0.0172</v>
+        <v>0.0376</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.5218</v>
+        <v>-0.4451</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.1955</v>
+        <v>0.4273</v>
       </c>
       <c r="F26" t="n">
-        <v>0.2121</v>
+        <v>1.2295</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.4076</v>
+        <v>-0.8022</v>
       </c>
       <c r="H26" t="n">
-        <v>0.2121</v>
+        <v>1.2295</v>
       </c>
       <c r="I26" t="n">
-        <v>0.1719</v>
+        <v>0.6393</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.4076</v>
+        <v>-0.8022</v>
       </c>
       <c r="K26" t="n">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="L26" t="n">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2357</v>
+        <v>-0.1629</v>
       </c>
       <c r="N26" t="n">
-        <v>255</v>
+        <v>91</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>obj</t>
+          <t>KILLDREAM</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>-0.3557</v>
+        <v>0.2777</v>
       </c>
       <c r="C27" t="n">
-        <v>-0.0313</v>
+        <v>0.0244</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5856</v>
+        <v>-0.5125999999999999</v>
       </c>
       <c r="E27" t="n">
-        <v>-0.3557</v>
+        <v>0.2777</v>
       </c>
       <c r="F27" t="n">
-        <v>-0.3557</v>
+        <v>0.2777</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>-0.3557</v>
+        <v>0.2777</v>
       </c>
       <c r="I27" t="n">
-        <v>-0.3557</v>
+        <v>0.2777</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>-0.3557</v>
+        <v>0.2777</v>
       </c>
       <c r="N27" t="n">
         <v>72</v>
@@ -1688,185 +1688,185 @@
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>-0.4474</v>
+        <v>0.255</v>
       </c>
       <c r="C28" t="n">
-        <v>-0.0394</v>
+        <v>0.0224</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.6222</v>
+        <v>-0.5229</v>
       </c>
       <c r="E28" t="n">
-        <v>-0.4474</v>
+        <v>0.255</v>
       </c>
       <c r="F28" t="n">
-        <v>-0.0253</v>
+        <v>0.4818</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.4221</v>
+        <v>-0.2268</v>
       </c>
       <c r="H28" t="n">
-        <v>-0.0253</v>
+        <v>0.4818</v>
       </c>
       <c r="I28" t="n">
-        <v>-0.0205</v>
+        <v>0.2505</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.4221</v>
+        <v>-0.2268</v>
       </c>
       <c r="K28" t="n">
-        <v>42</v>
+        <v>132</v>
       </c>
       <c r="L28" t="n">
-        <v>49</v>
+        <v>123</v>
       </c>
       <c r="M28" t="n">
-        <v>-0.4426</v>
+        <v>0.0237</v>
       </c>
       <c r="N28" t="n">
-        <v>91</v>
+        <v>255</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>torben</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>-0.4681</v>
+        <v>0.0556</v>
       </c>
       <c r="C29" t="n">
-        <v>-0.0412</v>
+        <v>0.0049</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6304</v>
+        <v>-0.6129</v>
       </c>
       <c r="E29" t="n">
-        <v>-0.4681</v>
+        <v>0.0556</v>
       </c>
       <c r="F29" t="n">
-        <v>0.5319</v>
+        <v>0.6479</v>
       </c>
       <c r="G29" t="n">
-        <v>-1</v>
+        <v>-0.5923</v>
       </c>
       <c r="H29" t="n">
-        <v>0.5319</v>
+        <v>0.6479</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4311</v>
+        <v>0.3369</v>
       </c>
       <c r="J29" t="n">
-        <v>-1</v>
+        <v>-0.5923</v>
       </c>
       <c r="K29" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L29" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.5689</v>
+        <v>-0.2554000000000001</v>
       </c>
       <c r="N29" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>-0.6266</v>
+        <v>0.0245</v>
       </c>
       <c r="C30" t="n">
-        <v>-0.0552</v>
+        <v>0.0022</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6935</v>
+        <v>-0.627</v>
       </c>
       <c r="E30" t="n">
-        <v>-0.6266</v>
+        <v>0.0245</v>
       </c>
       <c r="F30" t="n">
-        <v>-0.22</v>
+        <v>0.3241</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.4066</v>
+        <v>-0.2996</v>
       </c>
       <c r="H30" t="n">
-        <v>-0.22</v>
+        <v>0.3241</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1783</v>
+        <v>0.1685</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.4066</v>
+        <v>-0.2996</v>
       </c>
       <c r="K30" t="n">
-        <v>132</v>
+        <v>42</v>
       </c>
       <c r="L30" t="n">
-        <v>123</v>
+        <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.5849</v>
+        <v>-0.1311</v>
       </c>
       <c r="N30" t="n">
-        <v>255</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>obj</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.737</v>
+        <v>-0.2523</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0649</v>
+        <v>-0.0222</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7375</v>
+        <v>-0.7519</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.737</v>
+        <v>-0.2523</v>
       </c>
       <c r="F31" t="n">
-        <v>0.2303</v>
+        <v>-0.2523</v>
       </c>
       <c r="G31" t="n">
-        <v>-0.9673</v>
+        <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>0.2303</v>
+        <v>-0.2523</v>
       </c>
       <c r="I31" t="n">
-        <v>0.1867</v>
+        <v>-0.2523</v>
       </c>
       <c r="J31" t="n">
-        <v>-0.9673</v>
+        <v>0</v>
       </c>
       <c r="K31" t="n">
-        <v>51</v>
+        <v>72</v>
       </c>
       <c r="L31" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.7806000000000001</v>
+        <v>-0.2523</v>
       </c>
       <c r="N31" t="n">
-        <v>126</v>
+        <v>72</v>
       </c>
     </row>
     <row r="32">
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.8013</v>
+        <v>-0.3257</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.07049999999999999</v>
+        <v>-0.0287</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7631</v>
+        <v>-0.7851</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.8013</v>
+        <v>-0.3257</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.8013</v>
+        <v>-0.3257</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.8013</v>
+        <v>-0.3257</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.8013</v>
+        <v>-0.3257</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.8013</v>
+        <v>-0.3257</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-1.0216</v>
+        <v>-0.3839</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.08989999999999999</v>
+        <v>-0.0338</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8509</v>
+        <v>-0.8113</v>
       </c>
       <c r="E33" t="n">
-        <v>-1.0216</v>
+        <v>-0.3839</v>
       </c>
       <c r="F33" t="n">
-        <v>-1.0216</v>
+        <v>-0.3839</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-1.0216</v>
+        <v>-0.3839</v>
       </c>
       <c r="I33" t="n">
-        <v>-1.0302</v>
+        <v>-0.3997</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-1.0302</v>
+        <v>-0.3997</v>
       </c>
       <c r="N33" t="n">
         <v>153</v>
@@ -1964,124 +1964,124 @@
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-1.1003</v>
+        <v>-0.7134</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0968</v>
+        <v>-0.06279999999999999</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.8823</v>
+        <v>-0.9601</v>
       </c>
       <c r="E34" t="n">
-        <v>-1.1003</v>
+        <v>-0.7134</v>
       </c>
       <c r="F34" t="n">
-        <v>-1.1003</v>
+        <v>-0.7134</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-1.1003</v>
+        <v>-0.7134</v>
       </c>
       <c r="I34" t="n">
-        <v>-1.1003</v>
+        <v>-0.7134</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-1.1003</v>
+        <v>-0.7134</v>
       </c>
       <c r="N34" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-1.148</v>
+        <v>-0.7855</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.101</v>
+        <v>-0.06909999999999999</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9013</v>
+        <v>-0.9926</v>
       </c>
       <c r="E35" t="n">
-        <v>-1.148</v>
+        <v>-0.7855</v>
       </c>
       <c r="F35" t="n">
-        <v>-1.148</v>
+        <v>-0.7855</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-1.148</v>
+        <v>-0.7855</v>
       </c>
       <c r="I35" t="n">
-        <v>-1.148</v>
+        <v>-0.7855</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-1.148</v>
+        <v>-0.7855</v>
       </c>
       <c r="N35" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-1.3089</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.1152</v>
+        <v>-0.0722</v>
       </c>
       <c r="D36" t="n">
-        <v>-0.9654</v>
+        <v>-1.0082</v>
       </c>
       <c r="E36" t="n">
-        <v>-1.3089</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="F36" t="n">
-        <v>-1.3089</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-1.3089</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="I36" t="n">
-        <v>-1.3089</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
@@ -2093,7 +2093,7 @@
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-1.3089</v>
+        <v>-0.8201000000000001</v>
       </c>
       <c r="N36" t="n">
         <v>66</v>
@@ -2106,28 +2106,28 @@
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-1.3621</v>
+        <v>-0.8326</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.1199</v>
+        <v>-0.0733</v>
       </c>
       <c r="D37" t="n">
-        <v>-0.9866</v>
+        <v>-1.0139</v>
       </c>
       <c r="E37" t="n">
-        <v>-1.3621</v>
+        <v>-0.8326</v>
       </c>
       <c r="F37" t="n">
-        <v>-1.3621</v>
+        <v>-0.8326</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-1.3621</v>
+        <v>-0.8326</v>
       </c>
       <c r="I37" t="n">
-        <v>-1.3621</v>
+        <v>-0.8326</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-1.3621</v>
+        <v>-0.8326</v>
       </c>
       <c r="N37" t="n">
         <v>72</v>
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.3953</v>
+        <v>-0.9813</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.1228</v>
+        <v>-0.0864</v>
       </c>
       <c r="D38" t="n">
-        <v>-0.9998</v>
+        <v>-1.081</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.3953</v>
+        <v>-0.9813</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.3953</v>
+        <v>-0.9813</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.3953</v>
+        <v>-0.9813</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.3953</v>
+        <v>-0.9813</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.3953</v>
+        <v>-0.9813</v>
       </c>
       <c r="N38" t="n">
         <v>66</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.6601</v>
+        <v>-1.2055</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1461</v>
+        <v>-0.1061</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1053</v>
+        <v>-1.1822</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.6601</v>
+        <v>-1.2055</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.6601</v>
+        <v>-1.2055</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.6601</v>
+        <v>-1.2055</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.6741</v>
+        <v>-1.2551</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.6741</v>
+        <v>-1.2551</v>
       </c>
       <c r="N39" t="n">
         <v>156</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.8002</v>
+        <v>-1.4165</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1585</v>
+        <v>-0.1247</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.1611</v>
+        <v>-1.2775</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.8002</v>
+        <v>-1.4165</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.8002</v>
+        <v>-1.4165</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.8002</v>
+        <v>-1.4165</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.8002</v>
+        <v>-1.4165</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.8002</v>
+        <v>-1.4165</v>
       </c>
       <c r="N40" t="n">
         <v>66</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.703</v>
+        <v>-2.5903</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2379</v>
+        <v>-0.228</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.5208</v>
+        <v>-1.8074</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.703</v>
+        <v>-2.5903</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.595</v>
+        <v>-2.7712</v>
       </c>
       <c r="G41" t="n">
-        <v>-0.108</v>
+        <v>0.1809</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.595</v>
+        <v>-2.7712</v>
       </c>
       <c r="I41" t="n">
-        <v>-2.1033</v>
+        <v>-1.4409</v>
       </c>
       <c r="J41" t="n">
-        <v>-0.108</v>
+        <v>0.1809</v>
       </c>
       <c r="K41" t="n">
         <v>130</v>
@@ -2323,7 +2323,7 @@
         <v>97</v>
       </c>
       <c r="M41" t="n">
-        <v>-2.2113</v>
+        <v>-1.26</v>
       </c>
       <c r="N41" t="n">
         <v>227</v>
@@ -2429,10 +2429,10 @@
         <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>2.0093</v>
+        <v>1.7105</v>
       </c>
       <c r="J2" t="n">
-        <v>46.2139</v>
+        <v>39.3415</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4762</v>
+        <v>1.327</v>
       </c>
       <c r="J3" t="n">
-        <v>33.9526</v>
+        <v>30.521</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.5051</v>
+        <v>0.623</v>
       </c>
       <c r="J4" t="n">
-        <v>11.6173</v>
+        <v>14.329</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.4366</v>
+        <v>0.5511</v>
       </c>
       <c r="J5" t="n">
-        <v>10.0418</v>
+        <v>12.6753</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.22</v>
       </c>
       <c r="I6" t="n">
-        <v>0.4366</v>
+        <v>0.5511</v>
       </c>
       <c r="J6" t="n">
-        <v>10.0418</v>
+        <v>12.6753</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.97</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0891</v>
+        <v>0.0534</v>
       </c>
       <c r="J7" t="n">
-        <v>2.0493</v>
+        <v>1.2282</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.07729999999999999</v>
+        <v>-0.09180000000000001</v>
       </c>
       <c r="J8" t="n">
-        <v>-1.7779</v>
+        <v>-2.1114</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.6929999999999999</v>
+        <v>-0.4721</v>
       </c>
       <c r="J9" t="n">
-        <v>-15.939</v>
+        <v>-10.8583</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.42</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.5476</v>
       </c>
       <c r="J10" t="n">
-        <v>-18.3747</v>
+        <v>-12.5948</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.42</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.7989000000000001</v>
+        <v>-0.5476</v>
       </c>
       <c r="J11" t="n">
-        <v>-18.3747</v>
+        <v>-12.5948</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.76</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7099</v>
+        <v>1.4648</v>
       </c>
       <c r="J12" t="n">
-        <v>42.7475</v>
+        <v>36.62</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6924</v>
+        <v>0.6999</v>
       </c>
       <c r="J13" t="n">
-        <v>17.31</v>
+        <v>17.4975</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.2914</v>
+        <v>0.3569</v>
       </c>
       <c r="J14" t="n">
-        <v>7.285</v>
+        <v>8.922499999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.297</v>
+        <v>-0.218</v>
       </c>
       <c r="J15" t="n">
-        <v>-7.425</v>
+        <v>-5.45</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.4209</v>
+        <v>-0.3454</v>
       </c>
       <c r="J16" t="n">
-        <v>-10.5225</v>
+        <v>-8.635</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1629</v>
+        <v>0.1554</v>
       </c>
       <c r="J17" t="n">
-        <v>4.0725</v>
+        <v>3.885</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>0.0029</v>
+        <v>-0.0147</v>
       </c>
       <c r="J18" t="n">
-        <v>0.0725</v>
+        <v>-0.3675</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.97</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0469</v>
+        <v>-0.0448</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.1725</v>
+        <v>-1.12</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.89</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.2208</v>
+        <v>-0.138</v>
       </c>
       <c r="J20" t="n">
-        <v>-5.52</v>
+        <v>-3.45</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.77</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.4103</v>
+        <v>-0.2608</v>
       </c>
       <c r="J21" t="n">
-        <v>-10.2575</v>
+        <v>-6.52</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3025</v>
+        <v>0.3214</v>
       </c>
       <c r="J22" t="n">
-        <v>10.5875</v>
+        <v>11.249</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1606</v>
+        <v>0.145</v>
       </c>
       <c r="J23" t="n">
-        <v>5.621</v>
+        <v>5.075</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.85</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.2709</v>
+        <v>-0.1752</v>
       </c>
       <c r="J24" t="n">
-        <v>-9.4815</v>
+        <v>-6.132</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.74</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.4411</v>
+        <v>-0.2845</v>
       </c>
       <c r="J25" t="n">
-        <v>-15.4385</v>
+        <v>-9.9575</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.4968</v>
+        <v>-0.3229</v>
       </c>
       <c r="J26" t="n">
-        <v>-17.388</v>
+        <v>-11.3015</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.9802999999999999</v>
+        <v>0.7105</v>
       </c>
       <c r="J27" t="n">
-        <v>34.3105</v>
+        <v>24.8675</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.8695000000000001</v>
+        <v>0.6425</v>
       </c>
       <c r="J28" t="n">
-        <v>30.4325</v>
+        <v>22.4875</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4336</v>
+        <v>0.4003</v>
       </c>
       <c r="J29" t="n">
-        <v>15.176</v>
+        <v>14.0105</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.1598</v>
+        <v>-0.0892</v>
       </c>
       <c r="J30" t="n">
-        <v>-5.593</v>
+        <v>-3.122</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4861</v>
+        <v>-0.4179</v>
       </c>
       <c r="J31" t="n">
-        <v>-17.0135</v>
+        <v>-14.6265</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.19</v>
       </c>
       <c r="I32" t="n">
-        <v>1.3277</v>
+        <v>0.8757</v>
       </c>
       <c r="J32" t="n">
-        <v>25.2263</v>
+        <v>16.6383</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.52</v>
       </c>
       <c r="I33" t="n">
-        <v>0.6479</v>
+        <v>0.4936</v>
       </c>
       <c r="J33" t="n">
-        <v>12.3101</v>
+        <v>9.378399999999999</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.33</v>
       </c>
       <c r="I34" t="n">
-        <v>0.3952</v>
+        <v>0.377</v>
       </c>
       <c r="J34" t="n">
-        <v>7.5088</v>
+        <v>7.163</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3058</v>
+        <v>0.3245</v>
       </c>
       <c r="J35" t="n">
-        <v>5.8102</v>
+        <v>6.1655</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0184</v>
+        <v>0.0618</v>
       </c>
       <c r="J36" t="n">
-        <v>0.3496</v>
+        <v>1.1742</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.91</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0205</v>
+        <v>-0.0503</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.3895</v>
+        <v>-0.9557</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.4402</v>
+        <v>-0.3335</v>
       </c>
       <c r="J38" t="n">
-        <v>-8.363799999999999</v>
+        <v>-6.3365</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.61</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.523</v>
+        <v>-0.3684</v>
       </c>
       <c r="J39" t="n">
-        <v>-9.936999999999999</v>
+        <v>-6.9996</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.6032999999999999</v>
+        <v>-0.4141</v>
       </c>
       <c r="J40" t="n">
-        <v>-11.4627</v>
+        <v>-7.8679</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.41</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.8091</v>
+        <v>-0.5554</v>
       </c>
       <c r="J41" t="n">
-        <v>-15.3729</v>
+        <v>-10.5526</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.93</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.018</v>
+        <v>-0.0483</v>
       </c>
       <c r="J42" t="n">
-        <v>-0.378</v>
+        <v>-1.0143</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.73</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.3498</v>
+        <v>-0.2692</v>
       </c>
       <c r="J43" t="n">
-        <v>-7.3458</v>
+        <v>-5.6532</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.64</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.5143</v>
+        <v>-0.351</v>
       </c>
       <c r="J44" t="n">
-        <v>-10.8003</v>
+        <v>-7.371</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.62</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.5446</v>
+        <v>-0.3696</v>
       </c>
       <c r="J45" t="n">
-        <v>-11.4366</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.55</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.6438</v>
+        <v>-0.435</v>
       </c>
       <c r="J46" t="n">
-        <v>-13.5198</v>
+        <v>-9.135</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.96</v>
       </c>
       <c r="I47" t="n">
-        <v>1.854</v>
+        <v>1.3656</v>
       </c>
       <c r="J47" t="n">
-        <v>38.934</v>
+        <v>28.6776</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.736</v>
+        <v>0.6336000000000001</v>
       </c>
       <c r="J48" t="n">
-        <v>15.456</v>
+        <v>13.3056</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.32</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6903</v>
+        <v>0.6076</v>
       </c>
       <c r="J49" t="n">
-        <v>14.4963</v>
+        <v>12.7596</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.599</v>
+        <v>0.5544</v>
       </c>
       <c r="J50" t="n">
-        <v>12.579</v>
+        <v>11.6424</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3151</v>
+        <v>0.3825</v>
       </c>
       <c r="J51" t="n">
-        <v>6.6171</v>
+        <v>8.032500000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.353</v>
+        <v>0.3644</v>
       </c>
       <c r="J52" t="n">
-        <v>8.119</v>
+        <v>8.3812</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.9</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1054</v>
+        <v>-0.1045</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.4242</v>
+        <v>-2.4035</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.76</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.3557</v>
+        <v>-0.2496</v>
       </c>
       <c r="J54" t="n">
-        <v>-8.181100000000001</v>
+        <v>-5.7408</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.63</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.5575</v>
+        <v>-0.3716</v>
       </c>
       <c r="J55" t="n">
-        <v>-12.8225</v>
+        <v>-8.546799999999999</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.42</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.8253</v>
+        <v>-0.5665</v>
       </c>
       <c r="J56" t="n">
-        <v>-18.9819</v>
+        <v>-13.0295</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.02</v>
       </c>
       <c r="I57" t="n">
-        <v>1.9064</v>
+        <v>1.4307</v>
       </c>
       <c r="J57" t="n">
-        <v>43.8472</v>
+        <v>32.9061</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.86</v>
       </c>
       <c r="I58" t="n">
-        <v>1.757</v>
+        <v>1.2493</v>
       </c>
       <c r="J58" t="n">
-        <v>40.411</v>
+        <v>28.7339</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.26</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5493</v>
+        <v>0.5258</v>
       </c>
       <c r="J59" t="n">
-        <v>12.6339</v>
+        <v>12.0934</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.0733</v>
+        <v>0.164</v>
       </c>
       <c r="J60" t="n">
-        <v>1.6859</v>
+        <v>3.772</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.5286999999999999</v>
+        <v>-0.4526</v>
       </c>
       <c r="J61" t="n">
-        <v>-12.1601</v>
+        <v>-10.4098</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4077</v>
+        <v>0.4122</v>
       </c>
       <c r="J62" t="n">
-        <v>10.6002</v>
+        <v>10.7172</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.056</v>
+        <v>0.0423</v>
       </c>
       <c r="J63" t="n">
-        <v>1.456</v>
+        <v>1.0998</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.02</v>
+        <v>0.0039</v>
       </c>
       <c r="J64" t="n">
-        <v>0.52</v>
+        <v>0.1014</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.3167</v>
+        <v>-0.1951</v>
       </c>
       <c r="J65" t="n">
-        <v>-8.2342</v>
+        <v>-5.0726</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.3768</v>
+        <v>-0.2357</v>
       </c>
       <c r="J66" t="n">
-        <v>-9.796799999999999</v>
+        <v>-6.1282</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.9187</v>
+        <v>0.6716</v>
       </c>
       <c r="J67" t="n">
-        <v>23.8862</v>
+        <v>17.4616</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5834</v>
+        <v>0.4747</v>
       </c>
       <c r="J68" t="n">
-        <v>15.1684</v>
+        <v>12.3422</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4726</v>
+        <v>0.4159</v>
       </c>
       <c r="J69" t="n">
-        <v>12.2876</v>
+        <v>10.8134</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.12</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3365</v>
+        <v>0.3559</v>
       </c>
       <c r="J70" t="n">
-        <v>8.749000000000001</v>
+        <v>9.253399999999999</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.5635</v>
+        <v>-0.4996</v>
       </c>
       <c r="J71" t="n">
-        <v>-14.651</v>
+        <v>-12.9896</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.31</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8889</v>
+        <v>0.8645</v>
       </c>
       <c r="J72" t="n">
-        <v>26.667</v>
+        <v>25.935</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.12</v>
       </c>
       <c r="I73" t="n">
-        <v>0.4082</v>
+        <v>0.384</v>
       </c>
       <c r="J73" t="n">
-        <v>12.246</v>
+        <v>11.52</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2421</v>
+        <v>0.2436</v>
       </c>
       <c r="J74" t="n">
-        <v>7.263</v>
+        <v>7.308</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0435</v>
+        <v>0.0805</v>
       </c>
       <c r="J75" t="n">
-        <v>1.305</v>
+        <v>2.415</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.82</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.6429</v>
+        <v>-0.5886</v>
       </c>
       <c r="J76" t="n">
-        <v>-19.287</v>
+        <v>-17.658</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.4</v>
       </c>
       <c r="I77" t="n">
-        <v>0.6156</v>
+        <v>0.7513</v>
       </c>
       <c r="J77" t="n">
-        <v>18.468</v>
+        <v>22.539</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.3654</v>
+        <v>0.4309</v>
       </c>
       <c r="J78" t="n">
-        <v>10.962</v>
+        <v>12.927</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2403</v>
+        <v>0.2856</v>
       </c>
       <c r="J79" t="n">
-        <v>7.209</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.1654</v>
+        <v>-0.0857</v>
       </c>
       <c r="J80" t="n">
-        <v>-4.962</v>
+        <v>-2.571</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.78</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.4303</v>
+        <v>-0.2692</v>
       </c>
       <c r="J81" t="n">
-        <v>-12.909</v>
+        <v>-8.076000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.15</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3681</v>
+        <v>0.3106</v>
       </c>
       <c r="J82" t="n">
-        <v>8.8344</v>
+        <v>7.4544</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.12</v>
       </c>
       <c r="I83" t="n">
-        <v>0.3213</v>
+        <v>0.2632</v>
       </c>
       <c r="J83" t="n">
-        <v>7.7112</v>
+        <v>6.3168</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.98</v>
       </c>
       <c r="I84" t="n">
-        <v>0.0174</v>
+        <v>-0.0163</v>
       </c>
       <c r="J84" t="n">
-        <v>0.4176</v>
+        <v>-0.3912</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.5</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.7421</v>
+        <v>-0.5028</v>
       </c>
       <c r="J85" t="n">
-        <v>-17.8104</v>
+        <v>-12.0672</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.46</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.7897999999999999</v>
+        <v>-0.5392</v>
       </c>
       <c r="J86" t="n">
-        <v>-18.9552</v>
+        <v>-12.9408</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.54</v>
       </c>
       <c r="I87" t="n">
-        <v>0.7435</v>
+        <v>0.6637</v>
       </c>
       <c r="J87" t="n">
-        <v>17.844</v>
+        <v>15.9288</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.27</v>
       </c>
       <c r="I88" t="n">
-        <v>0.4077</v>
+        <v>0.3623</v>
       </c>
       <c r="J88" t="n">
-        <v>9.784800000000001</v>
+        <v>8.6952</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.18</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2591</v>
+        <v>0.2562</v>
       </c>
       <c r="J89" t="n">
-        <v>6.2184</v>
+        <v>6.1488</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.11</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1478</v>
+        <v>0.1643</v>
       </c>
       <c r="J90" t="n">
-        <v>3.5472</v>
+        <v>3.9432</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.1317</v>
+        <v>-0.0572</v>
       </c>
       <c r="J91" t="n">
-        <v>-3.1608</v>
+        <v>-1.3728</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.42</v>
       </c>
       <c r="I92" t="n">
-        <v>1.1068</v>
+        <v>1.0611</v>
       </c>
       <c r="J92" t="n">
-        <v>29.8836</v>
+        <v>28.6497</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5503</v>
+        <v>0.5309</v>
       </c>
       <c r="J93" t="n">
-        <v>14.8581</v>
+        <v>14.3343</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4082</v>
+        <v>0.4018</v>
       </c>
       <c r="J94" t="n">
-        <v>11.0214</v>
+        <v>10.8486</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3867</v>
+        <v>-0.3198</v>
       </c>
       <c r="J95" t="n">
-        <v>-10.4409</v>
+        <v>-8.634600000000001</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.5001</v>
+        <v>-0.436</v>
       </c>
       <c r="J96" t="n">
-        <v>-13.5027</v>
+        <v>-11.772</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.5279</v>
+        <v>0.6284</v>
       </c>
       <c r="J97" t="n">
-        <v>14.2533</v>
+        <v>16.9668</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2386</v>
+        <v>0.2627</v>
       </c>
       <c r="J98" t="n">
-        <v>6.4422</v>
+        <v>7.0929</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0574</v>
+        <v>0.0639</v>
       </c>
       <c r="J99" t="n">
-        <v>1.5498</v>
+        <v>1.7253</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.3434</v>
+        <v>-0.2105</v>
       </c>
       <c r="J100" t="n">
-        <v>-9.271800000000001</v>
+        <v>-5.6835</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.3728</v>
+        <v>-0.2308</v>
       </c>
       <c r="J101" t="n">
-        <v>-10.0656</v>
+        <v>-6.2316</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.38</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9987</v>
+        <v>0.9846</v>
       </c>
       <c r="J102" t="n">
-        <v>29.961</v>
+        <v>29.538</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.37</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9771</v>
+        <v>0.9656</v>
       </c>
       <c r="J103" t="n">
-        <v>29.313</v>
+        <v>28.968</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5738</v>
+        <v>0.5694</v>
       </c>
       <c r="J104" t="n">
-        <v>17.214</v>
+        <v>17.082</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.09</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2337</v>
+        <v>0.2856</v>
       </c>
       <c r="J105" t="n">
-        <v>7.011</v>
+        <v>8.568</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.923</v>
+        <v>-0.8888</v>
       </c>
       <c r="J106" t="n">
-        <v>-27.69</v>
+        <v>-26.664</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.33</v>
       </c>
       <c r="I107" t="n">
-        <v>0.5483</v>
+        <v>0.6568000000000001</v>
       </c>
       <c r="J107" t="n">
-        <v>16.449</v>
+        <v>19.704</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.25</v>
       </c>
       <c r="I108" t="n">
-        <v>0.4428</v>
+        <v>0.5184</v>
       </c>
       <c r="J108" t="n">
-        <v>13.284</v>
+        <v>15.552</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.185</v>
+        <v>-0.1034</v>
       </c>
       <c r="J109" t="n">
-        <v>-5.55</v>
+        <v>-3.102</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.2702</v>
+        <v>-0.1597</v>
       </c>
       <c r="J110" t="n">
-        <v>-8.106</v>
+        <v>-4.791</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.4327</v>
+        <v>-0.2724</v>
       </c>
       <c r="J111" t="n">
-        <v>-12.981</v>
+        <v>-8.172000000000001</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.21</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4889</v>
+        <v>0.4392</v>
       </c>
       <c r="J112" t="n">
-        <v>10.7558</v>
+        <v>9.6624</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.83</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2234</v>
+        <v>-0.1812</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.9148</v>
+        <v>-3.9864</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.3732</v>
+        <v>-0.2586</v>
       </c>
       <c r="J114" t="n">
-        <v>-8.2104</v>
+        <v>-5.6892</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.6767</v>
+        <v>-0.4554</v>
       </c>
       <c r="J115" t="n">
-        <v>-14.8874</v>
+        <v>-10.0188</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.49</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.7398</v>
+        <v>-0.5017</v>
       </c>
       <c r="J116" t="n">
-        <v>-16.2756</v>
+        <v>-11.0374</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>1.0552</v>
+        <v>0.9684</v>
       </c>
       <c r="J117" t="n">
-        <v>23.2144</v>
+        <v>21.3048</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.5245</v>
+        <v>0.4749</v>
       </c>
       <c r="J118" t="n">
-        <v>11.539</v>
+        <v>10.4478</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.25</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3308</v>
+        <v>0.3314</v>
       </c>
       <c r="J119" t="n">
-        <v>7.2776</v>
+        <v>7.2908</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.1</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1099</v>
+        <v>0.1392</v>
       </c>
       <c r="J120" t="n">
-        <v>2.4178</v>
+        <v>3.0624</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.96</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.1886</v>
+        <v>-0.09370000000000001</v>
       </c>
       <c r="J121" t="n">
-        <v>-4.1492</v>
+        <v>-2.0614</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.2363</v>
+        <v>1.1513</v>
       </c>
       <c r="J122" t="n">
-        <v>34.6164</v>
+        <v>32.2364</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.39</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9878</v>
+        <v>0.9847</v>
       </c>
       <c r="J123" t="n">
-        <v>27.6584</v>
+        <v>27.5716</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.24</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6349</v>
+        <v>0.6516</v>
       </c>
       <c r="J124" t="n">
-        <v>17.7772</v>
+        <v>18.2448</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.186</v>
+        <v>-0.1066</v>
       </c>
       <c r="J125" t="n">
-        <v>-5.208</v>
+        <v>-2.9848</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.394</v>
+        <v>-0.3169</v>
       </c>
       <c r="J126" t="n">
-        <v>-11.032</v>
+        <v>-8.873200000000001</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.42</v>
       </c>
       <c r="I127" t="n">
-        <v>0.701</v>
+        <v>0.8667</v>
       </c>
       <c r="J127" t="n">
-        <v>19.628</v>
+        <v>24.2676</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.82</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.3289</v>
+        <v>-0.2083</v>
       </c>
       <c r="J128" t="n">
-        <v>-9.209199999999999</v>
+        <v>-5.8324</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.3597</v>
+        <v>-0.2284</v>
       </c>
       <c r="J129" t="n">
-        <v>-10.0716</v>
+        <v>-6.3952</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.4187</v>
+        <v>-0.2678</v>
       </c>
       <c r="J130" t="n">
-        <v>-11.7236</v>
+        <v>-7.4984</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.4187</v>
+        <v>-0.2678</v>
       </c>
       <c r="J131" t="n">
-        <v>-11.7236</v>
+        <v>-7.4984</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7687</v>
+        <v>0.7401</v>
       </c>
       <c r="J132" t="n">
-        <v>21.5236</v>
+        <v>20.7228</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6468</v>
+        <v>0.6162</v>
       </c>
       <c r="J133" t="n">
-        <v>18.1104</v>
+        <v>17.2536</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.08</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2706</v>
+        <v>0.271</v>
       </c>
       <c r="J134" t="n">
-        <v>7.5768</v>
+        <v>7.588</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.1893</v>
+        <v>0.2129</v>
       </c>
       <c r="J135" t="n">
-        <v>5.3004</v>
+        <v>5.9612</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.767</v>
+        <v>-0.7203000000000001</v>
       </c>
       <c r="J136" t="n">
-        <v>-21.476</v>
+        <v>-20.1684</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.28</v>
       </c>
       <c r="I137" t="n">
-        <v>0.4953</v>
+        <v>0.5837</v>
       </c>
       <c r="J137" t="n">
-        <v>13.8684</v>
+        <v>16.3436</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.23</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4275</v>
+        <v>0.4947</v>
       </c>
       <c r="J138" t="n">
-        <v>11.97</v>
+        <v>13.8516</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.1337</v>
+        <v>-0.0755</v>
       </c>
       <c r="J139" t="n">
-        <v>-3.7436</v>
+        <v>-2.114</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.3681</v>
+        <v>-0.2285</v>
       </c>
       <c r="J140" t="n">
-        <v>-10.3068</v>
+        <v>-6.398</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.5064</v>
+        <v>-0.3263</v>
       </c>
       <c r="J141" t="n">
-        <v>-14.1792</v>
+        <v>-9.1364</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.12</v>
       </c>
       <c r="I142" t="n">
-        <v>2.0593</v>
+        <v>1.7983</v>
       </c>
       <c r="J142" t="n">
-        <v>43.2453</v>
+        <v>37.7643</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>2</v>
       </c>
       <c r="I143" t="n">
-        <v>1.9647</v>
+        <v>1.6658</v>
       </c>
       <c r="J143" t="n">
-        <v>41.2587</v>
+        <v>34.9818</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.32</v>
       </c>
       <c r="I144" t="n">
-        <v>0.6599</v>
+        <v>0.7836</v>
       </c>
       <c r="J144" t="n">
-        <v>13.8579</v>
+        <v>16.4556</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.3182</v>
+        <v>0.4262</v>
       </c>
       <c r="J145" t="n">
-        <v>6.6822</v>
+        <v>8.950200000000001</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.83</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.7145</v>
+        <v>-0.6556</v>
       </c>
       <c r="J146" t="n">
-        <v>-15.0045</v>
+        <v>-13.7676</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.95</v>
       </c>
       <c r="I147" t="n">
-        <v>0.0317</v>
+        <v>-0.0131</v>
       </c>
       <c r="J147" t="n">
-        <v>0.6657</v>
+        <v>-0.2751</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.1027</v>
       </c>
       <c r="J148" t="n">
-        <v>-1.9677</v>
+        <v>-2.1567</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1597</v>
+        <v>-0.149</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.3537</v>
+        <v>-3.129</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.34</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.9048</v>
+        <v>-0.6281</v>
       </c>
       <c r="J150" t="n">
-        <v>-19.0008</v>
+        <v>-13.1901</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.34</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.9048</v>
+        <v>-0.6281</v>
       </c>
       <c r="J151" t="n">
-        <v>-19.0008</v>
+        <v>-13.1901</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.87</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.09470000000000001</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.4616</v>
+        <v>-1.7046</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2563</v>
+        <v>-0.2201</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.6134</v>
+        <v>-3.9618</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.58</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.5642</v>
+        <v>-0.3933</v>
       </c>
       <c r="J154" t="n">
-        <v>-10.1556</v>
+        <v>-7.0794</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.54</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.6264</v>
+        <v>-0.4302</v>
       </c>
       <c r="J155" t="n">
-        <v>-11.2752</v>
+        <v>-7.7436</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.32</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.9189000000000001</v>
+        <v>-0.639</v>
       </c>
       <c r="J156" t="n">
-        <v>-16.5402</v>
+        <v>-11.502</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.9</v>
       </c>
       <c r="I157" t="n">
-        <v>1.8135</v>
+        <v>1.5458</v>
       </c>
       <c r="J157" t="n">
-        <v>32.643</v>
+        <v>27.8244</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.5</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0307</v>
+        <v>1.0921</v>
       </c>
       <c r="J158" t="n">
-        <v>18.5526</v>
+        <v>19.6578</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>0.9866</v>
+        <v>1.0685</v>
       </c>
       <c r="J159" t="n">
-        <v>17.7588</v>
+        <v>19.233</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.44</v>
       </c>
       <c r="I160" t="n">
-        <v>0.901</v>
+        <v>1.0158</v>
       </c>
       <c r="J160" t="n">
-        <v>16.218</v>
+        <v>18.2844</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.33</v>
       </c>
       <c r="I161" t="n">
-        <v>0.6673</v>
+        <v>0.7978</v>
       </c>
       <c r="J161" t="n">
-        <v>12.0114</v>
+        <v>14.3604</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5006</v>
+        <v>0.601</v>
       </c>
       <c r="J162" t="n">
-        <v>15.018</v>
+        <v>18.03</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4062</v>
+        <v>0.4818</v>
       </c>
       <c r="J163" t="n">
-        <v>12.186</v>
+        <v>14.454</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2198</v>
+        <v>0.2659</v>
       </c>
       <c r="J164" t="n">
-        <v>6.594</v>
+        <v>7.977</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.0574</v>
+        <v>0.1016</v>
       </c>
       <c r="J165" t="n">
-        <v>1.722</v>
+        <v>3.048</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.4177</v>
+        <v>-0.26</v>
       </c>
       <c r="J166" t="n">
-        <v>-12.531</v>
+        <v>-7.8</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I167" t="n">
-        <v>0.6315</v>
+        <v>0.5796</v>
       </c>
       <c r="J167" t="n">
-        <v>18.945</v>
+        <v>17.388</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.11</v>
       </c>
       <c r="I168" t="n">
-        <v>0.4418</v>
+        <v>0.3867</v>
       </c>
       <c r="J168" t="n">
-        <v>13.254</v>
+        <v>11.601</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.1361</v>
+        <v>-0.125</v>
       </c>
       <c r="J169" t="n">
-        <v>-4.083</v>
+        <v>-3.75</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5531</v>
+        <v>-0.5081</v>
       </c>
       <c r="J170" t="n">
-        <v>-16.593</v>
+        <v>-15.243</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.7075</v>
+        <v>-0.6655</v>
       </c>
       <c r="J171" t="n">
-        <v>-21.225</v>
+        <v>-19.965</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.5895</v>
+        <v>0.709</v>
       </c>
       <c r="J172" t="n">
-        <v>14.7375</v>
+        <v>17.725</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2307</v>
+        <v>0.2399</v>
       </c>
       <c r="J173" t="n">
-        <v>5.7675</v>
+        <v>5.9975</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.92</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1713</v>
+        <v>-0.1063</v>
       </c>
       <c r="J174" t="n">
-        <v>-4.2825</v>
+        <v>-2.6575</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.76</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.4281</v>
+        <v>-0.2724</v>
       </c>
       <c r="J175" t="n">
-        <v>-10.7025</v>
+        <v>-6.81</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.6005</v>
+        <v>-0.3959</v>
       </c>
       <c r="J176" t="n">
-        <v>-15.0125</v>
+        <v>-9.897500000000001</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.5</v>
       </c>
       <c r="I177" t="n">
-        <v>1.2818</v>
+        <v>1.1747</v>
       </c>
       <c r="J177" t="n">
-        <v>32.045</v>
+        <v>29.3675</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5646</v>
+        <v>0.5374</v>
       </c>
       <c r="J178" t="n">
-        <v>14.115</v>
+        <v>13.435</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.3158</v>
+        <v>-0.252</v>
       </c>
       <c r="J179" t="n">
-        <v>-7.895</v>
+        <v>-6.3</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.92</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3776</v>
+        <v>-0.3137</v>
       </c>
       <c r="J180" t="n">
-        <v>-9.44</v>
+        <v>-7.8425</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4919</v>
+        <v>-0.4299</v>
       </c>
       <c r="J181" t="n">
-        <v>-12.2975</v>
+        <v>-10.7475</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2591</v>
+        <v>0.2708</v>
       </c>
       <c r="J182" t="n">
-        <v>6.7366</v>
+        <v>7.0408</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I183" t="n">
-        <v>0.0101</v>
+        <v>-0.0126</v>
       </c>
       <c r="J183" t="n">
-        <v>0.2626</v>
+        <v>-0.3276</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.98</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0156</v>
+        <v>-0.0285</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.4056</v>
+        <v>-0.741</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.1037</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.6962</v>
+        <v>-2.1112</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.58</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.6575</v>
+        <v>-0.4386</v>
       </c>
       <c r="J186" t="n">
-        <v>-17.095</v>
+        <v>-11.4036</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1696</v>
+        <v>1.1067</v>
       </c>
       <c r="J187" t="n">
-        <v>30.4096</v>
+        <v>28.7742</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.3</v>
       </c>
       <c r="I188" t="n">
-        <v>0.8012</v>
+        <v>0.7981</v>
       </c>
       <c r="J188" t="n">
-        <v>20.8312</v>
+        <v>20.7506</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4176</v>
+        <v>0.4657</v>
       </c>
       <c r="J189" t="n">
-        <v>10.8576</v>
+        <v>12.1082</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.03</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0214</v>
+        <v>0.0885</v>
       </c>
       <c r="J190" t="n">
-        <v>0.5564</v>
+        <v>2.301</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2901</v>
+        <v>-0.213</v>
       </c>
       <c r="J191" t="n">
-        <v>-7.5426</v>
+        <v>-5.538</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.87</v>
       </c>
       <c r="I192" t="n">
-        <v>0.0467</v>
+        <v>0.0531</v>
       </c>
       <c r="J192" t="n">
-        <v>0.7939000000000001</v>
+        <v>0.9026999999999999</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.36</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.8002</v>
+        <v>-0.5599</v>
       </c>
       <c r="J193" t="n">
-        <v>-13.6034</v>
+        <v>-9.5183</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.34</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.8316</v>
+        <v>-0.58</v>
       </c>
       <c r="J194" t="n">
-        <v>-14.1372</v>
+        <v>-9.859999999999999</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.28</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.9206</v>
+        <v>-0.6419</v>
       </c>
       <c r="J195" t="n">
-        <v>-15.6502</v>
+        <v>-10.9123</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.9206</v>
+        <v>-0.6419</v>
       </c>
       <c r="J196" t="n">
-        <v>-15.6502</v>
+        <v>-10.9123</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.19</v>
       </c>
       <c r="I197" t="n">
-        <v>2.0593</v>
+        <v>1.8338</v>
       </c>
       <c r="J197" t="n">
-        <v>35.0081</v>
+        <v>31.1746</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.62</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2547</v>
+        <v>1.2217</v>
       </c>
       <c r="J198" t="n">
-        <v>21.3299</v>
+        <v>20.7689</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.59</v>
       </c>
       <c r="I199" t="n">
-        <v>1.1784</v>
+        <v>1.1887</v>
       </c>
       <c r="J199" t="n">
-        <v>20.0328</v>
+        <v>20.2079</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.8087</v>
+        <v>0.953</v>
       </c>
       <c r="J200" t="n">
-        <v>13.7479</v>
+        <v>16.201</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.25</v>
       </c>
       <c r="I201" t="n">
-        <v>0.4714</v>
+        <v>0.5984</v>
       </c>
       <c r="J201" t="n">
-        <v>8.0138</v>
+        <v>10.1728</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0059</v>
+        <v>1.0072</v>
       </c>
       <c r="J202" t="n">
-        <v>25.1475</v>
+        <v>25.18</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.33</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8268</v>
+        <v>0.8462</v>
       </c>
       <c r="J203" t="n">
-        <v>20.67</v>
+        <v>21.155</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.29</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7292</v>
+        <v>0.7568</v>
       </c>
       <c r="J204" t="n">
-        <v>18.23</v>
+        <v>18.92</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.2</v>
       </c>
       <c r="I205" t="n">
-        <v>0.4768</v>
+        <v>0.5499000000000001</v>
       </c>
       <c r="J205" t="n">
-        <v>11.92</v>
+        <v>13.7475</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.07</v>
       </c>
       <c r="I206" t="n">
-        <v>0.1225</v>
+        <v>0.2005</v>
       </c>
       <c r="J206" t="n">
-        <v>3.0625</v>
+        <v>5.0125</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.96</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0239</v>
+        <v>-0.0439</v>
       </c>
       <c r="J207" t="n">
-        <v>-0.5975</v>
+        <v>-1.0975</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.85</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.2298</v>
+        <v>-0.1705</v>
       </c>
       <c r="J208" t="n">
-        <v>-5.745</v>
+        <v>-4.2625</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.2501</v>
+        <v>-0.1803</v>
       </c>
       <c r="J209" t="n">
-        <v>-6.2525</v>
+        <v>-4.5075</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.3462</v>
+        <v>-0.2288</v>
       </c>
       <c r="J210" t="n">
-        <v>-8.654999999999999</v>
+        <v>-5.72</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.4238</v>
+        <v>-0.2773</v>
       </c>
       <c r="J211" t="n">
-        <v>-10.595</v>
+        <v>-6.9325</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.8104</v>
       </c>
       <c r="J212" t="n">
-        <v>17.1288</v>
+        <v>21.0704</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.22</v>
       </c>
       <c r="I213" t="n">
-        <v>0.3743</v>
+        <v>0.4448</v>
       </c>
       <c r="J213" t="n">
-        <v>9.7318</v>
+        <v>11.5648</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.05</v>
       </c>
       <c r="I214" t="n">
-        <v>0.0741</v>
+        <v>0.1231</v>
       </c>
       <c r="J214" t="n">
-        <v>1.9266</v>
+        <v>3.2006</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0488</v>
+        <v>-0.0098</v>
       </c>
       <c r="J215" t="n">
-        <v>-1.2688</v>
+        <v>-0.2548</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.3486</v>
+        <v>-0.2105</v>
       </c>
       <c r="J216" t="n">
-        <v>-9.063599999999999</v>
+        <v>-5.473</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.37</v>
       </c>
       <c r="I217" t="n">
-        <v>1.0158</v>
+        <v>0.9913</v>
       </c>
       <c r="J217" t="n">
-        <v>26.4108</v>
+        <v>25.7738</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5945</v>
+        <v>0.5649</v>
       </c>
       <c r="J218" t="n">
-        <v>15.457</v>
+        <v>14.6874</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0677</v>
+        <v>-0.0173</v>
       </c>
       <c r="J219" t="n">
-        <v>-1.7602</v>
+        <v>-0.4498</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.95</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2803</v>
+        <v>-0.2182</v>
       </c>
       <c r="J220" t="n">
-        <v>-7.2878</v>
+        <v>-5.6732</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.88</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4896</v>
+        <v>-0.4282</v>
       </c>
       <c r="J221" t="n">
-        <v>-12.7296</v>
+        <v>-11.1332</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.71</v>
       </c>
       <c r="I222" t="n">
-        <v>1.5201</v>
+        <v>1.3491</v>
       </c>
       <c r="J222" t="n">
-        <v>36.4824</v>
+        <v>32.3784</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.52</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1524</v>
+        <v>1.1248</v>
       </c>
       <c r="J223" t="n">
-        <v>27.6576</v>
+        <v>26.9952</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.33</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7066</v>
+        <v>0.8179</v>
       </c>
       <c r="J224" t="n">
-        <v>16.9584</v>
+        <v>19.6296</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.31</v>
       </c>
       <c r="I225" t="n">
-        <v>0.6615</v>
+        <v>0.7734</v>
       </c>
       <c r="J225" t="n">
-        <v>15.876</v>
+        <v>18.5616</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.26</v>
       </c>
       <c r="I226" t="n">
-        <v>0.5479000000000001</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="J226" t="n">
-        <v>13.1496</v>
+        <v>15.8112</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>0.2029</v>
+        <v>0.1892</v>
       </c>
       <c r="J227" t="n">
-        <v>4.8696</v>
+        <v>4.5408</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.74</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.3319</v>
+        <v>-0.2592</v>
       </c>
       <c r="J228" t="n">
-        <v>-7.9656</v>
+        <v>-6.2208</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.71</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.383</v>
+        <v>-0.2877</v>
       </c>
       <c r="J229" t="n">
-        <v>-9.192</v>
+        <v>-6.9048</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.4263</v>
+        <v>-0.3054</v>
       </c>
       <c r="J230" t="n">
-        <v>-10.2312</v>
+        <v>-7.3296</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.3</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.9555</v>
+        <v>-0.6683</v>
       </c>
       <c r="J231" t="n">
-        <v>-22.932</v>
+        <v>-16.0392</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3428/event_3428_evp_summary.xlsx
+++ b/database/event/3428/event_3428_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.3866</v>
+        <v>8.705299999999999</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7382</v>
+        <v>0.7662</v>
       </c>
       <c r="D2" t="n">
-        <v>3.1481</v>
+        <v>3.3386</v>
       </c>
       <c r="E2" t="n">
-        <v>8.3866</v>
+        <v>8.705299999999999</v>
       </c>
       <c r="F2" t="n">
-        <v>3.1316</v>
+        <v>3.0033</v>
       </c>
       <c r="G2" t="n">
-        <v>5.255</v>
+        <v>5.702</v>
       </c>
       <c r="H2" t="n">
-        <v>5.5474</v>
+        <v>5.0147</v>
       </c>
       <c r="I2" t="n">
-        <v>2.8844</v>
+        <v>2.7079</v>
       </c>
       <c r="J2" t="n">
-        <v>5.255</v>
+        <v>5.702</v>
       </c>
       <c r="K2" t="n">
         <v>130</v>
@@ -529,7 +529,7 @@
         <v>97</v>
       </c>
       <c r="M2" t="n">
-        <v>8.1394</v>
+        <v>8.4099</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.4397</v>
+        <v>5.5471</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4788</v>
+        <v>0.4883</v>
       </c>
       <c r="D3" t="n">
-        <v>1.8177</v>
+        <v>1.901</v>
       </c>
       <c r="E3" t="n">
-        <v>5.4397</v>
+        <v>5.5471</v>
       </c>
       <c r="F3" t="n">
-        <v>3.3302</v>
+        <v>3.218</v>
       </c>
       <c r="G3" t="n">
-        <v>2.1095</v>
+        <v>2.3291</v>
       </c>
       <c r="H3" t="n">
-        <v>6.2473</v>
+        <v>5.7231</v>
       </c>
       <c r="I3" t="n">
-        <v>3.2483</v>
+        <v>3.0904</v>
       </c>
       <c r="J3" t="n">
-        <v>2.1095</v>
+        <v>2.3291</v>
       </c>
       <c r="K3" t="n">
         <v>130</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>5.3578</v>
+        <v>5.419499999999999</v>
       </c>
       <c r="N3" t="n">
         <v>227</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2636</v>
+        <v>4.2939</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3753</v>
+        <v>0.3779</v>
       </c>
       <c r="D4" t="n">
-        <v>1.2868</v>
+        <v>1.3305</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2636</v>
+        <v>4.2939</v>
       </c>
       <c r="F4" t="n">
-        <v>2.2629</v>
+        <v>2.1744</v>
       </c>
       <c r="G4" t="n">
-        <v>2.0007</v>
+        <v>2.1195</v>
       </c>
       <c r="H4" t="n">
-        <v>2.4866</v>
+        <v>2.2798</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2929</v>
+        <v>1.2311</v>
       </c>
       <c r="J4" t="n">
-        <v>2.0007</v>
+        <v>2.1195</v>
       </c>
       <c r="K4" t="n">
         <v>130</v>
@@ -621,7 +621,7 @@
         <v>97</v>
       </c>
       <c r="M4" t="n">
-        <v>3.2936</v>
+        <v>3.3506</v>
       </c>
       <c r="N4" t="n">
         <v>227</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0123</v>
+        <v>4.0107</v>
       </c>
       <c r="C5" t="n">
-        <v>0.3532</v>
+        <v>0.353</v>
       </c>
       <c r="D5" t="n">
-        <v>1.1733</v>
+        <v>1.2015</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0123</v>
+        <v>4.0107</v>
       </c>
       <c r="F5" t="n">
-        <v>2.5244</v>
+        <v>2.4516</v>
       </c>
       <c r="G5" t="n">
-        <v>1.4879</v>
+        <v>1.5591</v>
       </c>
       <c r="H5" t="n">
-        <v>3.408</v>
+        <v>3.1947</v>
       </c>
       <c r="I5" t="n">
-        <v>1.772</v>
+        <v>1.7251</v>
       </c>
       <c r="J5" t="n">
-        <v>1.4879</v>
+        <v>1.5591</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2599</v>
+        <v>3.2842</v>
       </c>
       <c r="N5" t="n">
         <v>227</v>
@@ -676,93 +676,93 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>stavn</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.6746</v>
+        <v>3.5906</v>
       </c>
       <c r="C6" t="n">
-        <v>0.3234</v>
+        <v>0.316</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0209</v>
+        <v>1.0103</v>
       </c>
       <c r="E6" t="n">
-        <v>3.6746</v>
+        <v>3.5906</v>
       </c>
       <c r="F6" t="n">
-        <v>3.6746</v>
+        <v>2.7751</v>
       </c>
       <c r="G6" t="n">
-        <v>0</v>
+        <v>0.8155</v>
       </c>
       <c r="H6" t="n">
-        <v>4.709</v>
+        <v>4.2619</v>
       </c>
       <c r="I6" t="n">
-        <v>4.9027</v>
+        <v>2.3014</v>
       </c>
       <c r="J6" t="n">
-        <v>0</v>
+        <v>0.8155</v>
       </c>
       <c r="K6" t="n">
-        <v>156</v>
+        <v>42</v>
       </c>
       <c r="L6" t="n">
-        <v>0</v>
+        <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>4.9027</v>
+        <v>3.1169</v>
       </c>
       <c r="N6" t="n">
-        <v>156</v>
+        <v>91</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>stavn</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.6238</v>
+        <v>3.4003</v>
       </c>
       <c r="C7" t="n">
-        <v>0.319</v>
+        <v>0.2993</v>
       </c>
       <c r="D7" t="n">
-        <v>0.998</v>
+        <v>0.9237</v>
       </c>
       <c r="E7" t="n">
-        <v>3.6238</v>
+        <v>3.4003</v>
       </c>
       <c r="F7" t="n">
-        <v>2.8472</v>
+        <v>3.4003</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7766</v>
+        <v>0</v>
       </c>
       <c r="H7" t="n">
-        <v>4.5454</v>
+        <v>4.7173</v>
       </c>
       <c r="I7" t="n">
-        <v>2.3634</v>
+        <v>4.8389</v>
       </c>
       <c r="J7" t="n">
-        <v>0.7766</v>
+        <v>0</v>
       </c>
       <c r="K7" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="L7" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M7" t="n">
-        <v>3.14</v>
+        <v>4.8389</v>
       </c>
       <c r="N7" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
     </row>
     <row r="8">
@@ -772,31 +772,31 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2716</v>
+        <v>3.2603</v>
       </c>
       <c r="C8" t="n">
-        <v>0.288</v>
+        <v>0.287</v>
       </c>
       <c r="D8" t="n">
-        <v>0.839</v>
+        <v>0.86</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2716</v>
+        <v>3.2603</v>
       </c>
       <c r="F8" t="n">
-        <v>2.5002</v>
+        <v>2.4125</v>
       </c>
       <c r="G8" t="n">
-        <v>0.7714</v>
+        <v>0.8478</v>
       </c>
       <c r="H8" t="n">
-        <v>3.3228</v>
+        <v>3.0656</v>
       </c>
       <c r="I8" t="n">
-        <v>1.7277</v>
+        <v>1.6554</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7714</v>
+        <v>0.8478</v>
       </c>
       <c r="K8" t="n">
         <v>132</v>
@@ -805,7 +805,7 @@
         <v>123</v>
       </c>
       <c r="M8" t="n">
-        <v>2.4991</v>
+        <v>2.5032</v>
       </c>
       <c r="N8" t="n">
         <v>255</v>
@@ -814,81 +814,81 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>snatchie</t>
+          <t>es3tag</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.054</v>
+        <v>3.0191</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2688</v>
+        <v>0.2657</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7407</v>
+        <v>0.7502</v>
       </c>
       <c r="E9" t="n">
-        <v>3.054</v>
+        <v>3.0191</v>
       </c>
       <c r="F9" t="n">
-        <v>3.054</v>
+        <v>2.2043</v>
       </c>
       <c r="G9" t="n">
-        <v>0</v>
+        <v>0.8148</v>
       </c>
       <c r="H9" t="n">
-        <v>3.3463</v>
+        <v>2.3786</v>
       </c>
       <c r="I9" t="n">
-        <v>3.4839</v>
+        <v>1.2844</v>
       </c>
       <c r="J9" t="n">
-        <v>0</v>
+        <v>0.8148</v>
       </c>
       <c r="K9" t="n">
-        <v>153</v>
+        <v>51</v>
       </c>
       <c r="L9" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>3.4839</v>
+        <v>2.0992</v>
       </c>
       <c r="N9" t="n">
-        <v>153</v>
+        <v>126</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>es3tag</t>
+          <t>niko</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.0374</v>
+        <v>2.8409</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2673</v>
+        <v>0.2501</v>
       </c>
       <c r="D10" t="n">
-        <v>0.7332</v>
+        <v>0.669</v>
       </c>
       <c r="E10" t="n">
-        <v>3.0374</v>
+        <v>2.8409</v>
       </c>
       <c r="F10" t="n">
-        <v>2.2707</v>
+        <v>2.3137</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7667</v>
+        <v>0.5272</v>
       </c>
       <c r="H10" t="n">
-        <v>2.5141</v>
+        <v>2.7397</v>
       </c>
       <c r="I10" t="n">
-        <v>1.3072</v>
+        <v>1.4794</v>
       </c>
       <c r="J10" t="n">
-        <v>0.7667</v>
+        <v>0.5272</v>
       </c>
       <c r="K10" t="n">
         <v>51</v>
@@ -897,7 +897,7 @@
         <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0739</v>
+        <v>2.0066</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -906,139 +906,139 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>niko</t>
+          <t>snatchie</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.8372</v>
+        <v>2.7476</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2497</v>
+        <v>0.2418</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6428</v>
+        <v>0.6266</v>
       </c>
       <c r="E11" t="n">
-        <v>2.8372</v>
+        <v>2.7476</v>
       </c>
       <c r="F11" t="n">
-        <v>2.4059</v>
+        <v>2.7476</v>
       </c>
       <c r="G11" t="n">
-        <v>0.4313</v>
+        <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>2.9905</v>
+        <v>3.2888</v>
       </c>
       <c r="I11" t="n">
-        <v>1.5549</v>
+        <v>3.3735</v>
       </c>
       <c r="J11" t="n">
-        <v>0.4313</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>51</v>
+        <v>153</v>
       </c>
       <c r="L11" t="n">
-        <v>75</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>1.9862</v>
+        <v>3.3735</v>
       </c>
       <c r="N11" t="n">
-        <v>126</v>
+        <v>153</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>dragonfly</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.2783</v>
+        <v>2.184</v>
       </c>
       <c r="C12" t="n">
-        <v>0.2005</v>
+        <v>0.1922</v>
       </c>
       <c r="D12" t="n">
-        <v>0.3905</v>
+        <v>0.37</v>
       </c>
       <c r="E12" t="n">
-        <v>2.2783</v>
+        <v>2.184</v>
       </c>
       <c r="F12" t="n">
-        <v>2.1073</v>
+        <v>2.4502</v>
       </c>
       <c r="G12" t="n">
-        <v>0.171</v>
+        <v>-0.2662</v>
       </c>
       <c r="H12" t="n">
-        <v>2.1073</v>
+        <v>3.1899</v>
       </c>
       <c r="I12" t="n">
-        <v>1.0957</v>
+        <v>1.7225</v>
       </c>
       <c r="J12" t="n">
-        <v>0.171</v>
+        <v>-0.2662</v>
       </c>
       <c r="K12" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L12" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="M12" t="n">
-        <v>1.2667</v>
+        <v>1.4563</v>
       </c>
       <c r="N12" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>dragonfly</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.2716</v>
+        <v>2.1655</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1999</v>
+        <v>0.1906</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3875</v>
+        <v>0.3616</v>
       </c>
       <c r="E13" t="n">
-        <v>2.2716</v>
+        <v>2.1655</v>
       </c>
       <c r="F13" t="n">
-        <v>2.5173</v>
+        <v>1.9648</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.2457</v>
+        <v>0.2007</v>
       </c>
       <c r="H13" t="n">
-        <v>3.3832</v>
+        <v>1.9648</v>
       </c>
       <c r="I13" t="n">
-        <v>1.7591</v>
+        <v>1.061</v>
       </c>
       <c r="J13" t="n">
-        <v>-0.2457</v>
+        <v>0.2007</v>
       </c>
       <c r="K13" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L13" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="M13" t="n">
-        <v>1.5134</v>
+        <v>1.2617</v>
       </c>
       <c r="N13" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
     </row>
     <row r="14">
@@ -1048,28 +1048,28 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0997</v>
+        <v>2.0894</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1848</v>
+        <v>0.1839</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3099</v>
+        <v>0.3269</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0997</v>
+        <v>2.0894</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0997</v>
+        <v>2.0894</v>
       </c>
       <c r="G14" t="n">
         <v>0</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0997</v>
+        <v>2.0894</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1861</v>
+        <v>2.1432</v>
       </c>
       <c r="J14" t="n">
         <v>0</v>
@@ -1081,7 +1081,7 @@
         <v>0</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1861</v>
+        <v>2.1432</v>
       </c>
       <c r="N14" t="n">
         <v>156</v>
@@ -1094,28 +1094,28 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0253</v>
+        <v>2.0676</v>
       </c>
       <c r="C15" t="n">
-        <v>0.1783</v>
+        <v>0.182</v>
       </c>
       <c r="D15" t="n">
-        <v>0.2763</v>
+        <v>0.317</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0253</v>
+        <v>2.0676</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0253</v>
+        <v>2.0676</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0253</v>
+        <v>2.0676</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1086</v>
+        <v>2.1209</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1086</v>
+        <v>2.1209</v>
       </c>
       <c r="N15" t="n">
         <v>156</v>
@@ -1140,31 +1140,31 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0185</v>
+        <v>2.0494</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1777</v>
+        <v>0.1804</v>
       </c>
       <c r="D16" t="n">
-        <v>0.2732</v>
+        <v>0.3087</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0185</v>
+        <v>2.0494</v>
       </c>
       <c r="F16" t="n">
-        <v>2.3478</v>
+        <v>2.39</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3293</v>
+        <v>-0.3406</v>
       </c>
       <c r="H16" t="n">
-        <v>2.7859</v>
+        <v>2.9912</v>
       </c>
       <c r="I16" t="n">
-        <v>1.4485</v>
+        <v>1.6152</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3293</v>
+        <v>-0.3406</v>
       </c>
       <c r="K16" t="n">
         <v>42</v>
@@ -1173,7 +1173,7 @@
         <v>49</v>
       </c>
       <c r="M16" t="n">
-        <v>1.1192</v>
+        <v>1.2746</v>
       </c>
       <c r="N16" t="n">
         <v>91</v>
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.8398</v>
+        <v>1.7534</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1619</v>
+        <v>0.1543</v>
       </c>
       <c r="D17" t="n">
-        <v>0.1926</v>
+        <v>0.174</v>
       </c>
       <c r="E17" t="n">
-        <v>1.8398</v>
+        <v>1.7534</v>
       </c>
       <c r="F17" t="n">
-        <v>2.2732</v>
+        <v>2.1911</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4334</v>
+        <v>-0.4377</v>
       </c>
       <c r="H17" t="n">
-        <v>2.5231</v>
+        <v>2.3352</v>
       </c>
       <c r="I17" t="n">
-        <v>1.3119</v>
+        <v>1.261</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4334</v>
+        <v>-0.4377</v>
       </c>
       <c r="K17" t="n">
         <v>51</v>
@@ -1219,7 +1219,7 @@
         <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8785000000000001</v>
+        <v>0.8232999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>126</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3157</v>
+        <v>1.3205</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1158</v>
+        <v>0.1162</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.044</v>
+        <v>-0.0231</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3157</v>
+        <v>1.3205</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3157</v>
+        <v>1.3205</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3157</v>
+        <v>1.3205</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3698</v>
+        <v>1.3545</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3698</v>
+        <v>1.3545</v>
       </c>
       <c r="N18" t="n">
         <v>156</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.2269</v>
+        <v>1.1946</v>
       </c>
       <c r="C19" t="n">
-        <v>0.108</v>
+        <v>0.1051</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.08409999999999999</v>
+        <v>-0.0804</v>
       </c>
       <c r="E19" t="n">
-        <v>1.2269</v>
+        <v>1.1946</v>
       </c>
       <c r="F19" t="n">
-        <v>1.2269</v>
+        <v>1.1946</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.2269</v>
+        <v>1.1946</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2774</v>
+        <v>1.2254</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2774</v>
+        <v>1.2254</v>
       </c>
       <c r="N19" t="n">
         <v>153</v>
@@ -1320,78 +1320,78 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>HEN1</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.1181</v>
+        <v>1.0882</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0984</v>
+        <v>0.0958</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1332</v>
+        <v>-0.1288</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1181</v>
+        <v>1.0882</v>
       </c>
       <c r="F20" t="n">
-        <v>1.1181</v>
+        <v>0.3333</v>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>0.7549</v>
       </c>
       <c r="H20" t="n">
-        <v>1.1181</v>
+        <v>0.3333</v>
       </c>
       <c r="I20" t="n">
-        <v>1.1641</v>
+        <v>0.18</v>
       </c>
       <c r="J20" t="n">
-        <v>0</v>
+        <v>0.7549</v>
       </c>
       <c r="K20" t="n">
-        <v>153</v>
+        <v>132</v>
       </c>
       <c r="L20" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M20" t="n">
-        <v>1.1641</v>
+        <v>0.9349000000000001</v>
       </c>
       <c r="N20" t="n">
-        <v>153</v>
+        <v>255</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0714</v>
+        <v>1.0537</v>
       </c>
       <c r="C21" t="n">
-        <v>0.09429999999999999</v>
+        <v>0.0927</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1543</v>
+        <v>-0.1445</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0714</v>
+        <v>1.0537</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0714</v>
+        <v>1.0537</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0714</v>
+        <v>1.0537</v>
       </c>
       <c r="I21" t="n">
-        <v>1.1155</v>
+        <v>1.0809</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.1155</v>
+        <v>1.0809</v>
       </c>
       <c r="N21" t="n">
         <v>153</v>
@@ -1412,47 +1412,47 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>HEN1</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0491</v>
+        <v>1.0262</v>
       </c>
       <c r="C22" t="n">
-        <v>0.09229999999999999</v>
+        <v>0.09030000000000001</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1644</v>
+        <v>-0.1571</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0491</v>
+        <v>1.0262</v>
       </c>
       <c r="F22" t="n">
-        <v>0.371</v>
+        <v>1.0262</v>
       </c>
       <c r="G22" t="n">
-        <v>0.6781</v>
+        <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>0.371</v>
+        <v>1.0262</v>
       </c>
       <c r="I22" t="n">
-        <v>0.1929</v>
+        <v>1.0526</v>
       </c>
       <c r="J22" t="n">
-        <v>0.6781</v>
+        <v>0</v>
       </c>
       <c r="K22" t="n">
-        <v>132</v>
+        <v>153</v>
       </c>
       <c r="L22" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>0.871</v>
+        <v>1.0526</v>
       </c>
       <c r="N22" t="n">
-        <v>255</v>
+        <v>153</v>
       </c>
     </row>
     <row r="23">
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6891</v>
+        <v>0.6145</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0607</v>
+        <v>0.0541</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3269</v>
+        <v>-0.3445</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6891</v>
+        <v>0.6145</v>
       </c>
       <c r="F23" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4189</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1241</v>
+        <v>0.1956</v>
       </c>
       <c r="H23" t="n">
-        <v>0.5649999999999999</v>
+        <v>0.4189</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2938</v>
+        <v>0.2262</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1241</v>
+        <v>0.1956</v>
       </c>
       <c r="K23" t="n">
         <v>132</v>
@@ -1495,7 +1495,7 @@
         <v>123</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4179</v>
+        <v>0.4218</v>
       </c>
       <c r="N23" t="n">
         <v>255</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4878</v>
+        <v>0.4642</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0429</v>
+        <v>0.0409</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4178</v>
+        <v>-0.4129</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4878</v>
+        <v>0.4642</v>
       </c>
       <c r="F24" t="n">
-        <v>0.4878</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="H24" t="n">
-        <v>0.4878</v>
+        <v>0.5921999999999999</v>
       </c>
       <c r="I24" t="n">
-        <v>0.4878</v>
+        <v>0.3198</v>
       </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>-0.128</v>
       </c>
       <c r="K24" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="L24" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M24" t="n">
-        <v>0.4878</v>
+        <v>0.1918</v>
       </c>
       <c r="N24" t="n">
-        <v>66</v>
+        <v>255</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.4655</v>
+        <v>0.3673</v>
       </c>
       <c r="C25" t="n">
-        <v>0.041</v>
+        <v>0.0323</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.4279</v>
+        <v>-0.457</v>
       </c>
       <c r="E25" t="n">
-        <v>0.4655</v>
+        <v>0.3673</v>
       </c>
       <c r="F25" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.3673</v>
       </c>
       <c r="G25" t="n">
-        <v>-0.1872</v>
+        <v>0</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6526999999999999</v>
+        <v>0.3673</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3394</v>
+        <v>0.3673</v>
       </c>
       <c r="J25" t="n">
-        <v>-0.1872</v>
+        <v>0</v>
       </c>
       <c r="K25" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="L25" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M25" t="n">
-        <v>0.1522</v>
+        <v>0.3673</v>
       </c>
       <c r="N25" t="n">
-        <v>255</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.4273</v>
+        <v>0.3017</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0376</v>
+        <v>0.0266</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4451</v>
+        <v>-0.4869</v>
       </c>
       <c r="E26" t="n">
-        <v>0.4273</v>
+        <v>0.3017</v>
       </c>
       <c r="F26" t="n">
-        <v>1.2295</v>
+        <v>1.1224</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.8022</v>
+        <v>-0.8207</v>
       </c>
       <c r="H26" t="n">
-        <v>1.2295</v>
+        <v>1.1224</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6393</v>
+        <v>0.6061</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8022</v>
+        <v>-0.8207</v>
       </c>
       <c r="K26" t="n">
         <v>42</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.1629</v>
+        <v>-0.2146</v>
       </c>
       <c r="N26" t="n">
         <v>91</v>
@@ -1646,28 +1646,28 @@
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2777</v>
+        <v>0.2307</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0244</v>
+        <v>0.0203</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5125999999999999</v>
+        <v>-0.5192</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2777</v>
+        <v>0.2307</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2777</v>
+        <v>0.2307</v>
       </c>
       <c r="G27" t="n">
         <v>0</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2777</v>
+        <v>0.2307</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2777</v>
+        <v>0.2307</v>
       </c>
       <c r="J27" t="n">
         <v>0</v>
@@ -1679,7 +1679,7 @@
         <v>0</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2777</v>
+        <v>0.2307</v>
       </c>
       <c r="N27" t="n">
         <v>72</v>
@@ -1692,31 +1692,31 @@
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.255</v>
+        <v>0.2278</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0224</v>
+        <v>0.0201</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5229</v>
+        <v>-0.5205</v>
       </c>
       <c r="E28" t="n">
-        <v>0.255</v>
+        <v>0.2278</v>
       </c>
       <c r="F28" t="n">
-        <v>0.4818</v>
+        <v>0.3906</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.2268</v>
+        <v>-0.1628</v>
       </c>
       <c r="H28" t="n">
-        <v>0.4818</v>
+        <v>0.3906</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2505</v>
+        <v>0.2109</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.2268</v>
+        <v>-0.1628</v>
       </c>
       <c r="K28" t="n">
         <v>132</v>
@@ -1725,7 +1725,7 @@
         <v>123</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0237</v>
+        <v>0.0481</v>
       </c>
       <c r="N28" t="n">
         <v>255</v>
@@ -1738,31 +1738,31 @@
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0556</v>
+        <v>0.0208</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0049</v>
+        <v>0.0018</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6129</v>
+        <v>-0.6147</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0556</v>
+        <v>0.0208</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6479</v>
+        <v>0.6219</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.5923</v>
+        <v>-0.6011</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6479</v>
+        <v>0.6219</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3369</v>
+        <v>0.3358</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.5923</v>
+        <v>-0.6011</v>
       </c>
       <c r="K29" t="n">
         <v>51</v>
@@ -1771,7 +1771,7 @@
         <v>75</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2554000000000001</v>
+        <v>-0.2653</v>
       </c>
       <c r="N29" t="n">
         <v>126</v>
@@ -1784,31 +1784,31 @@
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.0245</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0022</v>
+        <v>0.0008</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.627</v>
+        <v>-0.6202</v>
       </c>
       <c r="E30" t="n">
-        <v>0.0245</v>
+        <v>0.008800000000000001</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3241</v>
+        <v>0.3422</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.2996</v>
+        <v>-0.3334</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3241</v>
+        <v>0.3422</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1685</v>
+        <v>0.1848</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.2996</v>
+        <v>-0.3334</v>
       </c>
       <c r="K30" t="n">
         <v>42</v>
@@ -1817,7 +1817,7 @@
         <v>49</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1311</v>
+        <v>-0.1486</v>
       </c>
       <c r="N30" t="n">
         <v>91</v>
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.2523</v>
+        <v>-0.29</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0222</v>
+        <v>-0.0255</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7519</v>
+        <v>-0.7562</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.2523</v>
+        <v>-0.29</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.2523</v>
+        <v>-0.29</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.2523</v>
+        <v>-0.29</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.2523</v>
+        <v>-0.29</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.2523</v>
+        <v>-0.29</v>
       </c>
       <c r="N31" t="n">
         <v>72</v>
@@ -1876,28 +1876,28 @@
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3257</v>
+        <v>-0.3602</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0287</v>
+        <v>-0.0317</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7851</v>
+        <v>-0.7882</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3257</v>
+        <v>-0.3602</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3257</v>
+        <v>-0.3602</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3257</v>
+        <v>-0.3602</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3257</v>
+        <v>-0.3602</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
@@ -1909,7 +1909,7 @@
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3257</v>
+        <v>-0.3602</v>
       </c>
       <c r="N32" t="n">
         <v>72</v>
@@ -1922,28 +1922,28 @@
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.3839</v>
+        <v>-0.4422</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0338</v>
+        <v>-0.0389</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8113</v>
+        <v>-0.8255</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.3839</v>
+        <v>-0.4422</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.3839</v>
+        <v>-0.4422</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.3839</v>
+        <v>-0.4422</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.3997</v>
+        <v>-0.4536</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
@@ -1955,7 +1955,7 @@
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.3997</v>
+        <v>-0.4536</v>
       </c>
       <c r="N33" t="n">
         <v>153</v>
@@ -1968,28 +1968,28 @@
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7134</v>
+        <v>-0.7361</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.06279999999999999</v>
+        <v>-0.0648</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9601</v>
+        <v>-0.9593</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7134</v>
+        <v>-0.7361</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7134</v>
+        <v>-0.7361</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7134</v>
+        <v>-0.7361</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7134</v>
+        <v>-0.7361</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
@@ -2001,7 +2001,7 @@
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7134</v>
+        <v>-0.7361</v>
       </c>
       <c r="N34" t="n">
         <v>66</v>
@@ -2010,32 +2010,32 @@
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.7855</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.06909999999999999</v>
+        <v>-0.0737</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.9926</v>
+        <v>-1.0053</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.7855</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.7855</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.7855</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.7855</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
@@ -2047,7 +2047,7 @@
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.7855</v>
+        <v>-0.8372000000000001</v>
       </c>
       <c r="N35" t="n">
         <v>72</v>
@@ -2056,93 +2056,93 @@
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8425</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0722</v>
+        <v>-0.0742</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0082</v>
+        <v>-1.0077</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8425</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8425</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8425</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8425</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8201000000000001</v>
+        <v>-0.8425</v>
       </c>
       <c r="N36" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8326</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.0733</v>
+        <v>-0.07580000000000001</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0139</v>
+        <v>-1.0163</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8326</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8326</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8326</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8326</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8326</v>
+        <v>-0.8614000000000001</v>
       </c>
       <c r="N37" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-0.9813</v>
+        <v>-1.0229</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.0864</v>
+        <v>-0.09</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.081</v>
+        <v>-1.0898</v>
       </c>
       <c r="E38" t="n">
-        <v>-0.9813</v>
+        <v>-1.0229</v>
       </c>
       <c r="F38" t="n">
-        <v>-0.9813</v>
+        <v>-1.0229</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-0.9813</v>
+        <v>-1.0229</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.9813</v>
+        <v>-1.0229</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-0.9813</v>
+        <v>-1.0229</v>
       </c>
       <c r="N38" t="n">
         <v>66</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.2055</v>
+        <v>-1.1154</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.1061</v>
+        <v>-0.0982</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.1822</v>
+        <v>-1.132</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.2055</v>
+        <v>-1.1154</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.2055</v>
+        <v>-1.1154</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.2055</v>
+        <v>-1.1154</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.2551</v>
+        <v>-1.1441</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.2551</v>
+        <v>-1.1441</v>
       </c>
       <c r="N39" t="n">
         <v>156</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4165</v>
+        <v>-1.4452</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1247</v>
+        <v>-0.1272</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2775</v>
+        <v>-1.2821</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4165</v>
+        <v>-1.4452</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4165</v>
+        <v>-1.4452</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4165</v>
+        <v>-1.4452</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4165</v>
+        <v>-1.4452</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4165</v>
+        <v>-1.4452</v>
       </c>
       <c r="N40" t="n">
         <v>66</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.5903</v>
+        <v>-2.3257</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.228</v>
+        <v>-0.2047</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.8074</v>
+        <v>-1.6829</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.5903</v>
+        <v>-2.3257</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.7712</v>
+        <v>-2.568</v>
       </c>
       <c r="G41" t="n">
-        <v>0.1809</v>
+        <v>0.2423</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.7712</v>
+        <v>-2.568</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.4409</v>
+        <v>-1.3867</v>
       </c>
       <c r="J41" t="n">
-        <v>0.1809</v>
+        <v>0.2423</v>
       </c>
       <c r="K41" t="n">
         <v>130</v>
@@ -2323,7 +2323,7 @@
         <v>97</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.26</v>
+        <v>-1.1444</v>
       </c>
       <c r="N41" t="n">
         <v>227</v>
@@ -2429,10 +2429,10 @@
         <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1.7105</v>
+        <v>1.8453</v>
       </c>
       <c r="J2" t="n">
-        <v>39.3415</v>
+        <v>42.4419</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.327</v>
+        <v>1.4217</v>
       </c>
       <c r="J3" t="n">
-        <v>30.521</v>
+        <v>32.6991</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.623</v>
+        <v>0.6129</v>
       </c>
       <c r="J4" t="n">
-        <v>14.329</v>
+        <v>14.0967</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5511</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="J5" t="n">
-        <v>12.6753</v>
+        <v>12.6247</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.22</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5511</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>12.6753</v>
+        <v>12.6247</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.97</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0534</v>
+        <v>0.0064</v>
       </c>
       <c r="J7" t="n">
-        <v>1.2282</v>
+        <v>0.1472</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.09180000000000001</v>
+        <v>-0.1193</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.1114</v>
+        <v>-2.7439</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4721</v>
+        <v>-0.4857</v>
       </c>
       <c r="J9" t="n">
-        <v>-10.8583</v>
+        <v>-11.1711</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.42</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.5476</v>
+        <v>-0.556</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.5948</v>
+        <v>-12.788</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.42</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.5476</v>
+        <v>-0.556</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.5948</v>
+        <v>-12.788</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.76</v>
       </c>
       <c r="I12" t="n">
-        <v>1.4648</v>
+        <v>1.5841</v>
       </c>
       <c r="J12" t="n">
-        <v>36.62</v>
+        <v>39.6025</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6999</v>
+        <v>0.6705</v>
       </c>
       <c r="J13" t="n">
-        <v>17.4975</v>
+        <v>16.7625</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3569</v>
+        <v>0.3605</v>
       </c>
       <c r="J14" t="n">
-        <v>8.922499999999999</v>
+        <v>9.012499999999999</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.218</v>
+        <v>-0.2061</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.45</v>
+        <v>-5.1525</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3454</v>
+        <v>-0.3262</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.635</v>
+        <v>-8.154999999999999</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1554</v>
+        <v>0.1595</v>
       </c>
       <c r="J17" t="n">
-        <v>3.885</v>
+        <v>3.9875</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0147</v>
+        <v>-0.0208</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.3675</v>
+        <v>-0.52</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.97</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0448</v>
+        <v>-0.0542</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.12</v>
+        <v>-1.355</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.89</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.138</v>
+        <v>-0.1526</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.45</v>
+        <v>-3.815</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.77</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2608</v>
+        <v>-0.2756</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.52</v>
+        <v>-6.89</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3214</v>
+        <v>0.3175</v>
       </c>
       <c r="J22" t="n">
-        <v>11.249</v>
+        <v>11.1125</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.145</v>
+        <v>0.1456</v>
       </c>
       <c r="J23" t="n">
-        <v>5.075</v>
+        <v>5.096</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.85</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1752</v>
+        <v>-0.1916</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.132</v>
+        <v>-6.706</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.74</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2845</v>
+        <v>-0.2998</v>
       </c>
       <c r="J25" t="n">
-        <v>-9.9575</v>
+        <v>-10.493</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3229</v>
+        <v>-0.3372</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.3015</v>
+        <v>-11.802</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7105</v>
+        <v>0.7844</v>
       </c>
       <c r="J27" t="n">
-        <v>24.8675</v>
+        <v>27.454</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.6425</v>
+        <v>0.7102000000000001</v>
       </c>
       <c r="J28" t="n">
-        <v>22.4875</v>
+        <v>24.857</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4003</v>
+        <v>0.4369</v>
       </c>
       <c r="J29" t="n">
-        <v>14.0105</v>
+        <v>15.2915</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0892</v>
+        <v>-0.0834</v>
       </c>
       <c r="J30" t="n">
-        <v>-3.122</v>
+        <v>-2.919</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.4179</v>
+        <v>-0.3964</v>
       </c>
       <c r="J31" t="n">
-        <v>-14.6265</v>
+        <v>-13.874</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.19</v>
       </c>
       <c r="I32" t="n">
-        <v>0.8757</v>
+        <v>1.0089</v>
       </c>
       <c r="J32" t="n">
-        <v>16.6383</v>
+        <v>19.1691</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.52</v>
       </c>
       <c r="I33" t="n">
-        <v>0.4936</v>
+        <v>0.5687</v>
       </c>
       <c r="J33" t="n">
-        <v>9.378399999999999</v>
+        <v>10.8053</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.33</v>
       </c>
       <c r="I34" t="n">
-        <v>0.377</v>
+        <v>0.4247</v>
       </c>
       <c r="J34" t="n">
-        <v>7.163</v>
+        <v>8.0693</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3245</v>
+        <v>0.3488</v>
       </c>
       <c r="J35" t="n">
-        <v>6.1655</v>
+        <v>6.6272</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.0618</v>
+        <v>0.08599999999999999</v>
       </c>
       <c r="J36" t="n">
-        <v>1.1742</v>
+        <v>1.634</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.91</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.0503</v>
+        <v>-0.07870000000000001</v>
       </c>
       <c r="J37" t="n">
-        <v>-0.9557</v>
+        <v>-1.4953</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3335</v>
+        <v>-0.3544</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.3365</v>
+        <v>-6.7336</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.61</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3684</v>
+        <v>-0.3881</v>
       </c>
       <c r="J39" t="n">
-        <v>-6.9996</v>
+        <v>-7.3739</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4141</v>
+        <v>-0.4315</v>
       </c>
       <c r="J40" t="n">
-        <v>-7.8679</v>
+        <v>-8.198499999999999</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.41</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5554</v>
+        <v>-0.5634</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.5526</v>
+        <v>-10.7046</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.93</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.0483</v>
+        <v>-0.07140000000000001</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.0143</v>
+        <v>-1.4994</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.73</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2692</v>
+        <v>-0.2901</v>
       </c>
       <c r="J43" t="n">
-        <v>-5.6532</v>
+        <v>-6.0921</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.64</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.351</v>
+        <v>-0.3696</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.371</v>
+        <v>-7.7616</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.62</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3696</v>
+        <v>-0.3873</v>
       </c>
       <c r="J45" t="n">
-        <v>-7.7616</v>
+        <v>-8.1333</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.55</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.435</v>
+        <v>-0.4493</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.135</v>
+        <v>-9.4353</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.96</v>
       </c>
       <c r="I47" t="n">
-        <v>1.3656</v>
+        <v>1.4928</v>
       </c>
       <c r="J47" t="n">
-        <v>28.6776</v>
+        <v>31.3488</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.6336000000000001</v>
+        <v>0.7088</v>
       </c>
       <c r="J48" t="n">
-        <v>13.3056</v>
+        <v>14.8848</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.32</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6076</v>
+        <v>0.6801</v>
       </c>
       <c r="J49" t="n">
-        <v>12.7596</v>
+        <v>14.2821</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.5544</v>
+        <v>0.6211</v>
       </c>
       <c r="J50" t="n">
-        <v>11.6424</v>
+        <v>13.0431</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.3825</v>
+        <v>0.4234</v>
       </c>
       <c r="J51" t="n">
-        <v>8.032500000000001</v>
+        <v>8.891400000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3644</v>
+        <v>0.3637</v>
       </c>
       <c r="J52" t="n">
-        <v>8.3812</v>
+        <v>8.3651</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.9</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.1045</v>
+        <v>-0.124</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.4035</v>
+        <v>-2.852</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.76</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2496</v>
+        <v>-0.2689</v>
       </c>
       <c r="J54" t="n">
-        <v>-5.7408</v>
+        <v>-6.1847</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.63</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3716</v>
+        <v>-0.3872</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.546799999999999</v>
+        <v>-8.9056</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.42</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5665</v>
+        <v>-0.5709</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.0295</v>
+        <v>-13.1307</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.02</v>
       </c>
       <c r="I57" t="n">
-        <v>1.4307</v>
+        <v>1.5612</v>
       </c>
       <c r="J57" t="n">
-        <v>32.9061</v>
+        <v>35.9076</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.86</v>
       </c>
       <c r="I58" t="n">
-        <v>1.2493</v>
+        <v>1.3713</v>
       </c>
       <c r="J58" t="n">
-        <v>28.7339</v>
+        <v>31.5399</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.26</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5258</v>
+        <v>0.5897</v>
       </c>
       <c r="J59" t="n">
-        <v>12.0934</v>
+        <v>13.5631</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.164</v>
+        <v>0.1931</v>
       </c>
       <c r="J60" t="n">
-        <v>3.772</v>
+        <v>4.4413</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4526</v>
+        <v>-0.4147</v>
       </c>
       <c r="J61" t="n">
-        <v>-10.4098</v>
+        <v>-9.5381</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4122</v>
+        <v>0.4518</v>
       </c>
       <c r="J62" t="n">
-        <v>10.7172</v>
+        <v>11.7468</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0423</v>
+        <v>0.0466</v>
       </c>
       <c r="J63" t="n">
-        <v>1.0998</v>
+        <v>1.2116</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0039</v>
+        <v>0.0027</v>
       </c>
       <c r="J64" t="n">
-        <v>0.1014</v>
+        <v>0.0702</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.1951</v>
+        <v>-0.2094</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.0726</v>
+        <v>-5.4444</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2357</v>
+        <v>-0.2498</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.1282</v>
+        <v>-6.4948</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.6716</v>
+        <v>0.7417</v>
       </c>
       <c r="J67" t="n">
-        <v>17.4616</v>
+        <v>19.2842</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.4747</v>
+        <v>0.5238</v>
       </c>
       <c r="J68" t="n">
-        <v>12.3422</v>
+        <v>13.6188</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4159</v>
+        <v>0.4566</v>
       </c>
       <c r="J69" t="n">
-        <v>10.8134</v>
+        <v>11.8716</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.12</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3559</v>
+        <v>0.3703</v>
       </c>
       <c r="J70" t="n">
-        <v>9.253399999999999</v>
+        <v>9.627800000000001</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4996</v>
+        <v>-0.4712</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.9896</v>
+        <v>-12.2512</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.31</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8645</v>
+        <v>0.8066</v>
       </c>
       <c r="J72" t="n">
-        <v>25.935</v>
+        <v>24.198</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.12</v>
       </c>
       <c r="I73" t="n">
-        <v>0.384</v>
+        <v>0.3789</v>
       </c>
       <c r="J73" t="n">
-        <v>11.52</v>
+        <v>11.367</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2436</v>
+        <v>0.2483</v>
       </c>
       <c r="J74" t="n">
-        <v>7.308</v>
+        <v>7.449</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0805</v>
+        <v>0.0906</v>
       </c>
       <c r="J75" t="n">
-        <v>2.415</v>
+        <v>2.718</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.82</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5886</v>
+        <v>-0.5547</v>
       </c>
       <c r="J76" t="n">
-        <v>-17.658</v>
+        <v>-16.641</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.4</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7513</v>
+        <v>0.7243000000000001</v>
       </c>
       <c r="J77" t="n">
-        <v>22.539</v>
+        <v>21.729</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4309</v>
+        <v>0.4316</v>
       </c>
       <c r="J78" t="n">
-        <v>12.927</v>
+        <v>12.948</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2856</v>
+        <v>0.2947</v>
       </c>
       <c r="J79" t="n">
-        <v>8.568</v>
+        <v>8.840999999999999</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0857</v>
+        <v>-0.0936</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.571</v>
+        <v>-2.808</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.78</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2692</v>
+        <v>-0.2802</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.076000000000001</v>
+        <v>-8.406000000000001</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.15</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3106</v>
+        <v>0.3062</v>
       </c>
       <c r="J82" t="n">
-        <v>7.4544</v>
+        <v>7.3488</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.12</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2632</v>
+        <v>0.2608</v>
       </c>
       <c r="J83" t="n">
-        <v>6.3168</v>
+        <v>6.2592</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.98</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0163</v>
+        <v>-0.0276</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.3912</v>
+        <v>-0.6624</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.5</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5028</v>
+        <v>-0.5098</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.0672</v>
+        <v>-12.2352</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.46</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.5392</v>
+        <v>-0.544</v>
       </c>
       <c r="J86" t="n">
-        <v>-12.9408</v>
+        <v>-13.056</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.54</v>
       </c>
       <c r="I87" t="n">
-        <v>0.6637</v>
+        <v>0.663</v>
       </c>
       <c r="J87" t="n">
-        <v>15.9288</v>
+        <v>15.912</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.27</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3623</v>
+        <v>0.3781</v>
       </c>
       <c r="J88" t="n">
-        <v>8.6952</v>
+        <v>9.074400000000001</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.18</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2562</v>
+        <v>0.2743</v>
       </c>
       <c r="J89" t="n">
-        <v>6.1488</v>
+        <v>6.5832</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.11</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1643</v>
+        <v>0.1829</v>
       </c>
       <c r="J90" t="n">
-        <v>3.9432</v>
+        <v>4.3896</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0572</v>
+        <v>-0.0592</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.3728</v>
+        <v>-1.4208</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.42</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0611</v>
+        <v>1.0083</v>
       </c>
       <c r="J92" t="n">
-        <v>28.6497</v>
+        <v>27.2241</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5309</v>
+        <v>0.5145</v>
       </c>
       <c r="J93" t="n">
-        <v>14.3343</v>
+        <v>13.8915</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.4018</v>
+        <v>0.3974</v>
       </c>
       <c r="J94" t="n">
-        <v>10.8486</v>
+        <v>10.7298</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3198</v>
+        <v>-0.3083</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.634600000000001</v>
+        <v>-8.3241</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.436</v>
+        <v>-0.4151</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.772</v>
+        <v>-11.2077</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6284</v>
+        <v>0.6087</v>
       </c>
       <c r="J97" t="n">
-        <v>16.9668</v>
+        <v>16.4349</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.2627</v>
+        <v>0.269</v>
       </c>
       <c r="J98" t="n">
-        <v>7.0929</v>
+        <v>7.263</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.0639</v>
+        <v>0.07190000000000001</v>
       </c>
       <c r="J99" t="n">
-        <v>1.7253</v>
+        <v>1.9413</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2105</v>
+        <v>-0.2236</v>
       </c>
       <c r="J100" t="n">
-        <v>-5.6835</v>
+        <v>-6.0372</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2308</v>
+        <v>-0.2439</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.2316</v>
+        <v>-6.5853</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.38</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9846</v>
+        <v>0.9239000000000001</v>
       </c>
       <c r="J102" t="n">
-        <v>29.538</v>
+        <v>27.717</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.37</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9656</v>
+        <v>0.9045</v>
       </c>
       <c r="J103" t="n">
-        <v>28.968</v>
+        <v>27.135</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5694</v>
+        <v>0.5514</v>
       </c>
       <c r="J104" t="n">
-        <v>17.082</v>
+        <v>16.542</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.09</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2856</v>
+        <v>0.2919</v>
       </c>
       <c r="J105" t="n">
-        <v>8.568</v>
+        <v>8.757</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8888</v>
+        <v>-0.8156</v>
       </c>
       <c r="J106" t="n">
-        <v>-26.664</v>
+        <v>-24.468</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.33</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6568000000000001</v>
+        <v>0.6354</v>
       </c>
       <c r="J107" t="n">
-        <v>19.704</v>
+        <v>19.062</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.25</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5184</v>
+        <v>0.5092</v>
       </c>
       <c r="J108" t="n">
-        <v>15.552</v>
+        <v>15.276</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1034</v>
+        <v>-0.1141</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.102</v>
+        <v>-3.423</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1597</v>
+        <v>-0.1721</v>
       </c>
       <c r="J110" t="n">
-        <v>-4.791</v>
+        <v>-5.163</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2724</v>
+        <v>-0.2846</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.172000000000001</v>
+        <v>-8.538</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.21</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4392</v>
+        <v>0.4207</v>
       </c>
       <c r="J112" t="n">
-        <v>9.6624</v>
+        <v>9.2554</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.83</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.1812</v>
+        <v>-0.2011</v>
       </c>
       <c r="J113" t="n">
-        <v>-3.9864</v>
+        <v>-4.4242</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2586</v>
+        <v>-0.2779</v>
       </c>
       <c r="J114" t="n">
-        <v>-5.6892</v>
+        <v>-6.1138</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4554</v>
+        <v>-0.4667</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.0188</v>
+        <v>-10.2674</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.49</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5017</v>
+        <v>-0.5104</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.0374</v>
+        <v>-11.2288</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9684</v>
+        <v>0.9499</v>
       </c>
       <c r="J117" t="n">
-        <v>21.3048</v>
+        <v>20.8978</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4749</v>
+        <v>0.4884</v>
       </c>
       <c r="J118" t="n">
-        <v>10.4478</v>
+        <v>10.7448</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.25</v>
       </c>
       <c r="I119" t="n">
-        <v>0.3314</v>
+        <v>0.35</v>
       </c>
       <c r="J119" t="n">
-        <v>7.2908</v>
+        <v>7.7</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.1</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1392</v>
+        <v>0.1604</v>
       </c>
       <c r="J120" t="n">
-        <v>3.0624</v>
+        <v>3.5288</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.96</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.09370000000000001</v>
+        <v>-0.09619999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.0614</v>
+        <v>-2.1164</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1513</v>
+        <v>1.1154</v>
       </c>
       <c r="J122" t="n">
-        <v>32.2364</v>
+        <v>31.2312</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.39</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9847</v>
+        <v>0.9276</v>
       </c>
       <c r="J123" t="n">
-        <v>27.5716</v>
+        <v>25.9728</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.24</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6516</v>
+        <v>0.6279</v>
       </c>
       <c r="J124" t="n">
-        <v>18.2448</v>
+        <v>17.5812</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.1066</v>
+        <v>-0.0955</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.9848</v>
+        <v>-2.674</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.3169</v>
+        <v>-0.2992</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.873200000000001</v>
+        <v>-8.377599999999999</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.42</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8667</v>
+        <v>0.8148</v>
       </c>
       <c r="J127" t="n">
-        <v>24.2676</v>
+        <v>22.8144</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.82</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2083</v>
+        <v>-0.2242</v>
       </c>
       <c r="J128" t="n">
-        <v>-5.8324</v>
+        <v>-6.2776</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2284</v>
+        <v>-0.2441</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.3952</v>
+        <v>-6.8348</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.2678</v>
+        <v>-0.283</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.4984</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.2678</v>
+        <v>-0.283</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.4984</v>
+        <v>-7.924</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.7401</v>
+        <v>0.6984</v>
       </c>
       <c r="J132" t="n">
-        <v>20.7228</v>
+        <v>19.5552</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.6162</v>
+        <v>0.5888</v>
       </c>
       <c r="J133" t="n">
-        <v>17.2536</v>
+        <v>16.4864</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.08</v>
       </c>
       <c r="I134" t="n">
-        <v>0.271</v>
+        <v>0.2746</v>
       </c>
       <c r="J134" t="n">
-        <v>7.588</v>
+        <v>7.6888</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2129</v>
+        <v>0.2195</v>
       </c>
       <c r="J135" t="n">
-        <v>5.9612</v>
+        <v>6.146</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.7203000000000001</v>
+        <v>-0.6711</v>
       </c>
       <c r="J136" t="n">
-        <v>-20.1684</v>
+        <v>-18.7908</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.28</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5837</v>
+        <v>0.5667</v>
       </c>
       <c r="J137" t="n">
-        <v>16.3436</v>
+        <v>15.8676</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.23</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4947</v>
+        <v>0.4852</v>
       </c>
       <c r="J138" t="n">
-        <v>13.8516</v>
+        <v>13.5856</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0755</v>
+        <v>-0.0858</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.114</v>
+        <v>-2.4024</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2285</v>
+        <v>-0.2421</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.398</v>
+        <v>-6.7788</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3263</v>
+        <v>-0.3381</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.1364</v>
+        <v>-9.466799999999999</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.12</v>
       </c>
       <c r="I142" t="n">
-        <v>1.7983</v>
+        <v>1.8088</v>
       </c>
       <c r="J142" t="n">
-        <v>37.7643</v>
+        <v>37.9848</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>2</v>
       </c>
       <c r="I143" t="n">
-        <v>1.6658</v>
+        <v>1.6707</v>
       </c>
       <c r="J143" t="n">
-        <v>34.9818</v>
+        <v>35.0847</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.32</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7836</v>
+        <v>0.7549</v>
       </c>
       <c r="J144" t="n">
-        <v>16.4556</v>
+        <v>15.8529</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4262</v>
+        <v>0.4368</v>
       </c>
       <c r="J145" t="n">
-        <v>8.950200000000001</v>
+        <v>9.172800000000001</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.83</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.6556</v>
+        <v>-0.597</v>
       </c>
       <c r="J146" t="n">
-        <v>-13.7676</v>
+        <v>-12.537</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.95</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0131</v>
+        <v>-0.0371</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.2751</v>
+        <v>-0.7791</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1027</v>
+        <v>-0.1279</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.1567</v>
+        <v>-2.6859</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.149</v>
+        <v>-0.1738</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.129</v>
+        <v>-3.6498</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.34</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6281</v>
+        <v>-0.6296</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.1901</v>
+        <v>-13.2216</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.34</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6281</v>
+        <v>-0.6296</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.1901</v>
+        <v>-13.2216</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.87</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.09470000000000001</v>
+        <v>-0.124</v>
       </c>
       <c r="J152" t="n">
-        <v>-1.7046</v>
+        <v>-2.232</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2201</v>
+        <v>-0.2461</v>
       </c>
       <c r="J153" t="n">
-        <v>-3.9618</v>
+        <v>-4.4298</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.58</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.3933</v>
+        <v>-0.4122</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.0794</v>
+        <v>-7.4196</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.54</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.4302</v>
+        <v>-0.447</v>
       </c>
       <c r="J155" t="n">
-        <v>-7.7436</v>
+        <v>-8.045999999999999</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.32</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.639</v>
+        <v>-0.6405999999999999</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.502</v>
+        <v>-11.5308</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.9</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5458</v>
+        <v>1.5463</v>
       </c>
       <c r="J157" t="n">
-        <v>27.8244</v>
+        <v>27.8334</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.5</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0921</v>
+        <v>1.0607</v>
       </c>
       <c r="J158" t="n">
-        <v>19.6578</v>
+        <v>19.0926</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0685</v>
+        <v>1.0334</v>
       </c>
       <c r="J159" t="n">
-        <v>19.233</v>
+        <v>18.6012</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.44</v>
       </c>
       <c r="I160" t="n">
-        <v>1.0158</v>
+        <v>0.9723000000000001</v>
       </c>
       <c r="J160" t="n">
-        <v>18.2844</v>
+        <v>17.5014</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.33</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7978</v>
+        <v>0.7689</v>
       </c>
       <c r="J161" t="n">
-        <v>14.3604</v>
+        <v>13.8402</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.601</v>
+        <v>0.5885</v>
       </c>
       <c r="J162" t="n">
-        <v>18.03</v>
+        <v>17.655</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4818</v>
+        <v>0.4792</v>
       </c>
       <c r="J163" t="n">
-        <v>14.454</v>
+        <v>14.376</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.2659</v>
+        <v>0.276</v>
       </c>
       <c r="J164" t="n">
-        <v>7.977</v>
+        <v>8.279999999999999</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1016</v>
+        <v>0.1144</v>
       </c>
       <c r="J165" t="n">
-        <v>3.048</v>
+        <v>3.432</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.26</v>
+        <v>-0.2709</v>
       </c>
       <c r="J166" t="n">
-        <v>-7.8</v>
+        <v>-8.127000000000001</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5796</v>
+        <v>0.5484</v>
       </c>
       <c r="J167" t="n">
-        <v>17.388</v>
+        <v>16.452</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.11</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3867</v>
+        <v>0.3746</v>
       </c>
       <c r="J168" t="n">
-        <v>11.601</v>
+        <v>11.238</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.125</v>
+        <v>-0.132</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.75</v>
+        <v>-3.96</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.5081</v>
+        <v>-0.4881</v>
       </c>
       <c r="J170" t="n">
-        <v>-15.243</v>
+        <v>-14.643</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.6655</v>
+        <v>-0.628</v>
       </c>
       <c r="J171" t="n">
-        <v>-19.965</v>
+        <v>-18.84</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.709</v>
+        <v>0.6768</v>
       </c>
       <c r="J172" t="n">
-        <v>17.725</v>
+        <v>16.92</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2399</v>
+        <v>0.2429</v>
       </c>
       <c r="J173" t="n">
-        <v>5.9975</v>
+        <v>6.0725</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.92</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1063</v>
+        <v>-0.1195</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.6575</v>
+        <v>-2.9875</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.76</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2724</v>
+        <v>-0.2865</v>
       </c>
       <c r="J175" t="n">
-        <v>-6.81</v>
+        <v>-7.1625</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.3959</v>
+        <v>-0.4063</v>
       </c>
       <c r="J176" t="n">
-        <v>-9.897500000000001</v>
+        <v>-10.1575</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.5</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1747</v>
+        <v>1.1337</v>
       </c>
       <c r="J177" t="n">
-        <v>29.3675</v>
+        <v>28.3425</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.5374</v>
+        <v>0.519</v>
       </c>
       <c r="J178" t="n">
-        <v>13.435</v>
+        <v>12.975</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.252</v>
+        <v>-0.2464</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.3</v>
+        <v>-6.16</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.92</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3137</v>
+        <v>-0.3041</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.8425</v>
+        <v>-7.6025</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4299</v>
+        <v>-0.4109</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.7475</v>
+        <v>-10.2725</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2708</v>
+        <v>0.2702</v>
       </c>
       <c r="J182" t="n">
-        <v>7.0408</v>
+        <v>7.0252</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0126</v>
+        <v>-0.0192</v>
       </c>
       <c r="J183" t="n">
-        <v>-0.3276</v>
+        <v>-0.4992</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.98</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0285</v>
+        <v>-0.0371</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.741</v>
+        <v>-0.9646</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.08119999999999999</v>
+        <v>-0.09379999999999999</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.1112</v>
+        <v>-2.4388</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.58</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4386</v>
+        <v>-0.4476</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.4036</v>
+        <v>-11.6376</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1.1067</v>
+        <v>1.0658</v>
       </c>
       <c r="J187" t="n">
-        <v>28.7742</v>
+        <v>27.7108</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.3</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7981</v>
+        <v>0.7561</v>
       </c>
       <c r="J188" t="n">
-        <v>20.7506</v>
+        <v>19.6586</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4657</v>
+        <v>0.4589</v>
       </c>
       <c r="J189" t="n">
-        <v>12.1082</v>
+        <v>11.9314</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.03</v>
       </c>
       <c r="I190" t="n">
-        <v>0.0885</v>
+        <v>0.1069</v>
       </c>
       <c r="J190" t="n">
-        <v>2.301</v>
+        <v>2.7794</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.213</v>
+        <v>-0.2025</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.538</v>
+        <v>-5.265</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.87</v>
       </c>
       <c r="I192" t="n">
-        <v>0.0531</v>
+        <v>-0.0256</v>
       </c>
       <c r="J192" t="n">
-        <v>0.9026999999999999</v>
+        <v>-0.4352</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.36</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.5599</v>
+        <v>-0.5735</v>
       </c>
       <c r="J193" t="n">
-        <v>-9.5183</v>
+        <v>-9.749499999999999</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.34</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.58</v>
+        <v>-0.5917</v>
       </c>
       <c r="J194" t="n">
-        <v>-9.859999999999999</v>
+        <v>-10.0589</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.28</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6419</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="J195" t="n">
-        <v>-10.9123</v>
+        <v>-11.0109</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6419</v>
+        <v>-0.6477000000000001</v>
       </c>
       <c r="J196" t="n">
-        <v>-10.9123</v>
+        <v>-11.0109</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.19</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8338</v>
+        <v>1.8616</v>
       </c>
       <c r="J197" t="n">
-        <v>31.1746</v>
+        <v>31.6472</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.62</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2217</v>
+        <v>1.2035</v>
       </c>
       <c r="J198" t="n">
-        <v>20.7689</v>
+        <v>20.4595</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.59</v>
       </c>
       <c r="I199" t="n">
-        <v>1.1887</v>
+        <v>1.1677</v>
       </c>
       <c r="J199" t="n">
-        <v>20.2079</v>
+        <v>19.8509</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.953</v>
+        <v>0.9102</v>
       </c>
       <c r="J200" t="n">
-        <v>16.201</v>
+        <v>15.4734</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.25</v>
       </c>
       <c r="I201" t="n">
-        <v>0.5984</v>
+        <v>0.5957</v>
       </c>
       <c r="J201" t="n">
-        <v>10.1728</v>
+        <v>10.1269</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.41</v>
       </c>
       <c r="I202" t="n">
-        <v>1.0072</v>
+        <v>0.9540999999999999</v>
       </c>
       <c r="J202" t="n">
-        <v>25.18</v>
+        <v>23.8525</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.33</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8462</v>
+        <v>0.8021</v>
       </c>
       <c r="J203" t="n">
-        <v>21.155</v>
+        <v>20.0525</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.29</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7568</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="J204" t="n">
-        <v>18.92</v>
+        <v>18.0825</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.2</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5499000000000001</v>
+        <v>0.5383</v>
       </c>
       <c r="J205" t="n">
-        <v>13.7475</v>
+        <v>13.4575</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.07</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2005</v>
+        <v>0.2186</v>
       </c>
       <c r="J206" t="n">
-        <v>5.0125</v>
+        <v>5.465</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.96</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0439</v>
+        <v>-0.0577</v>
       </c>
       <c r="J207" t="n">
-        <v>-1.0975</v>
+        <v>-1.4425</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.85</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.1705</v>
+        <v>-0.188</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.2625</v>
+        <v>-4.7</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.1803</v>
+        <v>-0.198</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.5075</v>
+        <v>-4.95</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2288</v>
+        <v>-0.2466</v>
       </c>
       <c r="J210" t="n">
-        <v>-5.72</v>
+        <v>-6.165</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2773</v>
+        <v>-0.2942</v>
       </c>
       <c r="J211" t="n">
-        <v>-6.9325</v>
+        <v>-7.355</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>0.8104</v>
+        <v>0.7782</v>
       </c>
       <c r="J212" t="n">
-        <v>21.0704</v>
+        <v>20.2332</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.22</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4448</v>
+        <v>0.4453</v>
       </c>
       <c r="J213" t="n">
-        <v>11.5648</v>
+        <v>11.5778</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.05</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1231</v>
+        <v>0.1364</v>
       </c>
       <c r="J214" t="n">
-        <v>3.2006</v>
+        <v>3.5464</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0098</v>
+        <v>-0.0075</v>
       </c>
       <c r="J215" t="n">
-        <v>-0.2548</v>
+        <v>-0.195</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2105</v>
+        <v>-0.2214</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.473</v>
+        <v>-5.7564</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.37</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9913</v>
+        <v>0.9258999999999999</v>
       </c>
       <c r="J217" t="n">
-        <v>25.7738</v>
+        <v>24.0734</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5649</v>
+        <v>0.5432</v>
       </c>
       <c r="J218" t="n">
-        <v>14.6874</v>
+        <v>14.1232</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0173</v>
+        <v>-0.0118</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.4498</v>
+        <v>-0.3068</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.95</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2182</v>
+        <v>-0.2148</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.6732</v>
+        <v>-5.5848</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.88</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4282</v>
+        <v>-0.4097</v>
       </c>
       <c r="J221" t="n">
-        <v>-11.1332</v>
+        <v>-10.6522</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.71</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3491</v>
+        <v>1.3349</v>
       </c>
       <c r="J222" t="n">
-        <v>32.3784</v>
+        <v>32.0376</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.52</v>
       </c>
       <c r="I223" t="n">
-        <v>1.1248</v>
+        <v>1.0946</v>
       </c>
       <c r="J223" t="n">
-        <v>26.9952</v>
+        <v>26.2704</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.33</v>
       </c>
       <c r="I224" t="n">
-        <v>0.8179</v>
+        <v>0.7829</v>
       </c>
       <c r="J224" t="n">
-        <v>19.6296</v>
+        <v>18.7896</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.31</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7734</v>
+        <v>0.7436</v>
       </c>
       <c r="J225" t="n">
-        <v>18.5616</v>
+        <v>17.8464</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.26</v>
       </c>
       <c r="I226" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.6424</v>
       </c>
       <c r="J226" t="n">
-        <v>15.8112</v>
+        <v>15.4176</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1892</v>
+        <v>0.1637</v>
       </c>
       <c r="J227" t="n">
-        <v>4.5408</v>
+        <v>3.9288</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.74</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2592</v>
+        <v>-0.2804</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.2208</v>
+        <v>-6.7296</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.71</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.2877</v>
+        <v>-0.3081</v>
       </c>
       <c r="J229" t="n">
-        <v>-6.9048</v>
+        <v>-7.3944</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3054</v>
+        <v>-0.3255</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.3296</v>
+        <v>-7.812</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.3</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6683</v>
+        <v>-0.6662</v>
       </c>
       <c r="J231" t="n">
-        <v>-16.0392</v>
+        <v>-15.9888</v>
       </c>
     </row>
   </sheetData>

--- a/database/event/3428/event_3428_evp_summary.xlsx
+++ b/database/event/3428/event_3428_evp_summary.xlsx
@@ -496,31 +496,31 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>8.705299999999999</v>
+        <v>8.6904</v>
       </c>
       <c r="C2" t="n">
-        <v>0.7662</v>
+        <v>0.7649</v>
       </c>
       <c r="D2" t="n">
-        <v>3.3386</v>
+        <v>3.3531</v>
       </c>
       <c r="E2" t="n">
-        <v>8.705299999999999</v>
+        <v>8.6904</v>
       </c>
       <c r="F2" t="n">
-        <v>3.0033</v>
+        <v>3.0052</v>
       </c>
       <c r="G2" t="n">
-        <v>5.702</v>
+        <v>5.6852</v>
       </c>
       <c r="H2" t="n">
-        <v>5.0147</v>
+        <v>4.8402</v>
       </c>
       <c r="I2" t="n">
-        <v>2.7079</v>
+        <v>2.7176</v>
       </c>
       <c r="J2" t="n">
-        <v>5.702</v>
+        <v>5.8094</v>
       </c>
       <c r="K2" t="n">
         <v>130</v>
@@ -529,7 +529,7 @@
         <v>97</v>
       </c>
       <c r="M2" t="n">
-        <v>8.4099</v>
+        <v>8.527000000000001</v>
       </c>
       <c r="N2" t="n">
         <v>227</v>
@@ -542,31 +542,31 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>5.5471</v>
+        <v>5.5715</v>
       </c>
       <c r="C3" t="n">
-        <v>0.4883</v>
+        <v>0.4904</v>
       </c>
       <c r="D3" t="n">
-        <v>1.901</v>
+        <v>1.9323</v>
       </c>
       <c r="E3" t="n">
-        <v>5.5471</v>
+        <v>5.5715</v>
       </c>
       <c r="F3" t="n">
-        <v>3.218</v>
+        <v>3.1851</v>
       </c>
       <c r="G3" t="n">
-        <v>2.3291</v>
+        <v>2.3864</v>
       </c>
       <c r="H3" t="n">
-        <v>5.7231</v>
+        <v>5.5155</v>
       </c>
       <c r="I3" t="n">
-        <v>3.0904</v>
+        <v>3.0968</v>
       </c>
       <c r="J3" t="n">
-        <v>2.3291</v>
+        <v>2.3864</v>
       </c>
       <c r="K3" t="n">
         <v>130</v>
@@ -575,7 +575,7 @@
         <v>97</v>
       </c>
       <c r="M3" t="n">
-        <v>5.419499999999999</v>
+        <v>5.4832</v>
       </c>
       <c r="N3" t="n">
         <v>227</v>
@@ -588,31 +588,31 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>4.2939</v>
+        <v>4.1927</v>
       </c>
       <c r="C4" t="n">
-        <v>0.3779</v>
+        <v>0.369</v>
       </c>
       <c r="D4" t="n">
-        <v>1.3305</v>
+        <v>1.3042</v>
       </c>
       <c r="E4" t="n">
-        <v>4.2939</v>
+        <v>4.1927</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1744</v>
+        <v>2.0819</v>
       </c>
       <c r="G4" t="n">
-        <v>2.1195</v>
+        <v>2.1108</v>
       </c>
       <c r="H4" t="n">
-        <v>2.2798</v>
+        <v>2.0819</v>
       </c>
       <c r="I4" t="n">
-        <v>1.2311</v>
+        <v>1.1689</v>
       </c>
       <c r="J4" t="n">
-        <v>2.1195</v>
+        <v>2.1108</v>
       </c>
       <c r="K4" t="n">
         <v>130</v>
@@ -621,7 +621,7 @@
         <v>97</v>
       </c>
       <c r="M4" t="n">
-        <v>3.3506</v>
+        <v>3.2797</v>
       </c>
       <c r="N4" t="n">
         <v>227</v>
@@ -634,31 +634,31 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>4.0107</v>
+        <v>3.9531</v>
       </c>
       <c r="C5" t="n">
-        <v>0.353</v>
+        <v>0.3479</v>
       </c>
       <c r="D5" t="n">
-        <v>1.2015</v>
+        <v>1.195</v>
       </c>
       <c r="E5" t="n">
-        <v>4.0107</v>
+        <v>3.9531</v>
       </c>
       <c r="F5" t="n">
-        <v>2.4516</v>
+        <v>2.516</v>
       </c>
       <c r="G5" t="n">
-        <v>1.5591</v>
+        <v>1.4371</v>
       </c>
       <c r="H5" t="n">
-        <v>3.1947</v>
+        <v>3.0036</v>
       </c>
       <c r="I5" t="n">
-        <v>1.7251</v>
+        <v>1.6864</v>
       </c>
       <c r="J5" t="n">
-        <v>1.5591</v>
+        <v>1.4371</v>
       </c>
       <c r="K5" t="n">
         <v>130</v>
@@ -667,7 +667,7 @@
         <v>97</v>
       </c>
       <c r="M5" t="n">
-        <v>3.2842</v>
+        <v>3.1235</v>
       </c>
       <c r="N5" t="n">
         <v>227</v>
@@ -680,31 +680,31 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>3.5906</v>
+        <v>3.5452</v>
       </c>
       <c r="C6" t="n">
-        <v>0.316</v>
+        <v>0.312</v>
       </c>
       <c r="D6" t="n">
-        <v>1.0103</v>
+        <v>1.0092</v>
       </c>
       <c r="E6" t="n">
-        <v>3.5906</v>
+        <v>3.5452</v>
       </c>
       <c r="F6" t="n">
-        <v>2.7751</v>
+        <v>2.8252</v>
       </c>
       <c r="G6" t="n">
-        <v>0.8155</v>
+        <v>0.72</v>
       </c>
       <c r="H6" t="n">
-        <v>4.2619</v>
+        <v>4.1643</v>
       </c>
       <c r="I6" t="n">
-        <v>2.3014</v>
+        <v>2.3381</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8155</v>
+        <v>0.72</v>
       </c>
       <c r="K6" t="n">
         <v>42</v>
@@ -713,7 +713,7 @@
         <v>49</v>
       </c>
       <c r="M6" t="n">
-        <v>3.1169</v>
+        <v>3.0581</v>
       </c>
       <c r="N6" t="n">
         <v>91</v>
@@ -722,93 +722,93 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>shox</t>
+          <t>NEKIZ</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>3.4003</v>
+        <v>3.3876</v>
       </c>
       <c r="C7" t="n">
-        <v>0.2993</v>
+        <v>0.2982</v>
       </c>
       <c r="D7" t="n">
-        <v>0.9237</v>
+        <v>0.9374</v>
       </c>
       <c r="E7" t="n">
-        <v>3.4003</v>
+        <v>3.3876</v>
       </c>
       <c r="F7" t="n">
-        <v>3.4003</v>
+        <v>2.4623</v>
       </c>
       <c r="G7" t="n">
-        <v>0</v>
+        <v>0.9253</v>
       </c>
       <c r="H7" t="n">
-        <v>4.7173</v>
+        <v>2.8019</v>
       </c>
       <c r="I7" t="n">
-        <v>4.8389</v>
+        <v>1.5732</v>
       </c>
       <c r="J7" t="n">
-        <v>0</v>
+        <v>0.9253</v>
       </c>
       <c r="K7" t="n">
-        <v>156</v>
+        <v>132</v>
       </c>
       <c r="L7" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M7" t="n">
-        <v>4.8389</v>
+        <v>2.4985</v>
       </c>
       <c r="N7" t="n">
-        <v>156</v>
+        <v>255</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>NEKIZ</t>
+          <t>shox</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>3.2603</v>
+        <v>3.2416</v>
       </c>
       <c r="C8" t="n">
-        <v>0.287</v>
+        <v>0.2853</v>
       </c>
       <c r="D8" t="n">
-        <v>0.86</v>
+        <v>0.8709</v>
       </c>
       <c r="E8" t="n">
-        <v>3.2603</v>
+        <v>3.2416</v>
       </c>
       <c r="F8" t="n">
-        <v>2.4125</v>
+        <v>3.2416</v>
       </c>
       <c r="G8" t="n">
-        <v>0.8478</v>
+        <v>0</v>
       </c>
       <c r="H8" t="n">
-        <v>3.0656</v>
+        <v>4.4787</v>
       </c>
       <c r="I8" t="n">
-        <v>1.6554</v>
+        <v>4.5984</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8478</v>
+        <v>0</v>
       </c>
       <c r="K8" t="n">
-        <v>132</v>
+        <v>156</v>
       </c>
       <c r="L8" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M8" t="n">
-        <v>2.5032</v>
+        <v>4.5984</v>
       </c>
       <c r="N8" t="n">
-        <v>255</v>
+        <v>156</v>
       </c>
     </row>
     <row r="9">
@@ -818,31 +818,31 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.0191</v>
+        <v>2.9973</v>
       </c>
       <c r="C9" t="n">
-        <v>0.2657</v>
+        <v>0.2638</v>
       </c>
       <c r="D9" t="n">
-        <v>0.7502</v>
+        <v>0.7596000000000001</v>
       </c>
       <c r="E9" t="n">
-        <v>3.0191</v>
+        <v>2.9973</v>
       </c>
       <c r="F9" t="n">
-        <v>2.2043</v>
+        <v>2.2495</v>
       </c>
       <c r="G9" t="n">
-        <v>0.8148</v>
+        <v>0.7478</v>
       </c>
       <c r="H9" t="n">
-        <v>2.3786</v>
+        <v>2.2495</v>
       </c>
       <c r="I9" t="n">
-        <v>1.2844</v>
+        <v>1.263</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8148</v>
+        <v>0.7478</v>
       </c>
       <c r="K9" t="n">
         <v>51</v>
@@ -851,7 +851,7 @@
         <v>75</v>
       </c>
       <c r="M9" t="n">
-        <v>2.0992</v>
+        <v>2.0108</v>
       </c>
       <c r="N9" t="n">
         <v>126</v>
@@ -864,31 +864,31 @@
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2.8409</v>
+        <v>2.8932</v>
       </c>
       <c r="C10" t="n">
-        <v>0.2501</v>
+        <v>0.2547</v>
       </c>
       <c r="D10" t="n">
-        <v>0.669</v>
+        <v>0.7122000000000001</v>
       </c>
       <c r="E10" t="n">
-        <v>2.8409</v>
+        <v>2.8932</v>
       </c>
       <c r="F10" t="n">
-        <v>2.3137</v>
+        <v>2.3925</v>
       </c>
       <c r="G10" t="n">
-        <v>0.5272</v>
+        <v>0.5007</v>
       </c>
       <c r="H10" t="n">
-        <v>2.7397</v>
+        <v>2.5399</v>
       </c>
       <c r="I10" t="n">
-        <v>1.4794</v>
+        <v>1.4261</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5272</v>
+        <v>0.5007</v>
       </c>
       <c r="K10" t="n">
         <v>51</v>
@@ -897,7 +897,7 @@
         <v>75</v>
       </c>
       <c r="M10" t="n">
-        <v>2.0066</v>
+        <v>1.9268</v>
       </c>
       <c r="N10" t="n">
         <v>126</v>
@@ -910,28 +910,28 @@
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2.7476</v>
+        <v>2.6821</v>
       </c>
       <c r="C11" t="n">
-        <v>0.2418</v>
+        <v>0.2361</v>
       </c>
       <c r="D11" t="n">
-        <v>0.6266</v>
+        <v>0.616</v>
       </c>
       <c r="E11" t="n">
-        <v>2.7476</v>
+        <v>2.6821</v>
       </c>
       <c r="F11" t="n">
-        <v>2.7476</v>
+        <v>2.6821</v>
       </c>
       <c r="G11" t="n">
         <v>0</v>
       </c>
       <c r="H11" t="n">
-        <v>3.2888</v>
+        <v>3.1964</v>
       </c>
       <c r="I11" t="n">
-        <v>3.3735</v>
+        <v>3.2818</v>
       </c>
       <c r="J11" t="n">
         <v>0</v>
@@ -943,7 +943,7 @@
         <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3735</v>
+        <v>3.2818</v>
       </c>
       <c r="N11" t="n">
         <v>153</v>
@@ -956,31 +956,31 @@
         </is>
       </c>
       <c r="B12" t="n">
-        <v>2.184</v>
+        <v>2.2736</v>
       </c>
       <c r="C12" t="n">
-        <v>0.1922</v>
+        <v>0.2001</v>
       </c>
       <c r="D12" t="n">
-        <v>0.37</v>
+        <v>0.4299</v>
       </c>
       <c r="E12" t="n">
-        <v>2.184</v>
+        <v>2.2736</v>
       </c>
       <c r="F12" t="n">
-        <v>2.4502</v>
+        <v>2.5248</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.2662</v>
+        <v>-0.2512</v>
       </c>
       <c r="H12" t="n">
-        <v>3.1899</v>
+        <v>3.0367</v>
       </c>
       <c r="I12" t="n">
-        <v>1.7225</v>
+        <v>1.705</v>
       </c>
       <c r="J12" t="n">
-        <v>-0.2662</v>
+        <v>-0.2512</v>
       </c>
       <c r="K12" t="n">
         <v>42</v>
@@ -989,7 +989,7 @@
         <v>49</v>
       </c>
       <c r="M12" t="n">
-        <v>1.4563</v>
+        <v>1.4538</v>
       </c>
       <c r="N12" t="n">
         <v>91</v>
@@ -998,124 +998,124 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>AcilioN</t>
+          <t>refrezh</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>2.1655</v>
+        <v>2.187</v>
       </c>
       <c r="C13" t="n">
-        <v>0.1906</v>
+        <v>0.1925</v>
       </c>
       <c r="D13" t="n">
-        <v>0.3616</v>
+        <v>0.3905</v>
       </c>
       <c r="E13" t="n">
-        <v>2.1655</v>
+        <v>2.187</v>
       </c>
       <c r="F13" t="n">
-        <v>1.9648</v>
+        <v>2.5306</v>
       </c>
       <c r="G13" t="n">
-        <v>0.2007</v>
+        <v>-0.3436</v>
       </c>
       <c r="H13" t="n">
-        <v>1.9648</v>
+        <v>3.0582</v>
       </c>
       <c r="I13" t="n">
-        <v>1.061</v>
+        <v>1.7171</v>
       </c>
       <c r="J13" t="n">
-        <v>0.2007</v>
+        <v>-0.3436</v>
       </c>
       <c r="K13" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L13" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="M13" t="n">
-        <v>1.2617</v>
+        <v>1.3735</v>
       </c>
       <c r="N13" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>bodyy</t>
+          <t>AcilioN</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>2.0894</v>
+        <v>1.9595</v>
       </c>
       <c r="C14" t="n">
-        <v>0.1839</v>
+        <v>0.1725</v>
       </c>
       <c r="D14" t="n">
-        <v>0.3269</v>
+        <v>0.2869</v>
       </c>
       <c r="E14" t="n">
-        <v>2.0894</v>
+        <v>1.9595</v>
       </c>
       <c r="F14" t="n">
-        <v>2.0894</v>
+        <v>1.837</v>
       </c>
       <c r="G14" t="n">
-        <v>0</v>
+        <v>0.1225</v>
       </c>
       <c r="H14" t="n">
-        <v>2.0894</v>
+        <v>1.837</v>
       </c>
       <c r="I14" t="n">
-        <v>2.1432</v>
+        <v>1.0314</v>
       </c>
       <c r="J14" t="n">
-        <v>0</v>
+        <v>0.1225</v>
       </c>
       <c r="K14" t="n">
-        <v>156</v>
+        <v>51</v>
       </c>
       <c r="L14" t="n">
-        <v>0</v>
+        <v>75</v>
       </c>
       <c r="M14" t="n">
-        <v>2.1432</v>
+        <v>1.1539</v>
       </c>
       <c r="N14" t="n">
-        <v>156</v>
+        <v>126</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Ex6TenZ</t>
+          <t>bodyy</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.0676</v>
+        <v>1.9198</v>
       </c>
       <c r="C15" t="n">
-        <v>0.182</v>
+        <v>0.169</v>
       </c>
       <c r="D15" t="n">
-        <v>0.317</v>
+        <v>0.2688</v>
       </c>
       <c r="E15" t="n">
-        <v>2.0676</v>
+        <v>1.9198</v>
       </c>
       <c r="F15" t="n">
-        <v>2.0676</v>
+        <v>1.9198</v>
       </c>
       <c r="G15" t="n">
         <v>0</v>
       </c>
       <c r="H15" t="n">
-        <v>2.0676</v>
+        <v>1.9198</v>
       </c>
       <c r="I15" t="n">
-        <v>2.1209</v>
+        <v>1.9711</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -1127,7 +1127,7 @@
         <v>0</v>
       </c>
       <c r="M15" t="n">
-        <v>2.1209</v>
+        <v>1.9711</v>
       </c>
       <c r="N15" t="n">
         <v>156</v>
@@ -1136,47 +1136,47 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>refrezh</t>
+          <t>Ex6TenZ</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.0494</v>
+        <v>1.8289</v>
       </c>
       <c r="C16" t="n">
-        <v>0.1804</v>
+        <v>0.161</v>
       </c>
       <c r="D16" t="n">
-        <v>0.3087</v>
+        <v>0.2274</v>
       </c>
       <c r="E16" t="n">
-        <v>2.0494</v>
+        <v>1.8289</v>
       </c>
       <c r="F16" t="n">
-        <v>2.39</v>
+        <v>1.8289</v>
       </c>
       <c r="G16" t="n">
-        <v>-0.3406</v>
+        <v>0</v>
       </c>
       <c r="H16" t="n">
-        <v>2.9912</v>
+        <v>1.8289</v>
       </c>
       <c r="I16" t="n">
-        <v>1.6152</v>
+        <v>1.8778</v>
       </c>
       <c r="J16" t="n">
-        <v>-0.3406</v>
+        <v>0</v>
       </c>
       <c r="K16" t="n">
-        <v>42</v>
+        <v>156</v>
       </c>
       <c r="L16" t="n">
-        <v>49</v>
+        <v>0</v>
       </c>
       <c r="M16" t="n">
-        <v>1.2746</v>
+        <v>1.8778</v>
       </c>
       <c r="N16" t="n">
-        <v>91</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17">
@@ -1186,31 +1186,31 @@
         </is>
       </c>
       <c r="B17" t="n">
-        <v>1.7534</v>
+        <v>1.6767</v>
       </c>
       <c r="C17" t="n">
-        <v>0.1543</v>
+        <v>0.1476</v>
       </c>
       <c r="D17" t="n">
-        <v>0.174</v>
+        <v>0.158</v>
       </c>
       <c r="E17" t="n">
-        <v>1.7534</v>
+        <v>1.6767</v>
       </c>
       <c r="F17" t="n">
-        <v>2.1911</v>
+        <v>2.144</v>
       </c>
       <c r="G17" t="n">
-        <v>-0.4377</v>
+        <v>-0.4673</v>
       </c>
       <c r="H17" t="n">
-        <v>2.3352</v>
+        <v>2.144</v>
       </c>
       <c r="I17" t="n">
-        <v>1.261</v>
+        <v>1.2038</v>
       </c>
       <c r="J17" t="n">
-        <v>-0.4377</v>
+        <v>-0.4673</v>
       </c>
       <c r="K17" t="n">
         <v>51</v>
@@ -1219,7 +1219,7 @@
         <v>75</v>
       </c>
       <c r="M17" t="n">
-        <v>0.8232999999999999</v>
+        <v>0.7364999999999999</v>
       </c>
       <c r="N17" t="n">
         <v>126</v>
@@ -1232,28 +1232,28 @@
         </is>
       </c>
       <c r="B18" t="n">
-        <v>1.3205</v>
+        <v>1.3795</v>
       </c>
       <c r="C18" t="n">
-        <v>0.1162</v>
+        <v>0.1214</v>
       </c>
       <c r="D18" t="n">
-        <v>-0.0231</v>
+        <v>0.0226</v>
       </c>
       <c r="E18" t="n">
-        <v>1.3205</v>
+        <v>1.3795</v>
       </c>
       <c r="F18" t="n">
-        <v>1.3205</v>
+        <v>1.3795</v>
       </c>
       <c r="G18" t="n">
         <v>0</v>
       </c>
       <c r="H18" t="n">
-        <v>1.3205</v>
+        <v>1.3795</v>
       </c>
       <c r="I18" t="n">
-        <v>1.3545</v>
+        <v>1.4164</v>
       </c>
       <c r="J18" t="n">
         <v>0</v>
@@ -1265,7 +1265,7 @@
         <v>0</v>
       </c>
       <c r="M18" t="n">
-        <v>1.3545</v>
+        <v>1.4164</v>
       </c>
       <c r="N18" t="n">
         <v>156</v>
@@ -1278,28 +1278,28 @@
         </is>
       </c>
       <c r="B19" t="n">
-        <v>1.1946</v>
+        <v>1.1598</v>
       </c>
       <c r="C19" t="n">
-        <v>0.1051</v>
+        <v>0.1021</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.0804</v>
+        <v>-0.0774</v>
       </c>
       <c r="E19" t="n">
-        <v>1.1946</v>
+        <v>1.1598</v>
       </c>
       <c r="F19" t="n">
-        <v>1.1946</v>
+        <v>1.1598</v>
       </c>
       <c r="G19" t="n">
         <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1.1946</v>
+        <v>1.1598</v>
       </c>
       <c r="I19" t="n">
-        <v>1.2254</v>
+        <v>1.1908</v>
       </c>
       <c r="J19" t="n">
         <v>0</v>
@@ -1311,7 +1311,7 @@
         <v>0</v>
       </c>
       <c r="M19" t="n">
-        <v>1.2254</v>
+        <v>1.1908</v>
       </c>
       <c r="N19" t="n">
         <v>153</v>
@@ -1324,31 +1324,31 @@
         </is>
       </c>
       <c r="B20" t="n">
-        <v>1.0882</v>
+        <v>1.0627</v>
       </c>
       <c r="C20" t="n">
-        <v>0.0958</v>
+        <v>0.0935</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.1288</v>
+        <v>-0.1217</v>
       </c>
       <c r="E20" t="n">
-        <v>1.0882</v>
+        <v>1.0627</v>
       </c>
       <c r="F20" t="n">
-        <v>0.3333</v>
+        <v>0.2875</v>
       </c>
       <c r="G20" t="n">
-        <v>0.7549</v>
+        <v>0.7752</v>
       </c>
       <c r="H20" t="n">
-        <v>0.3333</v>
+        <v>0.2875</v>
       </c>
       <c r="I20" t="n">
-        <v>0.18</v>
+        <v>0.1614</v>
       </c>
       <c r="J20" t="n">
-        <v>0.7549</v>
+        <v>0.7752</v>
       </c>
       <c r="K20" t="n">
         <v>132</v>
@@ -1357,7 +1357,7 @@
         <v>123</v>
       </c>
       <c r="M20" t="n">
-        <v>0.9349000000000001</v>
+        <v>0.9366</v>
       </c>
       <c r="N20" t="n">
         <v>255</v>
@@ -1366,32 +1366,32 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>GruBy</t>
+          <t>Furlan</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>1.0537</v>
+        <v>1.0068</v>
       </c>
       <c r="C21" t="n">
-        <v>0.0927</v>
+        <v>0.0886</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.1445</v>
+        <v>-0.1471</v>
       </c>
       <c r="E21" t="n">
-        <v>1.0537</v>
+        <v>1.0068</v>
       </c>
       <c r="F21" t="n">
-        <v>1.0537</v>
+        <v>1.0068</v>
       </c>
       <c r="G21" t="n">
         <v>0</v>
       </c>
       <c r="H21" t="n">
-        <v>1.0537</v>
+        <v>1.0068</v>
       </c>
       <c r="I21" t="n">
-        <v>1.0809</v>
+        <v>1.0337</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -1403,7 +1403,7 @@
         <v>0</v>
       </c>
       <c r="M21" t="n">
-        <v>1.0809</v>
+        <v>1.0337</v>
       </c>
       <c r="N21" t="n">
         <v>153</v>
@@ -1412,32 +1412,32 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Furlan</t>
+          <t>GruBy</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>1.0262</v>
+        <v>0.9948</v>
       </c>
       <c r="C22" t="n">
-        <v>0.09030000000000001</v>
+        <v>0.0876</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.1571</v>
+        <v>-0.1526</v>
       </c>
       <c r="E22" t="n">
-        <v>1.0262</v>
+        <v>0.9948</v>
       </c>
       <c r="F22" t="n">
-        <v>1.0262</v>
+        <v>0.9948</v>
       </c>
       <c r="G22" t="n">
         <v>0</v>
       </c>
       <c r="H22" t="n">
-        <v>1.0262</v>
+        <v>0.9948</v>
       </c>
       <c r="I22" t="n">
-        <v>1.0526</v>
+        <v>1.0214</v>
       </c>
       <c r="J22" t="n">
         <v>0</v>
@@ -1449,7 +1449,7 @@
         <v>0</v>
       </c>
       <c r="M22" t="n">
-        <v>1.0526</v>
+        <v>1.0214</v>
       </c>
       <c r="N22" t="n">
         <v>153</v>
@@ -1462,31 +1462,31 @@
         </is>
       </c>
       <c r="B23" t="n">
-        <v>0.6145</v>
+        <v>0.5679</v>
       </c>
       <c r="C23" t="n">
-        <v>0.0541</v>
+        <v>0.05</v>
       </c>
       <c r="D23" t="n">
-        <v>-0.3445</v>
+        <v>-0.3471</v>
       </c>
       <c r="E23" t="n">
-        <v>0.6145</v>
+        <v>0.5679</v>
       </c>
       <c r="F23" t="n">
-        <v>0.4189</v>
+        <v>0.4011</v>
       </c>
       <c r="G23" t="n">
-        <v>0.1956</v>
+        <v>0.1668</v>
       </c>
       <c r="H23" t="n">
-        <v>0.4189</v>
+        <v>0.4011</v>
       </c>
       <c r="I23" t="n">
-        <v>0.2262</v>
+        <v>0.2252</v>
       </c>
       <c r="J23" t="n">
-        <v>0.1956</v>
+        <v>0.1668</v>
       </c>
       <c r="K23" t="n">
         <v>132</v>
@@ -1495,7 +1495,7 @@
         <v>123</v>
       </c>
       <c r="M23" t="n">
-        <v>0.4218</v>
+        <v>0.392</v>
       </c>
       <c r="N23" t="n">
         <v>255</v>
@@ -1504,93 +1504,93 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>LUCAS1</t>
+          <t>byali</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>0.4642</v>
+        <v>0.4151</v>
       </c>
       <c r="C24" t="n">
-        <v>0.0409</v>
+        <v>0.0365</v>
       </c>
       <c r="D24" t="n">
-        <v>-0.4129</v>
+        <v>-0.4167</v>
       </c>
       <c r="E24" t="n">
-        <v>0.4642</v>
+        <v>0.4151</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.4151</v>
       </c>
       <c r="G24" t="n">
-        <v>-0.128</v>
+        <v>0</v>
       </c>
       <c r="H24" t="n">
-        <v>0.5921999999999999</v>
+        <v>0.4151</v>
       </c>
       <c r="I24" t="n">
-        <v>0.3198</v>
+        <v>0.4151</v>
       </c>
       <c r="J24" t="n">
-        <v>-0.128</v>
+        <v>0</v>
       </c>
       <c r="K24" t="n">
-        <v>132</v>
+        <v>66</v>
       </c>
       <c r="L24" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M24" t="n">
-        <v>0.1918</v>
+        <v>0.4151</v>
       </c>
       <c r="N24" t="n">
-        <v>255</v>
+        <v>66</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>byali</t>
+          <t>LUCAS1</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>0.3673</v>
+        <v>0.3487</v>
       </c>
       <c r="C25" t="n">
-        <v>0.0323</v>
+        <v>0.0307</v>
       </c>
       <c r="D25" t="n">
-        <v>-0.457</v>
+        <v>-0.4469</v>
       </c>
       <c r="E25" t="n">
-        <v>0.3673</v>
+        <v>0.3487</v>
       </c>
       <c r="F25" t="n">
-        <v>0.3673</v>
+        <v>0.4914</v>
       </c>
       <c r="G25" t="n">
-        <v>0</v>
+        <v>-0.1427</v>
       </c>
       <c r="H25" t="n">
-        <v>0.3673</v>
+        <v>0.4914</v>
       </c>
       <c r="I25" t="n">
-        <v>0.3673</v>
+        <v>0.2759</v>
       </c>
       <c r="J25" t="n">
-        <v>0</v>
+        <v>-0.1427</v>
       </c>
       <c r="K25" t="n">
-        <v>66</v>
+        <v>132</v>
       </c>
       <c r="L25" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M25" t="n">
-        <v>0.3673</v>
+        <v>0.1332</v>
       </c>
       <c r="N25" t="n">
-        <v>66</v>
+        <v>255</v>
       </c>
     </row>
     <row r="26">
@@ -1600,31 +1600,31 @@
         </is>
       </c>
       <c r="B26" t="n">
-        <v>0.3017</v>
+        <v>0.3437</v>
       </c>
       <c r="C26" t="n">
-        <v>0.0266</v>
+        <v>0.0303</v>
       </c>
       <c r="D26" t="n">
-        <v>-0.4869</v>
+        <v>-0.4492</v>
       </c>
       <c r="E26" t="n">
-        <v>0.3017</v>
+        <v>0.3437</v>
       </c>
       <c r="F26" t="n">
-        <v>1.1224</v>
+        <v>1.1534</v>
       </c>
       <c r="G26" t="n">
-        <v>-0.8207</v>
+        <v>-0.8097</v>
       </c>
       <c r="H26" t="n">
-        <v>1.1224</v>
+        <v>1.1534</v>
       </c>
       <c r="I26" t="n">
-        <v>0.6061</v>
+        <v>0.6476</v>
       </c>
       <c r="J26" t="n">
-        <v>-0.8207</v>
+        <v>-0.8097</v>
       </c>
       <c r="K26" t="n">
         <v>42</v>
@@ -1633,7 +1633,7 @@
         <v>49</v>
       </c>
       <c r="M26" t="n">
-        <v>-0.2146</v>
+        <v>-0.1621</v>
       </c>
       <c r="N26" t="n">
         <v>91</v>
@@ -1642,185 +1642,185 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>KILLDREAM</t>
+          <t>yel</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>0.2307</v>
+        <v>0.2734</v>
       </c>
       <c r="C27" t="n">
-        <v>0.0203</v>
+        <v>0.0241</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.5192</v>
+        <v>-0.4812</v>
       </c>
       <c r="E27" t="n">
-        <v>0.2307</v>
+        <v>0.2734</v>
       </c>
       <c r="F27" t="n">
-        <v>0.2307</v>
+        <v>0.4221</v>
       </c>
       <c r="G27" t="n">
-        <v>0</v>
+        <v>-0.1487</v>
       </c>
       <c r="H27" t="n">
-        <v>0.2307</v>
+        <v>0.4221</v>
       </c>
       <c r="I27" t="n">
-        <v>0.2307</v>
+        <v>0.237</v>
       </c>
       <c r="J27" t="n">
-        <v>0</v>
+        <v>-0.1487</v>
       </c>
       <c r="K27" t="n">
-        <v>72</v>
+        <v>132</v>
       </c>
       <c r="L27" t="n">
-        <v>0</v>
+        <v>123</v>
       </c>
       <c r="M27" t="n">
-        <v>0.2307</v>
+        <v>0.08829999999999999</v>
       </c>
       <c r="N27" t="n">
-        <v>72</v>
+        <v>255</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>yel</t>
+          <t>KILLDREAM</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>0.2278</v>
+        <v>0.1618</v>
       </c>
       <c r="C28" t="n">
-        <v>0.0201</v>
+        <v>0.0142</v>
       </c>
       <c r="D28" t="n">
-        <v>-0.5205</v>
+        <v>-0.5321</v>
       </c>
       <c r="E28" t="n">
-        <v>0.2278</v>
+        <v>0.1618</v>
       </c>
       <c r="F28" t="n">
-        <v>0.3906</v>
+        <v>0.1618</v>
       </c>
       <c r="G28" t="n">
-        <v>-0.1628</v>
+        <v>0</v>
       </c>
       <c r="H28" t="n">
-        <v>0.3906</v>
+        <v>0.1618</v>
       </c>
       <c r="I28" t="n">
-        <v>0.2109</v>
+        <v>0.1618</v>
       </c>
       <c r="J28" t="n">
-        <v>-0.1628</v>
+        <v>0</v>
       </c>
       <c r="K28" t="n">
-        <v>132</v>
+        <v>72</v>
       </c>
       <c r="L28" t="n">
-        <v>123</v>
+        <v>0</v>
       </c>
       <c r="M28" t="n">
-        <v>0.0481</v>
+        <v>0.1618</v>
       </c>
       <c r="N28" t="n">
-        <v>255</v>
+        <v>72</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>MODDII</t>
+          <t>Bubzkji</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>0.0208</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="C29" t="n">
-        <v>0.0018</v>
+        <v>0.0057</v>
       </c>
       <c r="D29" t="n">
-        <v>-0.6147</v>
+        <v>-0.5765</v>
       </c>
       <c r="E29" t="n">
-        <v>0.0208</v>
+        <v>0.06419999999999999</v>
       </c>
       <c r="F29" t="n">
-        <v>0.6219</v>
+        <v>0.3621</v>
       </c>
       <c r="G29" t="n">
-        <v>-0.6011</v>
+        <v>-0.2979</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6219</v>
+        <v>0.3621</v>
       </c>
       <c r="I29" t="n">
-        <v>0.3358</v>
+        <v>0.2033</v>
       </c>
       <c r="J29" t="n">
-        <v>-0.6011</v>
+        <v>-0.2979</v>
       </c>
       <c r="K29" t="n">
-        <v>51</v>
+        <v>42</v>
       </c>
       <c r="L29" t="n">
-        <v>75</v>
+        <v>49</v>
       </c>
       <c r="M29" t="n">
-        <v>-0.2653</v>
+        <v>-0.09459999999999999</v>
       </c>
       <c r="N29" t="n">
-        <v>126</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Bubzkji</t>
+          <t>MODDII</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="C30" t="n">
-        <v>0.0008</v>
+        <v>0.0005999999999999999</v>
       </c>
       <c r="D30" t="n">
-        <v>-0.6202</v>
+        <v>-0.6026</v>
       </c>
       <c r="E30" t="n">
-        <v>0.008800000000000001</v>
+        <v>0.0071</v>
       </c>
       <c r="F30" t="n">
-        <v>0.3422</v>
+        <v>0.6038</v>
       </c>
       <c r="G30" t="n">
-        <v>-0.3334</v>
+        <v>-0.5967</v>
       </c>
       <c r="H30" t="n">
-        <v>0.3422</v>
+        <v>0.6038</v>
       </c>
       <c r="I30" t="n">
-        <v>0.1848</v>
+        <v>0.339</v>
       </c>
       <c r="J30" t="n">
-        <v>-0.3334</v>
+        <v>-0.5967</v>
       </c>
       <c r="K30" t="n">
-        <v>42</v>
+        <v>51</v>
       </c>
       <c r="L30" t="n">
-        <v>49</v>
+        <v>75</v>
       </c>
       <c r="M30" t="n">
-        <v>-0.1486</v>
+        <v>-0.2577</v>
       </c>
       <c r="N30" t="n">
-        <v>91</v>
+        <v>126</v>
       </c>
     </row>
     <row r="31">
@@ -1830,28 +1830,28 @@
         </is>
       </c>
       <c r="B31" t="n">
-        <v>-0.29</v>
+        <v>-0.2817</v>
       </c>
       <c r="C31" t="n">
-        <v>-0.0255</v>
+        <v>-0.0248</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.7562</v>
+        <v>-0.7341</v>
       </c>
       <c r="E31" t="n">
-        <v>-0.29</v>
+        <v>-0.2817</v>
       </c>
       <c r="F31" t="n">
-        <v>-0.29</v>
+        <v>-0.2817</v>
       </c>
       <c r="G31" t="n">
         <v>0</v>
       </c>
       <c r="H31" t="n">
-        <v>-0.29</v>
+        <v>-0.2817</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.29</v>
+        <v>-0.2817</v>
       </c>
       <c r="J31" t="n">
         <v>0</v>
@@ -1863,7 +1863,7 @@
         <v>0</v>
       </c>
       <c r="M31" t="n">
-        <v>-0.29</v>
+        <v>-0.2817</v>
       </c>
       <c r="N31" t="n">
         <v>72</v>
@@ -1872,277 +1872,277 @@
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>arki</t>
+          <t>TOAO</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>-0.3602</v>
+        <v>-0.3288</v>
       </c>
       <c r="C32" t="n">
-        <v>-0.0317</v>
+        <v>-0.0289</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.7882</v>
+        <v>-0.7556</v>
       </c>
       <c r="E32" t="n">
-        <v>-0.3602</v>
+        <v>-0.3288</v>
       </c>
       <c r="F32" t="n">
-        <v>-0.3602</v>
+        <v>-0.3288</v>
       </c>
       <c r="G32" t="n">
         <v>0</v>
       </c>
       <c r="H32" t="n">
-        <v>-0.3602</v>
+        <v>-0.3288</v>
       </c>
       <c r="I32" t="n">
-        <v>-0.3602</v>
+        <v>-0.3376</v>
       </c>
       <c r="J32" t="n">
         <v>0</v>
       </c>
       <c r="K32" t="n">
-        <v>72</v>
+        <v>153</v>
       </c>
       <c r="L32" t="n">
         <v>0</v>
       </c>
       <c r="M32" t="n">
-        <v>-0.3602</v>
+        <v>-0.3376</v>
       </c>
       <c r="N32" t="n">
-        <v>72</v>
+        <v>153</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>TOAO</t>
+          <t>arki</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>-0.4422</v>
+        <v>-0.4252</v>
       </c>
       <c r="C33" t="n">
-        <v>-0.0389</v>
+        <v>-0.0374</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.8255</v>
+        <v>-0.7995</v>
       </c>
       <c r="E33" t="n">
-        <v>-0.4422</v>
+        <v>-0.4252</v>
       </c>
       <c r="F33" t="n">
-        <v>-0.4422</v>
+        <v>-0.4252</v>
       </c>
       <c r="G33" t="n">
         <v>0</v>
       </c>
       <c r="H33" t="n">
-        <v>-0.4422</v>
+        <v>-0.4252</v>
       </c>
       <c r="I33" t="n">
-        <v>-0.4536</v>
+        <v>-0.4252</v>
       </c>
       <c r="J33" t="n">
         <v>0</v>
       </c>
       <c r="K33" t="n">
-        <v>153</v>
+        <v>72</v>
       </c>
       <c r="L33" t="n">
         <v>0</v>
       </c>
       <c r="M33" t="n">
-        <v>-0.4536</v>
+        <v>-0.4252</v>
       </c>
       <c r="N33" t="n">
-        <v>153</v>
+        <v>72</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>MICHU</t>
+          <t>roman</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>-0.7361</v>
+        <v>-0.7965</v>
       </c>
       <c r="C34" t="n">
-        <v>-0.0648</v>
+        <v>-0.0701</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.9593</v>
+        <v>-0.9686</v>
       </c>
       <c r="E34" t="n">
-        <v>-0.7361</v>
+        <v>-0.7965</v>
       </c>
       <c r="F34" t="n">
-        <v>-0.7361</v>
+        <v>-0.7965</v>
       </c>
       <c r="G34" t="n">
         <v>0</v>
       </c>
       <c r="H34" t="n">
-        <v>-0.7361</v>
+        <v>-0.7965</v>
       </c>
       <c r="I34" t="n">
-        <v>-0.7361</v>
+        <v>-0.7965</v>
       </c>
       <c r="J34" t="n">
         <v>0</v>
       </c>
       <c r="K34" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L34" t="n">
         <v>0</v>
       </c>
       <c r="M34" t="n">
-        <v>-0.7361</v>
+        <v>-0.7965</v>
       </c>
       <c r="N34" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>alex</t>
+          <t>MICHU</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="C35" t="n">
-        <v>-0.0737</v>
+        <v>-0.0723</v>
       </c>
       <c r="D35" t="n">
-        <v>-1.0053</v>
+        <v>-0.9802</v>
       </c>
       <c r="E35" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="F35" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="G35" t="n">
         <v>0</v>
       </c>
       <c r="H35" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="I35" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="J35" t="n">
         <v>0</v>
       </c>
       <c r="K35" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L35" t="n">
         <v>0</v>
       </c>
       <c r="M35" t="n">
-        <v>-0.8372000000000001</v>
+        <v>-0.8218</v>
       </c>
       <c r="N35" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>roman</t>
+          <t>NEO</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>-0.8425</v>
+        <v>-0.8457</v>
       </c>
       <c r="C36" t="n">
-        <v>-0.0742</v>
+        <v>-0.07439999999999999</v>
       </c>
       <c r="D36" t="n">
-        <v>-1.0077</v>
+        <v>-0.991</v>
       </c>
       <c r="E36" t="n">
-        <v>-0.8425</v>
+        <v>-0.8457</v>
       </c>
       <c r="F36" t="n">
-        <v>-0.8425</v>
+        <v>-0.8457</v>
       </c>
       <c r="G36" t="n">
         <v>0</v>
       </c>
       <c r="H36" t="n">
-        <v>-0.8425</v>
+        <v>-0.8457</v>
       </c>
       <c r="I36" t="n">
-        <v>-0.8425</v>
+        <v>-0.8457</v>
       </c>
       <c r="J36" t="n">
         <v>0</v>
       </c>
       <c r="K36" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="L36" t="n">
         <v>0</v>
       </c>
       <c r="M36" t="n">
-        <v>-0.8425</v>
+        <v>-0.8457</v>
       </c>
       <c r="N36" t="n">
-        <v>72</v>
+        <v>66</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>NEO</t>
+          <t>alex</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="C37" t="n">
-        <v>-0.07580000000000001</v>
+        <v>-0.0794</v>
       </c>
       <c r="D37" t="n">
-        <v>-1.0163</v>
+        <v>-1.0166</v>
       </c>
       <c r="E37" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="F37" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="G37" t="n">
         <v>0</v>
       </c>
       <c r="H37" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="J37" t="n">
         <v>0</v>
       </c>
       <c r="K37" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
       <c r="L37" t="n">
         <v>0</v>
       </c>
       <c r="M37" t="n">
-        <v>-0.8614000000000001</v>
+        <v>-0.9016999999999999</v>
       </c>
       <c r="N37" t="n">
-        <v>66</v>
+        <v>72</v>
       </c>
     </row>
     <row r="38">
@@ -2152,28 +2152,28 @@
         </is>
       </c>
       <c r="B38" t="n">
-        <v>-1.0229</v>
+        <v>-1.0077</v>
       </c>
       <c r="C38" t="n">
-        <v>-0.09</v>
+        <v>-0.0887</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.0898</v>
+        <v>-1.0648</v>
       </c>
       <c r="E38" t="n">
-        <v>-1.0229</v>
+        <v>-1.0077</v>
       </c>
       <c r="F38" t="n">
-        <v>-1.0229</v>
+        <v>-1.0077</v>
       </c>
       <c r="G38" t="n">
         <v>0</v>
       </c>
       <c r="H38" t="n">
-        <v>-1.0229</v>
+        <v>-1.0077</v>
       </c>
       <c r="I38" t="n">
-        <v>-1.0229</v>
+        <v>-1.0077</v>
       </c>
       <c r="J38" t="n">
         <v>0</v>
@@ -2185,7 +2185,7 @@
         <v>0</v>
       </c>
       <c r="M38" t="n">
-        <v>-1.0229</v>
+        <v>-1.0077</v>
       </c>
       <c r="N38" t="n">
         <v>66</v>
@@ -2198,28 +2198,28 @@
         </is>
       </c>
       <c r="B39" t="n">
-        <v>-1.1154</v>
+        <v>-1.1122</v>
       </c>
       <c r="C39" t="n">
-        <v>-0.0982</v>
+        <v>-0.0979</v>
       </c>
       <c r="D39" t="n">
-        <v>-1.132</v>
+        <v>-1.1124</v>
       </c>
       <c r="E39" t="n">
-        <v>-1.1154</v>
+        <v>-1.1122</v>
       </c>
       <c r="F39" t="n">
-        <v>-1.1154</v>
+        <v>-1.1122</v>
       </c>
       <c r="G39" t="n">
         <v>0</v>
       </c>
       <c r="H39" t="n">
-        <v>-1.1154</v>
+        <v>-1.1122</v>
       </c>
       <c r="I39" t="n">
-        <v>-1.1441</v>
+        <v>-1.142</v>
       </c>
       <c r="J39" t="n">
         <v>0</v>
@@ -2231,7 +2231,7 @@
         <v>0</v>
       </c>
       <c r="M39" t="n">
-        <v>-1.1441</v>
+        <v>-1.142</v>
       </c>
       <c r="N39" t="n">
         <v>156</v>
@@ -2244,28 +2244,28 @@
         </is>
       </c>
       <c r="B40" t="n">
-        <v>-1.4452</v>
+        <v>-1.4501</v>
       </c>
       <c r="C40" t="n">
-        <v>-0.1272</v>
+        <v>-0.1276</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.2821</v>
+        <v>-1.2664</v>
       </c>
       <c r="E40" t="n">
-        <v>-1.4452</v>
+        <v>-1.4501</v>
       </c>
       <c r="F40" t="n">
-        <v>-1.4452</v>
+        <v>-1.4501</v>
       </c>
       <c r="G40" t="n">
         <v>0</v>
       </c>
       <c r="H40" t="n">
-        <v>-1.4452</v>
+        <v>-1.4501</v>
       </c>
       <c r="I40" t="n">
-        <v>-1.4452</v>
+        <v>-1.4501</v>
       </c>
       <c r="J40" t="n">
         <v>0</v>
@@ -2277,7 +2277,7 @@
         <v>0</v>
       </c>
       <c r="M40" t="n">
-        <v>-1.4452</v>
+        <v>-1.4501</v>
       </c>
       <c r="N40" t="n">
         <v>66</v>
@@ -2290,31 +2290,31 @@
         </is>
       </c>
       <c r="B41" t="n">
-        <v>-2.3257</v>
+        <v>-2.1284</v>
       </c>
       <c r="C41" t="n">
-        <v>-0.2047</v>
+        <v>-0.1873</v>
       </c>
       <c r="D41" t="n">
-        <v>-1.6829</v>
+        <v>-1.5754</v>
       </c>
       <c r="E41" t="n">
-        <v>-2.3257</v>
+        <v>-2.1284</v>
       </c>
       <c r="F41" t="n">
-        <v>-2.568</v>
+        <v>-2.3848</v>
       </c>
       <c r="G41" t="n">
-        <v>0.2423</v>
+        <v>0.2564</v>
       </c>
       <c r="H41" t="n">
-        <v>-2.568</v>
+        <v>-2.3848</v>
       </c>
       <c r="I41" t="n">
-        <v>-1.3867</v>
+        <v>-1.339</v>
       </c>
       <c r="J41" t="n">
-        <v>0.2423</v>
+        <v>0.2564</v>
       </c>
       <c r="K41" t="n">
         <v>130</v>
@@ -2323,7 +2323,7 @@
         <v>97</v>
       </c>
       <c r="M41" t="n">
-        <v>-1.1444</v>
+        <v>-1.0826</v>
       </c>
       <c r="N41" t="n">
         <v>227</v>
@@ -2429,10 +2429,10 @@
         <v>2.04</v>
       </c>
       <c r="I2" t="n">
-        <v>1.8453</v>
+        <v>1.903</v>
       </c>
       <c r="J2" t="n">
-        <v>42.4419</v>
+        <v>43.769</v>
       </c>
     </row>
     <row r="3">
@@ -2469,10 +2469,10 @@
         <v>1.7</v>
       </c>
       <c r="I3" t="n">
-        <v>1.4217</v>
+        <v>1.4594</v>
       </c>
       <c r="J3" t="n">
-        <v>32.6991</v>
+        <v>33.5662</v>
       </c>
     </row>
     <row r="4">
@@ -2509,10 +2509,10 @@
         <v>1.25</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6129</v>
+        <v>0.5893</v>
       </c>
       <c r="J4" t="n">
-        <v>14.0967</v>
+        <v>13.5539</v>
       </c>
     </row>
     <row r="5">
@@ -2549,10 +2549,10 @@
         <v>1.22</v>
       </c>
       <c r="I5" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5221</v>
       </c>
       <c r="J5" t="n">
-        <v>12.6247</v>
+        <v>12.0083</v>
       </c>
     </row>
     <row r="6">
@@ -2589,10 +2589,10 @@
         <v>1.22</v>
       </c>
       <c r="I6" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.5221</v>
       </c>
       <c r="J6" t="n">
-        <v>12.6247</v>
+        <v>12.0083</v>
       </c>
     </row>
     <row r="7">
@@ -2629,10 +2629,10 @@
         <v>0.97</v>
       </c>
       <c r="I7" t="n">
-        <v>0.0064</v>
+        <v>0.0363</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1472</v>
+        <v>0.8349</v>
       </c>
     </row>
     <row r="8">
@@ -2669,10 +2669,10 @@
         <v>0.88</v>
       </c>
       <c r="I8" t="n">
-        <v>-0.1193</v>
+        <v>-0.1003</v>
       </c>
       <c r="J8" t="n">
-        <v>-2.7439</v>
+        <v>-2.3069</v>
       </c>
     </row>
     <row r="9">
@@ -2709,10 +2709,10 @@
         <v>0.5</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.4857</v>
+        <v>-0.4823</v>
       </c>
       <c r="J9" t="n">
-        <v>-11.1711</v>
+        <v>-11.0929</v>
       </c>
     </row>
     <row r="10">
@@ -2749,10 +2749,10 @@
         <v>0.42</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.556</v>
+        <v>-0.5611</v>
       </c>
       <c r="J10" t="n">
-        <v>-12.788</v>
+        <v>-12.9053</v>
       </c>
     </row>
     <row r="11">
@@ -2789,10 +2789,10 @@
         <v>0.42</v>
       </c>
       <c r="I11" t="n">
-        <v>-0.556</v>
+        <v>-0.5611</v>
       </c>
       <c r="J11" t="n">
-        <v>-12.788</v>
+        <v>-12.9053</v>
       </c>
     </row>
     <row r="12">
@@ -2829,10 +2829,10 @@
         <v>1.76</v>
       </c>
       <c r="I12" t="n">
-        <v>1.5841</v>
+        <v>1.6151</v>
       </c>
       <c r="J12" t="n">
-        <v>39.6025</v>
+        <v>40.3775</v>
       </c>
     </row>
     <row r="13">
@@ -2869,10 +2869,10 @@
         <v>1.26</v>
       </c>
       <c r="I13" t="n">
-        <v>0.6705</v>
+        <v>0.6397</v>
       </c>
       <c r="J13" t="n">
-        <v>16.7625</v>
+        <v>15.9925</v>
       </c>
     </row>
     <row r="14">
@@ -2909,10 +2909,10 @@
         <v>1.12</v>
       </c>
       <c r="I14" t="n">
-        <v>0.3605</v>
+        <v>0.3268</v>
       </c>
       <c r="J14" t="n">
-        <v>9.012499999999999</v>
+        <v>8.17</v>
       </c>
     </row>
     <row r="15">
@@ -2949,10 +2949,10 @@
         <v>0.96</v>
       </c>
       <c r="I15" t="n">
-        <v>-0.2061</v>
+        <v>-0.1718</v>
       </c>
       <c r="J15" t="n">
-        <v>-5.1525</v>
+        <v>-4.295</v>
       </c>
     </row>
     <row r="16">
@@ -2989,10 +2989,10 @@
         <v>0.92</v>
       </c>
       <c r="I16" t="n">
-        <v>-0.3262</v>
+        <v>-0.2861</v>
       </c>
       <c r="J16" t="n">
-        <v>-8.154999999999999</v>
+        <v>-7.1525</v>
       </c>
     </row>
     <row r="17">
@@ -3029,10 +3029,10 @@
         <v>1.05</v>
       </c>
       <c r="I17" t="n">
-        <v>0.1595</v>
+        <v>0.123</v>
       </c>
       <c r="J17" t="n">
-        <v>3.9875</v>
+        <v>3.075</v>
       </c>
     </row>
     <row r="18">
@@ -3069,10 +3069,10 @@
         <v>0.99</v>
       </c>
       <c r="I18" t="n">
-        <v>-0.0208</v>
+        <v>-0.0155</v>
       </c>
       <c r="J18" t="n">
-        <v>-0.52</v>
+        <v>-0.3875</v>
       </c>
     </row>
     <row r="19">
@@ -3109,10 +3109,10 @@
         <v>0.97</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.0542</v>
+        <v>-0.0435</v>
       </c>
       <c r="J19" t="n">
-        <v>-1.355</v>
+        <v>-1.0875</v>
       </c>
     </row>
     <row r="20">
@@ -3149,10 +3149,10 @@
         <v>0.89</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.1526</v>
+        <v>-0.1336</v>
       </c>
       <c r="J20" t="n">
-        <v>-3.815</v>
+        <v>-3.34</v>
       </c>
     </row>
     <row r="21">
@@ -3189,10 +3189,10 @@
         <v>0.77</v>
       </c>
       <c r="I21" t="n">
-        <v>-0.2756</v>
+        <v>-0.2564</v>
       </c>
       <c r="J21" t="n">
-        <v>-6.89</v>
+        <v>-6.41</v>
       </c>
     </row>
     <row r="22">
@@ -3229,10 +3229,10 @@
         <v>1.12</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3175</v>
+        <v>0.2669</v>
       </c>
       <c r="J22" t="n">
-        <v>11.1125</v>
+        <v>9.3415</v>
       </c>
     </row>
     <row r="23">
@@ -3269,10 +3269,10 @@
         <v>1.04</v>
       </c>
       <c r="I23" t="n">
-        <v>0.1456</v>
+        <v>0.1116</v>
       </c>
       <c r="J23" t="n">
-        <v>5.096</v>
+        <v>3.906</v>
       </c>
     </row>
     <row r="24">
@@ -3309,10 +3309,10 @@
         <v>0.85</v>
       </c>
       <c r="I24" t="n">
-        <v>-0.1916</v>
+        <v>-0.1723</v>
       </c>
       <c r="J24" t="n">
-        <v>-6.706</v>
+        <v>-6.0305</v>
       </c>
     </row>
     <row r="25">
@@ -3349,10 +3349,10 @@
         <v>0.74</v>
       </c>
       <c r="I25" t="n">
-        <v>-0.2998</v>
+        <v>-0.2818</v>
       </c>
       <c r="J25" t="n">
-        <v>-10.493</v>
+        <v>-9.863</v>
       </c>
     </row>
     <row r="26">
@@ -3389,10 +3389,10 @@
         <v>0.7</v>
       </c>
       <c r="I26" t="n">
-        <v>-0.3372</v>
+        <v>-0.3211</v>
       </c>
       <c r="J26" t="n">
-        <v>-11.802</v>
+        <v>-11.2385</v>
       </c>
     </row>
     <row r="27">
@@ -3429,10 +3429,10 @@
         <v>1.37</v>
       </c>
       <c r="I27" t="n">
-        <v>0.7844</v>
+        <v>0.7683</v>
       </c>
       <c r="J27" t="n">
-        <v>27.454</v>
+        <v>26.8905</v>
       </c>
     </row>
     <row r="28">
@@ -3469,10 +3469,10 @@
         <v>1.32</v>
       </c>
       <c r="I28" t="n">
-        <v>0.7102000000000001</v>
+        <v>0.695</v>
       </c>
       <c r="J28" t="n">
-        <v>24.857</v>
+        <v>24.325</v>
       </c>
     </row>
     <row r="29">
@@ -3509,10 +3509,10 @@
         <v>1.15</v>
       </c>
       <c r="I29" t="n">
-        <v>0.4369</v>
+        <v>0.4025</v>
       </c>
       <c r="J29" t="n">
-        <v>15.2915</v>
+        <v>14.0875</v>
       </c>
     </row>
     <row r="30">
@@ -3549,10 +3549,10 @@
         <v>0.99</v>
       </c>
       <c r="I30" t="n">
-        <v>-0.0834</v>
+        <v>-0.0626</v>
       </c>
       <c r="J30" t="n">
-        <v>-2.919</v>
+        <v>-2.191</v>
       </c>
     </row>
     <row r="31">
@@ -3589,10 +3589,10 @@
         <v>0.89</v>
       </c>
       <c r="I31" t="n">
-        <v>-0.3964</v>
+        <v>-0.3542</v>
       </c>
       <c r="J31" t="n">
-        <v>-13.874</v>
+        <v>-12.397</v>
       </c>
     </row>
     <row r="32">
@@ -3629,10 +3629,10 @@
         <v>2.19</v>
       </c>
       <c r="I32" t="n">
-        <v>1.0089</v>
+        <v>0.9493</v>
       </c>
       <c r="J32" t="n">
-        <v>19.1691</v>
+        <v>18.0367</v>
       </c>
     </row>
     <row r="33">
@@ -3669,10 +3669,10 @@
         <v>1.52</v>
       </c>
       <c r="I33" t="n">
-        <v>0.5687</v>
+        <v>0.5363</v>
       </c>
       <c r="J33" t="n">
-        <v>10.8053</v>
+        <v>10.1897</v>
       </c>
     </row>
     <row r="34">
@@ -3709,10 +3709,10 @@
         <v>1.33</v>
       </c>
       <c r="I34" t="n">
-        <v>0.4247</v>
+        <v>0.3682</v>
       </c>
       <c r="J34" t="n">
-        <v>8.0693</v>
+        <v>6.9958</v>
       </c>
     </row>
     <row r="35">
@@ -3749,10 +3749,10 @@
         <v>1.26</v>
       </c>
       <c r="I35" t="n">
-        <v>0.3488</v>
+        <v>0.296</v>
       </c>
       <c r="J35" t="n">
-        <v>6.6272</v>
+        <v>5.624</v>
       </c>
     </row>
     <row r="36">
@@ -3789,10 +3789,10 @@
         <v>1.06</v>
       </c>
       <c r="I36" t="n">
-        <v>0.08599999999999999</v>
+        <v>0.0609</v>
       </c>
       <c r="J36" t="n">
-        <v>1.634</v>
+        <v>1.1571</v>
       </c>
     </row>
     <row r="37">
@@ -3829,10 +3829,10 @@
         <v>0.91</v>
       </c>
       <c r="I37" t="n">
-        <v>-0.07870000000000001</v>
+        <v>-0.0579</v>
       </c>
       <c r="J37" t="n">
-        <v>-1.4953</v>
+        <v>-1.1001</v>
       </c>
     </row>
     <row r="38">
@@ -3869,10 +3869,10 @@
         <v>0.65</v>
       </c>
       <c r="I38" t="n">
-        <v>-0.3544</v>
+        <v>-0.3443</v>
       </c>
       <c r="J38" t="n">
-        <v>-6.7336</v>
+        <v>-6.5417</v>
       </c>
     </row>
     <row r="39">
@@ -3909,10 +3909,10 @@
         <v>0.61</v>
       </c>
       <c r="I39" t="n">
-        <v>-0.3881</v>
+        <v>-0.3787</v>
       </c>
       <c r="J39" t="n">
-        <v>-7.3739</v>
+        <v>-7.1953</v>
       </c>
     </row>
     <row r="40">
@@ -3949,10 +3949,10 @@
         <v>0.5600000000000001</v>
       </c>
       <c r="I40" t="n">
-        <v>-0.4315</v>
+        <v>-0.4239</v>
       </c>
       <c r="J40" t="n">
-        <v>-8.198499999999999</v>
+        <v>-8.0541</v>
       </c>
     </row>
     <row r="41">
@@ -3989,10 +3989,10 @@
         <v>0.41</v>
       </c>
       <c r="I41" t="n">
-        <v>-0.5634</v>
+        <v>-0.5695</v>
       </c>
       <c r="J41" t="n">
-        <v>-10.7046</v>
+        <v>-10.8205</v>
       </c>
     </row>
     <row r="42">
@@ -4029,10 +4029,10 @@
         <v>0.93</v>
       </c>
       <c r="I42" t="n">
-        <v>-0.07140000000000001</v>
+        <v>-0.0554</v>
       </c>
       <c r="J42" t="n">
-        <v>-1.4994</v>
+        <v>-1.1634</v>
       </c>
     </row>
     <row r="43">
@@ -4069,10 +4069,10 @@
         <v>0.73</v>
       </c>
       <c r="I43" t="n">
-        <v>-0.2901</v>
+        <v>-0.2763</v>
       </c>
       <c r="J43" t="n">
-        <v>-6.0921</v>
+        <v>-5.8023</v>
       </c>
     </row>
     <row r="44">
@@ -4109,10 +4109,10 @@
         <v>0.64</v>
       </c>
       <c r="I44" t="n">
-        <v>-0.3696</v>
+        <v>-0.3573</v>
       </c>
       <c r="J44" t="n">
-        <v>-7.7616</v>
+        <v>-7.5033</v>
       </c>
     </row>
     <row r="45">
@@ -4149,10 +4149,10 @@
         <v>0.62</v>
       </c>
       <c r="I45" t="n">
-        <v>-0.3873</v>
+        <v>-0.3758</v>
       </c>
       <c r="J45" t="n">
-        <v>-8.1333</v>
+        <v>-7.8918</v>
       </c>
     </row>
     <row r="46">
@@ -4189,10 +4189,10 @@
         <v>0.55</v>
       </c>
       <c r="I46" t="n">
-        <v>-0.4493</v>
+        <v>-0.4422</v>
       </c>
       <c r="J46" t="n">
-        <v>-9.4353</v>
+        <v>-9.286199999999999</v>
       </c>
     </row>
     <row r="47">
@@ -4229,10 +4229,10 @@
         <v>1.96</v>
       </c>
       <c r="I47" t="n">
-        <v>1.4928</v>
+        <v>1.5104</v>
       </c>
       <c r="J47" t="n">
-        <v>31.3488</v>
+        <v>31.7184</v>
       </c>
     </row>
     <row r="48">
@@ -4269,10 +4269,10 @@
         <v>1.34</v>
       </c>
       <c r="I48" t="n">
-        <v>0.7088</v>
+        <v>0.7015</v>
       </c>
       <c r="J48" t="n">
-        <v>14.8848</v>
+        <v>14.7315</v>
       </c>
     </row>
     <row r="49">
@@ -4309,10 +4309,10 @@
         <v>1.32</v>
       </c>
       <c r="I49" t="n">
-        <v>0.6801</v>
+        <v>0.6737</v>
       </c>
       <c r="J49" t="n">
-        <v>14.2821</v>
+        <v>14.1477</v>
       </c>
     </row>
     <row r="50">
@@ -4349,10 +4349,10 @@
         <v>1.28</v>
       </c>
       <c r="I50" t="n">
-        <v>0.6211</v>
+        <v>0.6166</v>
       </c>
       <c r="J50" t="n">
-        <v>13.0431</v>
+        <v>12.9486</v>
       </c>
     </row>
     <row r="51">
@@ -4389,10 +4389,10 @@
         <v>1.16</v>
       </c>
       <c r="I51" t="n">
-        <v>0.4234</v>
+        <v>0.3935</v>
       </c>
       <c r="J51" t="n">
-        <v>8.891400000000001</v>
+        <v>8.263500000000001</v>
       </c>
     </row>
     <row r="52">
@@ -4429,10 +4429,10 @@
         <v>1.12</v>
       </c>
       <c r="I52" t="n">
-        <v>0.3637</v>
+        <v>0.3202</v>
       </c>
       <c r="J52" t="n">
-        <v>8.3651</v>
+        <v>7.3646</v>
       </c>
     </row>
     <row r="53">
@@ -4469,10 +4469,10 @@
         <v>0.9</v>
       </c>
       <c r="I53" t="n">
-        <v>-0.124</v>
+        <v>-0.1091</v>
       </c>
       <c r="J53" t="n">
-        <v>-2.852</v>
+        <v>-2.5093</v>
       </c>
     </row>
     <row r="54">
@@ -4509,10 +4509,10 @@
         <v>0.76</v>
       </c>
       <c r="I54" t="n">
-        <v>-0.2689</v>
+        <v>-0.2525</v>
       </c>
       <c r="J54" t="n">
-        <v>-6.1847</v>
+        <v>-5.8075</v>
       </c>
     </row>
     <row r="55">
@@ -4549,10 +4549,10 @@
         <v>0.63</v>
       </c>
       <c r="I55" t="n">
-        <v>-0.3872</v>
+        <v>-0.3748</v>
       </c>
       <c r="J55" t="n">
-        <v>-8.9056</v>
+        <v>-8.6204</v>
       </c>
     </row>
     <row r="56">
@@ -4589,10 +4589,10 @@
         <v>0.42</v>
       </c>
       <c r="I56" t="n">
-        <v>-0.5709</v>
+        <v>-0.5798</v>
       </c>
       <c r="J56" t="n">
-        <v>-13.1307</v>
+        <v>-13.3354</v>
       </c>
     </row>
     <row r="57">
@@ -4629,10 +4629,10 @@
         <v>2.02</v>
       </c>
       <c r="I57" t="n">
-        <v>1.5612</v>
+        <v>1.5852</v>
       </c>
       <c r="J57" t="n">
-        <v>35.9076</v>
+        <v>36.4596</v>
       </c>
     </row>
     <row r="58">
@@ -4669,10 +4669,10 @@
         <v>1.86</v>
       </c>
       <c r="I58" t="n">
-        <v>1.3713</v>
+        <v>1.3786</v>
       </c>
       <c r="J58" t="n">
-        <v>31.5399</v>
+        <v>31.7078</v>
       </c>
     </row>
     <row r="59">
@@ -4709,10 +4709,10 @@
         <v>1.26</v>
       </c>
       <c r="I59" t="n">
-        <v>0.5897</v>
+        <v>0.5865</v>
       </c>
       <c r="J59" t="n">
-        <v>13.5631</v>
+        <v>13.4895</v>
       </c>
     </row>
     <row r="60">
@@ -4749,10 +4749,10 @@
         <v>1.07</v>
       </c>
       <c r="I60" t="n">
-        <v>0.1931</v>
+        <v>0.1624</v>
       </c>
       <c r="J60" t="n">
-        <v>4.4413</v>
+        <v>3.7352</v>
       </c>
     </row>
     <row r="61">
@@ -4789,10 +4789,10 @@
         <v>0.9</v>
       </c>
       <c r="I61" t="n">
-        <v>-0.4147</v>
+        <v>-0.3804</v>
       </c>
       <c r="J61" t="n">
-        <v>-9.5381</v>
+        <v>-8.7492</v>
       </c>
     </row>
     <row r="62">
@@ -4829,10 +4829,10 @@
         <v>1.21</v>
       </c>
       <c r="I62" t="n">
-        <v>0.4518</v>
+        <v>0.3998</v>
       </c>
       <c r="J62" t="n">
-        <v>11.7468</v>
+        <v>10.3948</v>
       </c>
     </row>
     <row r="63">
@@ -4869,10 +4869,10 @@
         <v>1.01</v>
       </c>
       <c r="I63" t="n">
-        <v>0.0466</v>
+        <v>0.0312</v>
       </c>
       <c r="J63" t="n">
-        <v>1.2116</v>
+        <v>0.8112</v>
       </c>
     </row>
     <row r="64">
@@ -4909,10 +4909,10 @@
         <v>1</v>
       </c>
       <c r="I64" t="n">
-        <v>0.0027</v>
+        <v>0.0013</v>
       </c>
       <c r="J64" t="n">
-        <v>0.0702</v>
+        <v>0.0338</v>
       </c>
     </row>
     <row r="65">
@@ -4949,10 +4949,10 @@
         <v>0.84</v>
       </c>
       <c r="I65" t="n">
-        <v>-0.2094</v>
+        <v>-0.1888</v>
       </c>
       <c r="J65" t="n">
-        <v>-5.4444</v>
+        <v>-4.9088</v>
       </c>
     </row>
     <row r="66">
@@ -4989,10 +4989,10 @@
         <v>0.8</v>
       </c>
       <c r="I66" t="n">
-        <v>-0.2498</v>
+        <v>-0.2299</v>
       </c>
       <c r="J66" t="n">
-        <v>-6.4948</v>
+        <v>-5.9774</v>
       </c>
     </row>
     <row r="67">
@@ -5029,10 +5029,10 @@
         <v>1.34</v>
       </c>
       <c r="I67" t="n">
-        <v>0.7417</v>
+        <v>0.7259</v>
       </c>
       <c r="J67" t="n">
-        <v>19.2842</v>
+        <v>18.8734</v>
       </c>
     </row>
     <row r="68">
@@ -5069,10 +5069,10 @@
         <v>1.2</v>
       </c>
       <c r="I68" t="n">
-        <v>0.5238</v>
+        <v>0.5123</v>
       </c>
       <c r="J68" t="n">
-        <v>13.6188</v>
+        <v>13.3198</v>
       </c>
     </row>
     <row r="69">
@@ -5109,10 +5109,10 @@
         <v>1.16</v>
       </c>
       <c r="I69" t="n">
-        <v>0.4566</v>
+        <v>0.4258</v>
       </c>
       <c r="J69" t="n">
-        <v>11.8716</v>
+        <v>11.0708</v>
       </c>
     </row>
     <row r="70">
@@ -5149,10 +5149,10 @@
         <v>1.12</v>
       </c>
       <c r="I70" t="n">
-        <v>0.3703</v>
+        <v>0.3336</v>
       </c>
       <c r="J70" t="n">
-        <v>9.627800000000001</v>
+        <v>8.6736</v>
       </c>
     </row>
     <row r="71">
@@ -5189,10 +5189,10 @@
         <v>0.86</v>
       </c>
       <c r="I71" t="n">
-        <v>-0.4712</v>
+        <v>-0.4296</v>
       </c>
       <c r="J71" t="n">
-        <v>-12.2512</v>
+        <v>-11.1696</v>
       </c>
     </row>
     <row r="72">
@@ -5229,10 +5229,10 @@
         <v>1.31</v>
       </c>
       <c r="I72" t="n">
-        <v>0.8066</v>
+        <v>0.7805</v>
       </c>
       <c r="J72" t="n">
-        <v>24.198</v>
+        <v>23.415</v>
       </c>
     </row>
     <row r="73">
@@ -5269,10 +5269,10 @@
         <v>1.12</v>
       </c>
       <c r="I73" t="n">
-        <v>0.3789</v>
+        <v>0.3385</v>
       </c>
       <c r="J73" t="n">
-        <v>11.367</v>
+        <v>10.155</v>
       </c>
     </row>
     <row r="74">
@@ -5309,10 +5309,10 @@
         <v>1.07</v>
       </c>
       <c r="I74" t="n">
-        <v>0.2483</v>
+        <v>0.2135</v>
       </c>
       <c r="J74" t="n">
-        <v>7.449</v>
+        <v>6.405</v>
       </c>
     </row>
     <row r="75">
@@ -5349,10 +5349,10 @@
         <v>1.02</v>
       </c>
       <c r="I75" t="n">
-        <v>0.0906</v>
+        <v>0.07149999999999999</v>
       </c>
       <c r="J75" t="n">
-        <v>2.718</v>
+        <v>2.145</v>
       </c>
     </row>
     <row r="76">
@@ -5389,10 +5389,10 @@
         <v>0.82</v>
       </c>
       <c r="I76" t="n">
-        <v>-0.5547</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="J76" t="n">
-        <v>-16.641</v>
+        <v>-15.438</v>
       </c>
     </row>
     <row r="77">
@@ -5429,10 +5429,10 @@
         <v>1.4</v>
       </c>
       <c r="I77" t="n">
-        <v>0.7243000000000001</v>
+        <v>0.6666</v>
       </c>
       <c r="J77" t="n">
-        <v>21.729</v>
+        <v>19.998</v>
       </c>
     </row>
     <row r="78">
@@ -5469,10 +5469,10 @@
         <v>1.21</v>
       </c>
       <c r="I78" t="n">
-        <v>0.4316</v>
+        <v>0.375</v>
       </c>
       <c r="J78" t="n">
-        <v>12.948</v>
+        <v>11.25</v>
       </c>
     </row>
     <row r="79">
@@ -5509,10 +5509,10 @@
         <v>1.13</v>
       </c>
       <c r="I79" t="n">
-        <v>0.2947</v>
+        <v>0.2468</v>
       </c>
       <c r="J79" t="n">
-        <v>8.840999999999999</v>
+        <v>7.404</v>
       </c>
     </row>
     <row r="80">
@@ -5549,10 +5549,10 @@
         <v>0.95</v>
       </c>
       <c r="I80" t="n">
-        <v>-0.0936</v>
+        <v>-0.07679999999999999</v>
       </c>
       <c r="J80" t="n">
-        <v>-2.808</v>
+        <v>-2.304</v>
       </c>
     </row>
     <row r="81">
@@ -5589,10 +5589,10 @@
         <v>0.78</v>
       </c>
       <c r="I81" t="n">
-        <v>-0.2802</v>
+        <v>-0.2619</v>
       </c>
       <c r="J81" t="n">
-        <v>-8.406000000000001</v>
+        <v>-7.857</v>
       </c>
     </row>
     <row r="82">
@@ -5629,10 +5629,10 @@
         <v>1.15</v>
       </c>
       <c r="I82" t="n">
-        <v>0.3062</v>
+        <v>0.2987</v>
       </c>
       <c r="J82" t="n">
-        <v>7.3488</v>
+        <v>7.1688</v>
       </c>
     </row>
     <row r="83">
@@ -5669,10 +5669,10 @@
         <v>1.12</v>
       </c>
       <c r="I83" t="n">
-        <v>0.2608</v>
+        <v>0.2495</v>
       </c>
       <c r="J83" t="n">
-        <v>6.2592</v>
+        <v>5.988</v>
       </c>
     </row>
     <row r="84">
@@ -5709,10 +5709,10 @@
         <v>0.98</v>
       </c>
       <c r="I84" t="n">
-        <v>-0.0276</v>
+        <v>-0.0204</v>
       </c>
       <c r="J84" t="n">
-        <v>-0.6624</v>
+        <v>-0.4896</v>
       </c>
     </row>
     <row r="85">
@@ -5749,10 +5749,10 @@
         <v>0.5</v>
       </c>
       <c r="I85" t="n">
-        <v>-0.5098</v>
+        <v>-0.5107</v>
       </c>
       <c r="J85" t="n">
-        <v>-12.2352</v>
+        <v>-12.2568</v>
       </c>
     </row>
     <row r="86">
@@ -5789,10 +5789,10 @@
         <v>0.46</v>
       </c>
       <c r="I86" t="n">
-        <v>-0.544</v>
+        <v>-0.5499000000000001</v>
       </c>
       <c r="J86" t="n">
-        <v>-13.056</v>
+        <v>-13.1976</v>
       </c>
     </row>
     <row r="87">
@@ -5829,10 +5829,10 @@
         <v>1.54</v>
       </c>
       <c r="I87" t="n">
-        <v>0.663</v>
+        <v>0.591</v>
       </c>
       <c r="J87" t="n">
-        <v>15.912</v>
+        <v>14.184</v>
       </c>
     </row>
     <row r="88">
@@ -5869,10 +5869,10 @@
         <v>1.27</v>
       </c>
       <c r="I88" t="n">
-        <v>0.3781</v>
+        <v>0.3184</v>
       </c>
       <c r="J88" t="n">
-        <v>9.074400000000001</v>
+        <v>7.6416</v>
       </c>
     </row>
     <row r="89">
@@ -5909,10 +5909,10 @@
         <v>1.18</v>
       </c>
       <c r="I89" t="n">
-        <v>0.2743</v>
+        <v>0.225</v>
       </c>
       <c r="J89" t="n">
-        <v>6.5832</v>
+        <v>5.4</v>
       </c>
     </row>
     <row r="90">
@@ -5949,10 +5949,10 @@
         <v>1.11</v>
       </c>
       <c r="I90" t="n">
-        <v>0.1829</v>
+        <v>0.145</v>
       </c>
       <c r="J90" t="n">
-        <v>4.3896</v>
+        <v>3.48</v>
       </c>
     </row>
     <row r="91">
@@ -5989,10 +5989,10 @@
         <v>0.98</v>
       </c>
       <c r="I91" t="n">
-        <v>-0.0592</v>
+        <v>-0.0469</v>
       </c>
       <c r="J91" t="n">
-        <v>-1.4208</v>
+        <v>-1.1256</v>
       </c>
     </row>
     <row r="92">
@@ -6029,10 +6029,10 @@
         <v>1.42</v>
       </c>
       <c r="I92" t="n">
-        <v>1.0083</v>
+        <v>1.007</v>
       </c>
       <c r="J92" t="n">
-        <v>27.2241</v>
+        <v>27.189</v>
       </c>
     </row>
     <row r="93">
@@ -6069,10 +6069,10 @@
         <v>1.18</v>
       </c>
       <c r="I93" t="n">
-        <v>0.5145</v>
+        <v>0.4752</v>
       </c>
       <c r="J93" t="n">
-        <v>13.8915</v>
+        <v>12.8304</v>
       </c>
     </row>
     <row r="94">
@@ -6109,10 +6109,10 @@
         <v>1.13</v>
       </c>
       <c r="I94" t="n">
-        <v>0.3974</v>
+        <v>0.3585</v>
       </c>
       <c r="J94" t="n">
-        <v>10.7298</v>
+        <v>9.679500000000001</v>
       </c>
     </row>
     <row r="95">
@@ -6149,10 +6149,10 @@
         <v>0.92</v>
       </c>
       <c r="I95" t="n">
-        <v>-0.3083</v>
+        <v>-0.2669</v>
       </c>
       <c r="J95" t="n">
-        <v>-8.3241</v>
+        <v>-7.2063</v>
       </c>
     </row>
     <row r="96">
@@ -6189,10 +6189,10 @@
         <v>0.88</v>
       </c>
       <c r="I96" t="n">
-        <v>-0.4151</v>
+        <v>-0.3724</v>
       </c>
       <c r="J96" t="n">
-        <v>-11.2077</v>
+        <v>-10.0548</v>
       </c>
     </row>
     <row r="97">
@@ -6229,10 +6229,10 @@
         <v>1.31</v>
       </c>
       <c r="I97" t="n">
-        <v>0.6087</v>
+        <v>0.5496</v>
       </c>
       <c r="J97" t="n">
-        <v>16.4349</v>
+        <v>14.8392</v>
       </c>
     </row>
     <row r="98">
@@ -6269,10 +6269,10 @@
         <v>1.11</v>
       </c>
       <c r="I98" t="n">
-        <v>0.269</v>
+        <v>0.2212</v>
       </c>
       <c r="J98" t="n">
-        <v>7.263</v>
+        <v>5.9724</v>
       </c>
     </row>
     <row r="99">
@@ -6309,10 +6309,10 @@
         <v>1.02</v>
       </c>
       <c r="I99" t="n">
-        <v>0.07190000000000001</v>
+        <v>0.0518</v>
       </c>
       <c r="J99" t="n">
-        <v>1.9413</v>
+        <v>1.3986</v>
       </c>
     </row>
     <row r="100">
@@ -6349,10 +6349,10 @@
         <v>0.83</v>
       </c>
       <c r="I100" t="n">
-        <v>-0.2236</v>
+        <v>-0.2031</v>
       </c>
       <c r="J100" t="n">
-        <v>-6.0372</v>
+        <v>-5.4837</v>
       </c>
     </row>
     <row r="101">
@@ -6389,10 +6389,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I101" t="n">
-        <v>-0.2439</v>
+        <v>-0.2238</v>
       </c>
       <c r="J101" t="n">
-        <v>-6.5853</v>
+        <v>-6.0426</v>
       </c>
     </row>
     <row r="102">
@@ -6429,10 +6429,10 @@
         <v>1.38</v>
       </c>
       <c r="I102" t="n">
-        <v>0.9239000000000001</v>
+        <v>0.9085</v>
       </c>
       <c r="J102" t="n">
-        <v>27.717</v>
+        <v>27.255</v>
       </c>
     </row>
     <row r="103">
@@ -6469,10 +6469,10 @@
         <v>1.37</v>
       </c>
       <c r="I103" t="n">
-        <v>0.9045</v>
+        <v>0.887</v>
       </c>
       <c r="J103" t="n">
-        <v>27.135</v>
+        <v>26.61</v>
       </c>
     </row>
     <row r="104">
@@ -6509,10 +6509,10 @@
         <v>1.2</v>
       </c>
       <c r="I104" t="n">
-        <v>0.5514</v>
+        <v>0.5147</v>
       </c>
       <c r="J104" t="n">
-        <v>16.542</v>
+        <v>15.441</v>
       </c>
     </row>
     <row r="105">
@@ -6549,10 +6549,10 @@
         <v>1.09</v>
       </c>
       <c r="I105" t="n">
-        <v>0.2919</v>
+        <v>0.2583</v>
       </c>
       <c r="J105" t="n">
-        <v>8.757</v>
+        <v>7.749</v>
       </c>
     </row>
     <row r="106">
@@ -6589,10 +6589,10 @@
         <v>0.71</v>
       </c>
       <c r="I106" t="n">
-        <v>-0.8156</v>
+        <v>-0.7954</v>
       </c>
       <c r="J106" t="n">
-        <v>-24.468</v>
+        <v>-23.862</v>
       </c>
     </row>
     <row r="107">
@@ -6629,10 +6629,10 @@
         <v>1.33</v>
       </c>
       <c r="I107" t="n">
-        <v>0.6354</v>
+        <v>0.5764</v>
       </c>
       <c r="J107" t="n">
-        <v>19.062</v>
+        <v>17.292</v>
       </c>
     </row>
     <row r="108">
@@ -6669,10 +6669,10 @@
         <v>1.25</v>
       </c>
       <c r="I108" t="n">
-        <v>0.5092</v>
+        <v>0.4499</v>
       </c>
       <c r="J108" t="n">
-        <v>15.276</v>
+        <v>13.497</v>
       </c>
     </row>
     <row r="109">
@@ -6709,10 +6709,10 @@
         <v>0.93</v>
       </c>
       <c r="I109" t="n">
-        <v>-0.1141</v>
+        <v>-0.0959</v>
       </c>
       <c r="J109" t="n">
-        <v>-3.423</v>
+        <v>-2.877</v>
       </c>
     </row>
     <row r="110">
@@ -6749,10 +6749,10 @@
         <v>0.88</v>
       </c>
       <c r="I110" t="n">
-        <v>-0.1721</v>
+        <v>-0.1516</v>
       </c>
       <c r="J110" t="n">
-        <v>-5.163</v>
+        <v>-4.548</v>
       </c>
     </row>
     <row r="111">
@@ -6789,10 +6789,10 @@
         <v>0.77</v>
       </c>
       <c r="I111" t="n">
-        <v>-0.2846</v>
+        <v>-0.2661</v>
       </c>
       <c r="J111" t="n">
-        <v>-8.538</v>
+        <v>-7.983</v>
       </c>
     </row>
     <row r="112">
@@ -6829,10 +6829,10 @@
         <v>1.21</v>
       </c>
       <c r="I112" t="n">
-        <v>0.4207</v>
+        <v>0.4351</v>
       </c>
       <c r="J112" t="n">
-        <v>9.2554</v>
+        <v>9.5722</v>
       </c>
     </row>
     <row r="113">
@@ -6869,10 +6869,10 @@
         <v>0.83</v>
       </c>
       <c r="I113" t="n">
-        <v>-0.2011</v>
+        <v>-0.1851</v>
       </c>
       <c r="J113" t="n">
-        <v>-4.4242</v>
+        <v>-4.0722</v>
       </c>
     </row>
     <row r="114">
@@ -6909,10 +6909,10 @@
         <v>0.75</v>
       </c>
       <c r="I114" t="n">
-        <v>-0.2779</v>
+        <v>-0.2615</v>
       </c>
       <c r="J114" t="n">
-        <v>-6.1138</v>
+        <v>-5.753</v>
       </c>
     </row>
     <row r="115">
@@ -6949,10 +6949,10 @@
         <v>0.54</v>
       </c>
       <c r="I115" t="n">
-        <v>-0.4667</v>
+        <v>-0.4615</v>
       </c>
       <c r="J115" t="n">
-        <v>-10.2674</v>
+        <v>-10.153</v>
       </c>
     </row>
     <row r="116">
@@ -6989,10 +6989,10 @@
         <v>0.49</v>
       </c>
       <c r="I116" t="n">
-        <v>-0.5104</v>
+        <v>-0.5105</v>
       </c>
       <c r="J116" t="n">
-        <v>-11.2288</v>
+        <v>-11.231</v>
       </c>
     </row>
     <row r="117">
@@ -7029,10 +7029,10 @@
         <v>1.86</v>
       </c>
       <c r="I117" t="n">
-        <v>0.9499</v>
+        <v>0.8847</v>
       </c>
       <c r="J117" t="n">
-        <v>20.8978</v>
+        <v>19.4634</v>
       </c>
     </row>
     <row r="118">
@@ -7069,10 +7069,10 @@
         <v>1.38</v>
       </c>
       <c r="I118" t="n">
-        <v>0.4884</v>
+        <v>0.423</v>
       </c>
       <c r="J118" t="n">
-        <v>10.7448</v>
+        <v>9.305999999999999</v>
       </c>
     </row>
     <row r="119">
@@ -7109,10 +7109,10 @@
         <v>1.25</v>
       </c>
       <c r="I119" t="n">
-        <v>0.35</v>
+        <v>0.2951</v>
       </c>
       <c r="J119" t="n">
-        <v>7.7</v>
+        <v>6.4922</v>
       </c>
     </row>
     <row r="120">
@@ -7149,10 +7149,10 @@
         <v>1.1</v>
       </c>
       <c r="I120" t="n">
-        <v>0.1604</v>
+        <v>0.1259</v>
       </c>
       <c r="J120" t="n">
-        <v>3.5288</v>
+        <v>2.7698</v>
       </c>
     </row>
     <row r="121">
@@ -7189,10 +7189,10 @@
         <v>0.96</v>
       </c>
       <c r="I121" t="n">
-        <v>-0.09619999999999999</v>
+        <v>-0.08119999999999999</v>
       </c>
       <c r="J121" t="n">
-        <v>-2.1164</v>
+        <v>-1.7864</v>
       </c>
     </row>
     <row r="122">
@@ -7229,10 +7229,10 @@
         <v>1.51</v>
       </c>
       <c r="I122" t="n">
-        <v>1.1154</v>
+        <v>1.1273</v>
       </c>
       <c r="J122" t="n">
-        <v>31.2312</v>
+        <v>31.5644</v>
       </c>
     </row>
     <row r="123">
@@ -7269,10 +7269,10 @@
         <v>1.39</v>
       </c>
       <c r="I123" t="n">
-        <v>0.9276</v>
+        <v>0.9137</v>
       </c>
       <c r="J123" t="n">
-        <v>25.9728</v>
+        <v>25.5836</v>
       </c>
     </row>
     <row r="124">
@@ -7309,10 +7309,10 @@
         <v>1.24</v>
       </c>
       <c r="I124" t="n">
-        <v>0.6279</v>
+        <v>0.5962</v>
       </c>
       <c r="J124" t="n">
-        <v>17.5812</v>
+        <v>16.6936</v>
       </c>
     </row>
     <row r="125">
@@ -7349,10 +7349,10 @@
         <v>0.99</v>
       </c>
       <c r="I125" t="n">
-        <v>-0.0955</v>
+        <v>-0.0746</v>
       </c>
       <c r="J125" t="n">
-        <v>-2.674</v>
+        <v>-2.0888</v>
       </c>
     </row>
     <row r="126">
@@ -7389,10 +7389,10 @@
         <v>0.93</v>
       </c>
       <c r="I126" t="n">
-        <v>-0.2992</v>
+        <v>-0.26</v>
       </c>
       <c r="J126" t="n">
-        <v>-8.377599999999999</v>
+        <v>-7.28</v>
       </c>
     </row>
     <row r="127">
@@ -7429,10 +7429,10 @@
         <v>1.42</v>
       </c>
       <c r="I127" t="n">
-        <v>0.8148</v>
+        <v>0.7708</v>
       </c>
       <c r="J127" t="n">
-        <v>22.8144</v>
+        <v>21.5824</v>
       </c>
     </row>
     <row r="128">
@@ -7469,10 +7469,10 @@
         <v>0.82</v>
       </c>
       <c r="I128" t="n">
-        <v>-0.2242</v>
+        <v>-0.2042</v>
       </c>
       <c r="J128" t="n">
-        <v>-6.2776</v>
+        <v>-5.7176</v>
       </c>
     </row>
     <row r="129">
@@ -7509,10 +7509,10 @@
         <v>0.8</v>
       </c>
       <c r="I129" t="n">
-        <v>-0.2441</v>
+        <v>-0.2243</v>
       </c>
       <c r="J129" t="n">
-        <v>-6.8348</v>
+        <v>-6.2804</v>
       </c>
     </row>
     <row r="130">
@@ -7549,10 +7549,10 @@
         <v>0.76</v>
       </c>
       <c r="I130" t="n">
-        <v>-0.283</v>
+        <v>-0.2642</v>
       </c>
       <c r="J130" t="n">
-        <v>-7.924</v>
+        <v>-7.3976</v>
       </c>
     </row>
     <row r="131">
@@ -7589,10 +7589,10 @@
         <v>0.76</v>
       </c>
       <c r="I131" t="n">
-        <v>-0.283</v>
+        <v>-0.2642</v>
       </c>
       <c r="J131" t="n">
-        <v>-7.924</v>
+        <v>-7.3976</v>
       </c>
     </row>
     <row r="132">
@@ -7629,10 +7629,10 @@
         <v>1.26</v>
       </c>
       <c r="I132" t="n">
-        <v>0.6984</v>
+        <v>0.6647999999999999</v>
       </c>
       <c r="J132" t="n">
-        <v>19.5552</v>
+        <v>18.6144</v>
       </c>
     </row>
     <row r="133">
@@ -7669,10 +7669,10 @@
         <v>1.21</v>
       </c>
       <c r="I133" t="n">
-        <v>0.5888</v>
+        <v>0.5502</v>
       </c>
       <c r="J133" t="n">
-        <v>16.4864</v>
+        <v>15.4056</v>
       </c>
     </row>
     <row r="134">
@@ -7709,10 +7709,10 @@
         <v>1.08</v>
       </c>
       <c r="I134" t="n">
-        <v>0.2746</v>
+        <v>0.2387</v>
       </c>
       <c r="J134" t="n">
-        <v>7.6888</v>
+        <v>6.6836</v>
       </c>
     </row>
     <row r="135">
@@ -7749,10 +7749,10 @@
         <v>1.06</v>
       </c>
       <c r="I135" t="n">
-        <v>0.2195</v>
+        <v>0.1871</v>
       </c>
       <c r="J135" t="n">
-        <v>6.146</v>
+        <v>5.2388</v>
       </c>
     </row>
     <row r="136">
@@ -7789,10 +7789,10 @@
         <v>0.77</v>
       </c>
       <c r="I136" t="n">
-        <v>-0.6711</v>
+        <v>-0.6373</v>
       </c>
       <c r="J136" t="n">
-        <v>-18.7908</v>
+        <v>-17.8444</v>
       </c>
     </row>
     <row r="137">
@@ -7829,10 +7829,10 @@
         <v>1.28</v>
       </c>
       <c r="I137" t="n">
-        <v>0.5667</v>
+        <v>0.5076000000000001</v>
       </c>
       <c r="J137" t="n">
-        <v>15.8676</v>
+        <v>14.2128</v>
       </c>
     </row>
     <row r="138">
@@ -7869,10 +7869,10 @@
         <v>1.23</v>
       </c>
       <c r="I138" t="n">
-        <v>0.4852</v>
+        <v>0.4265</v>
       </c>
       <c r="J138" t="n">
-        <v>13.5856</v>
+        <v>11.942</v>
       </c>
     </row>
     <row r="139">
@@ -7909,10 +7909,10 @@
         <v>0.95</v>
       </c>
       <c r="I139" t="n">
-        <v>-0.0858</v>
+        <v>-0.0702</v>
       </c>
       <c r="J139" t="n">
-        <v>-2.4024</v>
+        <v>-1.9656</v>
       </c>
     </row>
     <row r="140">
@@ -7949,10 +7949,10 @@
         <v>0.8100000000000001</v>
       </c>
       <c r="I140" t="n">
-        <v>-0.2421</v>
+        <v>-0.2219</v>
       </c>
       <c r="J140" t="n">
-        <v>-6.7788</v>
+        <v>-6.2132</v>
       </c>
     </row>
     <row r="141">
@@ -7989,10 +7989,10 @@
         <v>0.71</v>
       </c>
       <c r="I141" t="n">
-        <v>-0.3381</v>
+        <v>-0.3226</v>
       </c>
       <c r="J141" t="n">
-        <v>-9.466799999999999</v>
+        <v>-9.0328</v>
       </c>
     </row>
     <row r="142">
@@ -8029,10 +8029,10 @@
         <v>2.12</v>
       </c>
       <c r="I142" t="n">
-        <v>1.8088</v>
+        <v>1.8677</v>
       </c>
       <c r="J142" t="n">
-        <v>37.9848</v>
+        <v>39.2217</v>
       </c>
     </row>
     <row r="143">
@@ -8069,10 +8069,10 @@
         <v>2</v>
       </c>
       <c r="I143" t="n">
-        <v>1.6707</v>
+        <v>1.7157</v>
       </c>
       <c r="J143" t="n">
-        <v>35.0847</v>
+        <v>36.0297</v>
       </c>
     </row>
     <row r="144">
@@ -8109,10 +8109,10 @@
         <v>1.32</v>
       </c>
       <c r="I144" t="n">
-        <v>0.7549</v>
+        <v>0.7401</v>
       </c>
       <c r="J144" t="n">
-        <v>15.8529</v>
+        <v>15.5421</v>
       </c>
     </row>
     <row r="145">
@@ -8149,10 +8149,10 @@
         <v>1.17</v>
       </c>
       <c r="I145" t="n">
-        <v>0.4368</v>
+        <v>0.4056</v>
       </c>
       <c r="J145" t="n">
-        <v>9.172800000000001</v>
+        <v>8.5176</v>
       </c>
     </row>
     <row r="146">
@@ -8189,10 +8189,10 @@
         <v>0.83</v>
       </c>
       <c r="I146" t="n">
-        <v>-0.597</v>
+        <v>-0.5702</v>
       </c>
       <c r="J146" t="n">
-        <v>-12.537</v>
+        <v>-11.9742</v>
       </c>
     </row>
     <row r="147">
@@ -8229,10 +8229,10 @@
         <v>0.95</v>
       </c>
       <c r="I147" t="n">
-        <v>-0.0371</v>
+        <v>-0.0203</v>
       </c>
       <c r="J147" t="n">
-        <v>-0.7791</v>
+        <v>-0.4263</v>
       </c>
     </row>
     <row r="148">
@@ -8269,10 +8269,10 @@
         <v>0.88</v>
       </c>
       <c r="I148" t="n">
-        <v>-0.1279</v>
+        <v>-0.1107</v>
       </c>
       <c r="J148" t="n">
-        <v>-2.6859</v>
+        <v>-2.3247</v>
       </c>
     </row>
     <row r="149">
@@ -8309,10 +8309,10 @@
         <v>0.84</v>
       </c>
       <c r="I149" t="n">
-        <v>-0.1738</v>
+        <v>-0.1576</v>
       </c>
       <c r="J149" t="n">
-        <v>-3.6498</v>
+        <v>-3.3096</v>
       </c>
     </row>
     <row r="150">
@@ -8349,10 +8349,10 @@
         <v>0.34</v>
       </c>
       <c r="I150" t="n">
-        <v>-0.6296</v>
+        <v>-0.6471</v>
       </c>
       <c r="J150" t="n">
-        <v>-13.2216</v>
+        <v>-13.5891</v>
       </c>
     </row>
     <row r="151">
@@ -8389,10 +8389,10 @@
         <v>0.34</v>
       </c>
       <c r="I151" t="n">
-        <v>-0.6296</v>
+        <v>-0.6471</v>
       </c>
       <c r="J151" t="n">
-        <v>-13.2216</v>
+        <v>-13.5891</v>
       </c>
     </row>
     <row r="152">
@@ -8429,10 +8429,10 @@
         <v>0.87</v>
       </c>
       <c r="I152" t="n">
-        <v>-0.124</v>
+        <v>-0.1036</v>
       </c>
       <c r="J152" t="n">
-        <v>-2.232</v>
+        <v>-1.8648</v>
       </c>
     </row>
     <row r="153">
@@ -8469,10 +8469,10 @@
         <v>0.76</v>
       </c>
       <c r="I153" t="n">
-        <v>-0.2461</v>
+        <v>-0.232</v>
       </c>
       <c r="J153" t="n">
-        <v>-4.4298</v>
+        <v>-4.176</v>
       </c>
     </row>
     <row r="154">
@@ -8509,10 +8509,10 @@
         <v>0.58</v>
       </c>
       <c r="I154" t="n">
-        <v>-0.4122</v>
+        <v>-0.4041</v>
       </c>
       <c r="J154" t="n">
-        <v>-7.4196</v>
+        <v>-7.2738</v>
       </c>
     </row>
     <row r="155">
@@ -8549,10 +8549,10 @@
         <v>0.54</v>
       </c>
       <c r="I155" t="n">
-        <v>-0.447</v>
+        <v>-0.4407</v>
       </c>
       <c r="J155" t="n">
-        <v>-8.045999999999999</v>
+        <v>-7.9326</v>
       </c>
     </row>
     <row r="156">
@@ -8589,10 +8589,10 @@
         <v>0.32</v>
       </c>
       <c r="I156" t="n">
-        <v>-0.6405999999999999</v>
+        <v>-0.6592</v>
       </c>
       <c r="J156" t="n">
-        <v>-11.5308</v>
+        <v>-11.8656</v>
       </c>
     </row>
     <row r="157">
@@ -8629,10 +8629,10 @@
         <v>1.9</v>
       </c>
       <c r="I157" t="n">
-        <v>1.5463</v>
+        <v>1.5814</v>
       </c>
       <c r="J157" t="n">
-        <v>27.8334</v>
+        <v>28.4652</v>
       </c>
     </row>
     <row r="158">
@@ -8669,10 +8669,10 @@
         <v>1.5</v>
       </c>
       <c r="I158" t="n">
-        <v>1.0607</v>
+        <v>1.077</v>
       </c>
       <c r="J158" t="n">
-        <v>19.0926</v>
+        <v>19.386</v>
       </c>
     </row>
     <row r="159">
@@ -8709,10 +8709,10 @@
         <v>1.48</v>
       </c>
       <c r="I159" t="n">
-        <v>1.0334</v>
+        <v>1.0469</v>
       </c>
       <c r="J159" t="n">
-        <v>18.6012</v>
+        <v>18.8442</v>
       </c>
     </row>
     <row r="160">
@@ -8749,10 +8749,10 @@
         <v>1.44</v>
       </c>
       <c r="I160" t="n">
-        <v>0.9723000000000001</v>
+        <v>0.9778</v>
       </c>
       <c r="J160" t="n">
-        <v>17.5014</v>
+        <v>17.6004</v>
       </c>
     </row>
     <row r="161">
@@ -8789,10 +8789,10 @@
         <v>1.33</v>
       </c>
       <c r="I161" t="n">
-        <v>0.7689</v>
+        <v>0.7558</v>
       </c>
       <c r="J161" t="n">
-        <v>13.8402</v>
+        <v>13.6044</v>
       </c>
     </row>
     <row r="162">
@@ -8829,10 +8829,10 @@
         <v>1.31</v>
       </c>
       <c r="I162" t="n">
-        <v>0.5885</v>
+        <v>0.5286999999999999</v>
       </c>
       <c r="J162" t="n">
-        <v>17.655</v>
+        <v>15.861</v>
       </c>
     </row>
     <row r="163">
@@ -8869,10 +8869,10 @@
         <v>1.24</v>
       </c>
       <c r="I163" t="n">
-        <v>0.4792</v>
+        <v>0.421</v>
       </c>
       <c r="J163" t="n">
-        <v>14.376</v>
+        <v>12.63</v>
       </c>
     </row>
     <row r="164">
@@ -8909,10 +8909,10 @@
         <v>1.12</v>
       </c>
       <c r="I164" t="n">
-        <v>0.276</v>
+        <v>0.2301</v>
       </c>
       <c r="J164" t="n">
-        <v>8.279999999999999</v>
+        <v>6.903</v>
       </c>
     </row>
     <row r="165">
@@ -8949,10 +8949,10 @@
         <v>1.04</v>
       </c>
       <c r="I165" t="n">
-        <v>0.1144</v>
+        <v>0.0885</v>
       </c>
       <c r="J165" t="n">
-        <v>3.432</v>
+        <v>2.655</v>
       </c>
     </row>
     <row r="166">
@@ -8989,10 +8989,10 @@
         <v>0.79</v>
       </c>
       <c r="I166" t="n">
-        <v>-0.2709</v>
+        <v>-0.2523</v>
       </c>
       <c r="J166" t="n">
-        <v>-8.127000000000001</v>
+        <v>-7.569</v>
       </c>
     </row>
     <row r="167">
@@ -9029,10 +9029,10 @@
         <v>1.18</v>
       </c>
       <c r="I167" t="n">
-        <v>0.5484</v>
+        <v>0.5078</v>
       </c>
       <c r="J167" t="n">
-        <v>16.452</v>
+        <v>15.234</v>
       </c>
     </row>
     <row r="168">
@@ -9069,10 +9069,10 @@
         <v>1.11</v>
       </c>
       <c r="I168" t="n">
-        <v>0.3746</v>
+        <v>0.3317</v>
       </c>
       <c r="J168" t="n">
-        <v>11.238</v>
+        <v>9.951000000000001</v>
       </c>
     </row>
     <row r="169">
@@ -9109,10 +9109,10 @@
         <v>0.97</v>
       </c>
       <c r="I169" t="n">
-        <v>-0.132</v>
+        <v>-0.1057</v>
       </c>
       <c r="J169" t="n">
-        <v>-3.96</v>
+        <v>-3.171</v>
       </c>
     </row>
     <row r="170">
@@ -9149,10 +9149,10 @@
         <v>0.84</v>
       </c>
       <c r="I170" t="n">
-        <v>-0.4881</v>
+        <v>-0.4459</v>
       </c>
       <c r="J170" t="n">
-        <v>-14.643</v>
+        <v>-13.377</v>
       </c>
     </row>
     <row r="171">
@@ -9189,10 +9189,10 @@
         <v>0.78</v>
       </c>
       <c r="I171" t="n">
-        <v>-0.628</v>
+        <v>-0.5904</v>
       </c>
       <c r="J171" t="n">
-        <v>-18.84</v>
+        <v>-17.712</v>
       </c>
     </row>
     <row r="172">
@@ -9229,10 +9229,10 @@
         <v>1.34</v>
       </c>
       <c r="I172" t="n">
-        <v>0.6768</v>
+        <v>0.622</v>
       </c>
       <c r="J172" t="n">
-        <v>16.92</v>
+        <v>15.55</v>
       </c>
     </row>
     <row r="173">
@@ -9269,10 +9269,10 @@
         <v>1.09</v>
       </c>
       <c r="I173" t="n">
-        <v>0.2429</v>
+        <v>0.1969</v>
       </c>
       <c r="J173" t="n">
-        <v>6.0725</v>
+        <v>4.9225</v>
       </c>
     </row>
     <row r="174">
@@ -9309,10 +9309,10 @@
         <v>0.92</v>
       </c>
       <c r="I174" t="n">
-        <v>-0.1195</v>
+        <v>-0.1021</v>
       </c>
       <c r="J174" t="n">
-        <v>-2.9875</v>
+        <v>-2.5525</v>
       </c>
     </row>
     <row r="175">
@@ -9349,10 +9349,10 @@
         <v>0.76</v>
       </c>
       <c r="I175" t="n">
-        <v>-0.2865</v>
+        <v>-0.2678</v>
       </c>
       <c r="J175" t="n">
-        <v>-7.1625</v>
+        <v>-6.695</v>
       </c>
     </row>
     <row r="176">
@@ -9389,10 +9389,10 @@
         <v>0.63</v>
       </c>
       <c r="I176" t="n">
-        <v>-0.4063</v>
+        <v>-0.3961</v>
       </c>
       <c r="J176" t="n">
-        <v>-10.1575</v>
+        <v>-9.9025</v>
       </c>
     </row>
     <row r="177">
@@ -9429,10 +9429,10 @@
         <v>1.5</v>
       </c>
       <c r="I177" t="n">
-        <v>1.1337</v>
+        <v>1.1483</v>
       </c>
       <c r="J177" t="n">
-        <v>28.3425</v>
+        <v>28.7075</v>
       </c>
     </row>
     <row r="178">
@@ -9469,10 +9469,10 @@
         <v>1.18</v>
       </c>
       <c r="I178" t="n">
-        <v>0.519</v>
+        <v>0.4789</v>
       </c>
       <c r="J178" t="n">
-        <v>12.975</v>
+        <v>11.9725</v>
       </c>
     </row>
     <row r="179">
@@ -9509,10 +9509,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I179" t="n">
-        <v>-0.2464</v>
+        <v>-0.2076</v>
       </c>
       <c r="J179" t="n">
-        <v>-6.16</v>
+        <v>-5.19</v>
       </c>
     </row>
     <row r="180">
@@ -9549,10 +9549,10 @@
         <v>0.92</v>
       </c>
       <c r="I180" t="n">
-        <v>-0.3041</v>
+        <v>-0.2627</v>
       </c>
       <c r="J180" t="n">
-        <v>-7.6025</v>
+        <v>-6.5675</v>
       </c>
     </row>
     <row r="181">
@@ -9589,10 +9589,10 @@
         <v>0.88</v>
       </c>
       <c r="I181" t="n">
-        <v>-0.4109</v>
+        <v>-0.3679</v>
       </c>
       <c r="J181" t="n">
-        <v>-10.2725</v>
+        <v>-9.1975</v>
       </c>
     </row>
     <row r="182">
@@ -9629,10 +9629,10 @@
         <v>1.1</v>
       </c>
       <c r="I182" t="n">
-        <v>0.2702</v>
+        <v>0.2222</v>
       </c>
       <c r="J182" t="n">
-        <v>7.0252</v>
+        <v>5.7772</v>
       </c>
     </row>
     <row r="183">
@@ -9669,10 +9669,10 @@
         <v>0.99</v>
       </c>
       <c r="I183" t="n">
-        <v>-0.0192</v>
+        <v>-0.0142</v>
       </c>
       <c r="J183" t="n">
-        <v>-0.4992</v>
+        <v>-0.3692</v>
       </c>
     </row>
     <row r="184">
@@ -9709,10 +9709,10 @@
         <v>0.98</v>
       </c>
       <c r="I184" t="n">
-        <v>-0.0371</v>
+        <v>-0.029</v>
       </c>
       <c r="J184" t="n">
-        <v>-0.9646</v>
+        <v>-0.754</v>
       </c>
     </row>
     <row r="185">
@@ -9749,10 +9749,10 @@
         <v>0.9399999999999999</v>
       </c>
       <c r="I185" t="n">
-        <v>-0.09379999999999999</v>
+        <v>-0.0791</v>
       </c>
       <c r="J185" t="n">
-        <v>-2.4388</v>
+        <v>-2.0566</v>
       </c>
     </row>
     <row r="186">
@@ -9789,10 +9789,10 @@
         <v>0.58</v>
       </c>
       <c r="I186" t="n">
-        <v>-0.4476</v>
+        <v>-0.4416</v>
       </c>
       <c r="J186" t="n">
-        <v>-11.6376</v>
+        <v>-11.4816</v>
       </c>
     </row>
     <row r="187">
@@ -9829,10 +9829,10 @@
         <v>1.47</v>
       </c>
       <c r="I187" t="n">
-        <v>1.0658</v>
+        <v>1.0735</v>
       </c>
       <c r="J187" t="n">
-        <v>27.7108</v>
+        <v>27.911</v>
       </c>
     </row>
     <row r="188">
@@ -9869,10 +9869,10 @@
         <v>1.3</v>
       </c>
       <c r="I188" t="n">
-        <v>0.7561</v>
+        <v>0.7285</v>
       </c>
       <c r="J188" t="n">
-        <v>19.6586</v>
+        <v>18.941</v>
       </c>
     </row>
     <row r="189">
@@ -9909,10 +9909,10 @@
         <v>1.16</v>
       </c>
       <c r="I189" t="n">
-        <v>0.4589</v>
+        <v>0.4234</v>
       </c>
       <c r="J189" t="n">
-        <v>11.9314</v>
+        <v>11.0084</v>
       </c>
     </row>
     <row r="190">
@@ -9949,10 +9949,10 @@
         <v>1.03</v>
       </c>
       <c r="I190" t="n">
-        <v>0.1069</v>
+        <v>0.0863</v>
       </c>
       <c r="J190" t="n">
-        <v>2.7794</v>
+        <v>2.2438</v>
       </c>
     </row>
     <row r="191">
@@ -9989,10 +9989,10 @@
         <v>0.96</v>
       </c>
       <c r="I191" t="n">
-        <v>-0.2025</v>
+        <v>-0.168</v>
       </c>
       <c r="J191" t="n">
-        <v>-5.265</v>
+        <v>-4.368</v>
       </c>
     </row>
     <row r="192">
@@ -10029,10 +10029,10 @@
         <v>0.87</v>
       </c>
       <c r="I192" t="n">
-        <v>-0.0256</v>
+        <v>0.068</v>
       </c>
       <c r="J192" t="n">
-        <v>-0.4352</v>
+        <v>1.156</v>
       </c>
     </row>
     <row r="193">
@@ -10069,10 +10069,10 @@
         <v>0.36</v>
       </c>
       <c r="I193" t="n">
-        <v>-0.5735</v>
+        <v>-0.5810999999999999</v>
       </c>
       <c r="J193" t="n">
-        <v>-9.749499999999999</v>
+        <v>-9.8787</v>
       </c>
     </row>
     <row r="194">
@@ -10109,10 +10109,10 @@
         <v>0.34</v>
       </c>
       <c r="I194" t="n">
-        <v>-0.5917</v>
+        <v>-0.6012</v>
       </c>
       <c r="J194" t="n">
-        <v>-10.0589</v>
+        <v>-10.2204</v>
       </c>
     </row>
     <row r="195">
@@ -10149,10 +10149,10 @@
         <v>0.28</v>
       </c>
       <c r="I195" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="J195" t="n">
-        <v>-11.0109</v>
+        <v>-11.3016</v>
       </c>
     </row>
     <row r="196">
@@ -10189,10 +10189,10 @@
         <v>0.28</v>
       </c>
       <c r="I196" t="n">
-        <v>-0.6477000000000001</v>
+        <v>-0.6647999999999999</v>
       </c>
       <c r="J196" t="n">
-        <v>-11.0109</v>
+        <v>-11.3016</v>
       </c>
     </row>
     <row r="197">
@@ -10229,10 +10229,10 @@
         <v>2.19</v>
       </c>
       <c r="I197" t="n">
-        <v>1.8616</v>
+        <v>1.9247</v>
       </c>
       <c r="J197" t="n">
-        <v>31.6472</v>
+        <v>32.7199</v>
       </c>
     </row>
     <row r="198">
@@ -10269,10 +10269,10 @@
         <v>1.62</v>
       </c>
       <c r="I198" t="n">
-        <v>1.2035</v>
+        <v>1.2261</v>
       </c>
       <c r="J198" t="n">
-        <v>20.4595</v>
+        <v>20.8437</v>
       </c>
     </row>
     <row r="199">
@@ -10309,10 +10309,10 @@
         <v>1.59</v>
       </c>
       <c r="I199" t="n">
-        <v>1.1677</v>
+        <v>1.1898</v>
       </c>
       <c r="J199" t="n">
-        <v>19.8509</v>
+        <v>20.2266</v>
       </c>
     </row>
     <row r="200">
@@ -10349,10 +10349,10 @@
         <v>1.41</v>
       </c>
       <c r="I200" t="n">
-        <v>0.9102</v>
+        <v>0.9103</v>
       </c>
       <c r="J200" t="n">
-        <v>15.4734</v>
+        <v>15.4751</v>
       </c>
     </row>
     <row r="201">
@@ -10389,10 +10389,10 @@
         <v>1.25</v>
       </c>
       <c r="I201" t="n">
-        <v>0.5957</v>
+        <v>0.5712</v>
       </c>
       <c r="J201" t="n">
-        <v>10.1269</v>
+        <v>9.7104</v>
       </c>
     </row>
     <row r="202">
@@ -10429,10 +10429,10 @@
         <v>1.41</v>
       </c>
       <c r="I202" t="n">
-        <v>0.9540999999999999</v>
+        <v>0.9451000000000001</v>
       </c>
       <c r="J202" t="n">
-        <v>23.8525</v>
+        <v>23.6275</v>
       </c>
     </row>
     <row r="203">
@@ -10469,10 +10469,10 @@
         <v>1.33</v>
       </c>
       <c r="I203" t="n">
-        <v>0.8021</v>
+        <v>0.7804</v>
       </c>
       <c r="J203" t="n">
-        <v>20.0525</v>
+        <v>19.51</v>
       </c>
     </row>
     <row r="204">
@@ -10509,10 +10509,10 @@
         <v>1.29</v>
       </c>
       <c r="I204" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.6976</v>
       </c>
       <c r="J204" t="n">
-        <v>18.0825</v>
+        <v>17.44</v>
       </c>
     </row>
     <row r="205">
@@ -10549,10 +10549,10 @@
         <v>1.2</v>
       </c>
       <c r="I205" t="n">
-        <v>0.5383</v>
+        <v>0.507</v>
       </c>
       <c r="J205" t="n">
-        <v>13.4575</v>
+        <v>12.675</v>
       </c>
     </row>
     <row r="206">
@@ -10589,10 +10589,10 @@
         <v>1.07</v>
       </c>
       <c r="I206" t="n">
-        <v>0.2186</v>
+        <v>0.1895</v>
       </c>
       <c r="J206" t="n">
-        <v>5.465</v>
+        <v>4.7375</v>
       </c>
     </row>
     <row r="207">
@@ -10629,10 +10629,10 @@
         <v>0.96</v>
       </c>
       <c r="I207" t="n">
-        <v>-0.0577</v>
+        <v>-0.0469</v>
       </c>
       <c r="J207" t="n">
-        <v>-1.4425</v>
+        <v>-1.1725</v>
       </c>
     </row>
     <row r="208">
@@ -10669,10 +10669,10 @@
         <v>0.85</v>
       </c>
       <c r="I208" t="n">
-        <v>-0.188</v>
+        <v>-0.1704</v>
       </c>
       <c r="J208" t="n">
-        <v>-4.7</v>
+        <v>-4.26</v>
       </c>
     </row>
     <row r="209">
@@ -10709,10 +10709,10 @@
         <v>0.84</v>
       </c>
       <c r="I209" t="n">
-        <v>-0.198</v>
+        <v>-0.1801</v>
       </c>
       <c r="J209" t="n">
-        <v>-4.95</v>
+        <v>-4.5025</v>
       </c>
     </row>
     <row r="210">
@@ -10749,10 +10749,10 @@
         <v>0.79</v>
       </c>
       <c r="I210" t="n">
-        <v>-0.2466</v>
+        <v>-0.228</v>
       </c>
       <c r="J210" t="n">
-        <v>-6.165</v>
+        <v>-5.7</v>
       </c>
     </row>
     <row r="211">
@@ -10789,10 +10789,10 @@
         <v>0.74</v>
       </c>
       <c r="I211" t="n">
-        <v>-0.2942</v>
+        <v>-0.2765</v>
       </c>
       <c r="J211" t="n">
-        <v>-7.355</v>
+        <v>-6.9125</v>
       </c>
     </row>
     <row r="212">
@@ -10829,10 +10829,10 @@
         <v>1.44</v>
       </c>
       <c r="I212" t="n">
-        <v>0.7782</v>
+        <v>0.7222</v>
       </c>
       <c r="J212" t="n">
-        <v>20.2332</v>
+        <v>18.7772</v>
       </c>
     </row>
     <row r="213">
@@ -10869,10 +10869,10 @@
         <v>1.22</v>
       </c>
       <c r="I213" t="n">
-        <v>0.4453</v>
+        <v>0.3885</v>
       </c>
       <c r="J213" t="n">
-        <v>11.5778</v>
+        <v>10.101</v>
       </c>
     </row>
     <row r="214">
@@ -10909,10 +10909,10 @@
         <v>1.05</v>
       </c>
       <c r="I214" t="n">
-        <v>0.1364</v>
+        <v>0.1073</v>
       </c>
       <c r="J214" t="n">
-        <v>3.5464</v>
+        <v>2.7898</v>
       </c>
     </row>
     <row r="215">
@@ -10949,10 +10949,10 @@
         <v>1</v>
       </c>
       <c r="I215" t="n">
-        <v>-0.0075</v>
+        <v>-0.0054</v>
       </c>
       <c r="J215" t="n">
-        <v>-0.195</v>
+        <v>-0.1404</v>
       </c>
     </row>
     <row r="216">
@@ -10989,10 +10989,10 @@
         <v>0.84</v>
       </c>
       <c r="I216" t="n">
-        <v>-0.2214</v>
+        <v>-0.2013</v>
       </c>
       <c r="J216" t="n">
-        <v>-5.7564</v>
+        <v>-5.2338</v>
       </c>
     </row>
     <row r="217">
@@ -11029,10 +11029,10 @@
         <v>1.37</v>
       </c>
       <c r="I217" t="n">
-        <v>0.9258999999999999</v>
+        <v>0.9111</v>
       </c>
       <c r="J217" t="n">
-        <v>24.0734</v>
+        <v>23.6886</v>
       </c>
     </row>
     <row r="218">
@@ -11069,10 +11069,10 @@
         <v>1.19</v>
       </c>
       <c r="I218" t="n">
-        <v>0.5432</v>
+        <v>0.5034</v>
       </c>
       <c r="J218" t="n">
-        <v>14.1232</v>
+        <v>13.0884</v>
       </c>
     </row>
     <row r="219">
@@ -11109,10 +11109,10 @@
         <v>1</v>
       </c>
       <c r="I219" t="n">
-        <v>-0.0118</v>
+        <v>-0.007900000000000001</v>
       </c>
       <c r="J219" t="n">
-        <v>-0.3068</v>
+        <v>-0.2054</v>
       </c>
     </row>
     <row r="220">
@@ -11149,10 +11149,10 @@
         <v>0.95</v>
       </c>
       <c r="I220" t="n">
-        <v>-0.2148</v>
+        <v>-0.1781</v>
       </c>
       <c r="J220" t="n">
-        <v>-5.5848</v>
+        <v>-4.6306</v>
       </c>
     </row>
     <row r="221">
@@ -11189,10 +11189,10 @@
         <v>0.88</v>
       </c>
       <c r="I221" t="n">
-        <v>-0.4097</v>
+        <v>-0.3667</v>
       </c>
       <c r="J221" t="n">
-        <v>-10.6522</v>
+        <v>-9.5342</v>
       </c>
     </row>
     <row r="222">
@@ -11229,10 +11229,10 @@
         <v>1.71</v>
       </c>
       <c r="I222" t="n">
-        <v>1.3349</v>
+        <v>1.3566</v>
       </c>
       <c r="J222" t="n">
-        <v>32.0376</v>
+        <v>32.5584</v>
       </c>
     </row>
     <row r="223">
@@ -11269,10 +11269,10 @@
         <v>1.52</v>
       </c>
       <c r="I223" t="n">
-        <v>1.0946</v>
+        <v>1.1095</v>
       </c>
       <c r="J223" t="n">
-        <v>26.2704</v>
+        <v>26.628</v>
       </c>
     </row>
     <row r="224">
@@ -11309,10 +11309,10 @@
         <v>1.33</v>
       </c>
       <c r="I224" t="n">
-        <v>0.7829</v>
+        <v>0.7681</v>
       </c>
       <c r="J224" t="n">
-        <v>18.7896</v>
+        <v>18.4344</v>
       </c>
     </row>
     <row r="225">
@@ -11349,10 +11349,10 @@
         <v>1.31</v>
       </c>
       <c r="I225" t="n">
-        <v>0.7436</v>
+        <v>0.7265</v>
       </c>
       <c r="J225" t="n">
-        <v>17.8464</v>
+        <v>17.436</v>
       </c>
     </row>
     <row r="226">
@@ -11389,10 +11389,10 @@
         <v>1.26</v>
       </c>
       <c r="I226" t="n">
-        <v>0.6424</v>
+        <v>0.6195000000000001</v>
       </c>
       <c r="J226" t="n">
-        <v>15.4176</v>
+        <v>14.868</v>
       </c>
     </row>
     <row r="227">
@@ -11429,10 +11429,10 @@
         <v>1.02</v>
       </c>
       <c r="I227" t="n">
-        <v>0.1637</v>
+        <v>0.146</v>
       </c>
       <c r="J227" t="n">
-        <v>3.9288</v>
+        <v>3.504</v>
       </c>
     </row>
     <row r="228">
@@ -11469,10 +11469,10 @@
         <v>0.74</v>
       </c>
       <c r="I228" t="n">
-        <v>-0.2804</v>
+        <v>-0.2666</v>
       </c>
       <c r="J228" t="n">
-        <v>-6.7296</v>
+        <v>-6.3984</v>
       </c>
     </row>
     <row r="229">
@@ -11509,10 +11509,10 @@
         <v>0.71</v>
       </c>
       <c r="I229" t="n">
-        <v>-0.3081</v>
+        <v>-0.2947</v>
       </c>
       <c r="J229" t="n">
-        <v>-7.3944</v>
+        <v>-7.0728</v>
       </c>
     </row>
     <row r="230">
@@ -11549,10 +11549,10 @@
         <v>0.6899999999999999</v>
       </c>
       <c r="I230" t="n">
-        <v>-0.3255</v>
+        <v>-0.3122</v>
       </c>
       <c r="J230" t="n">
-        <v>-7.812</v>
+        <v>-7.4928</v>
       </c>
     </row>
     <row r="231">
@@ -11589,10 +11589,10 @@
         <v>0.3</v>
       </c>
       <c r="I231" t="n">
-        <v>-0.6662</v>
+        <v>-0.6911</v>
       </c>
       <c r="J231" t="n">
-        <v>-15.9888</v>
+        <v>-16.5864</v>
       </c>
     </row>
   </sheetData>
